--- a/Exam/Excel/advanced_assessment_project/Raw_Transactions_2024_finish.xlsx
+++ b/Exam/Excel/advanced_assessment_project/Raw_Transactions_2024_finish.xlsx
@@ -1,26 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\Project\Data-Analyst\Exam\Excel\advanced_assessment_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D5F27987-C968-473A-9A63-5CAD7C27F90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FFFBB6-6BEC-46FE-A39F-C7C56514214A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{56521A79-FDF7-45C8-BAA3-ABC64B3F8849}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Transactions_2024" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="228">
   <si>
     <t>Trx_ID</t>
   </si>
@@ -691,16 +707,28 @@
     <t>PROD_PRD-ELEC-002</t>
   </si>
   <si>
-    <t>Cust_ID_FIX</t>
-  </si>
-  <si>
-    <t>FIX_SKU</t>
+    <t>CLEAN_ID_FIX</t>
+  </si>
+  <si>
+    <t>CLEAN_SKU</t>
+  </si>
+  <si>
+    <t>Clean_Cust_Name</t>
+  </si>
+  <si>
+    <t>Clean_Phone_Number</t>
+  </si>
+  <si>
+    <t>Tracking_Code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.E+00"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1199,11 +1227,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1260,6 +1289,133 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Master_Customer_Profile"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>CUST-001</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v xml:space="preserve">  Ahmad  Fauzi </v>
+          </cell>
+          <cell r="C2">
+            <v>81234567890</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>CUST-002</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v xml:space="preserve">Siti Nurhaliza  </v>
+          </cell>
+          <cell r="C3">
+            <v>628189876543</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>CUST-003</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v xml:space="preserve">  budi santoso</v>
+          </cell>
+          <cell r="C4">
+            <v>6285611223344</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>CUST-004</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>DEWI LESTARI</v>
+          </cell>
+          <cell r="C5">
+            <v>87855443322</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>CUST-005</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v xml:space="preserve"> hendra wijaya  </v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>8189876543</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>CUST-006</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v xml:space="preserve">Rina  Anggraini </v>
+          </cell>
+          <cell r="C7">
+            <v>81122334455</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>CUST-007</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v xml:space="preserve"> EKO PRASETYO </v>
+          </cell>
+          <cell r="C8">
+            <v>628170099887</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>CUST-008</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Maya  Indah  Sari</v>
+          </cell>
+          <cell r="C9">
+            <v>85211447788</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>CUST-009</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v xml:space="preserve">  rizky hidayat </v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>+62 819 3322 1100</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>CUST-010</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>VALENTINA ROSI</v>
+          </cell>
+          <cell r="C11">
+            <v>81377665544</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1579,7 +1735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A4B63D-0D46-44D9-8B15-778A85DACDCF}">
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -1594,10 +1750,14 @@
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1638,10 +1798,19 @@
         <v>223</v>
       </c>
       <c r="N1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q1" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -1683,11 +1852,23 @@
         <v>CUST-002</v>
       </c>
       <c r="N2" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D2,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M2,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O2" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M2,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P2" s="1" t="str">
+        <f t="shared" ref="P2:P33" si="0">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D2,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-ELEC-001</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q2" s="1" t="str">
+        <f>_xlfn.CONCAT(G2,"-",A2,"-",P2)</f>
+        <v>SISEPAT-BEST-TRX-2024-0001-PRD-ELEC-001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1725,15 +1906,27 @@
         <v>27</v>
       </c>
       <c r="M3" s="1" t="str">
-        <f t="shared" ref="M3:M66" si="0">TRIM(C3)</f>
+        <f t="shared" ref="M3:M66" si="1">TRIM(C3)</f>
         <v>CUST-001</v>
       </c>
       <c r="N3" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D3,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M3,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Ahmad Fauzi</v>
+      </c>
+      <c r="O3" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M3,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81234567890</v>
+      </c>
+      <c r="P3" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>PRD-ELEC-002-2024</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q3" s="1" t="str">
+        <f>_xlfn.CONCAT(G3,"-",A3,"-",P3)</f>
+        <v>JNT-REG-TRX-2024-0002-PRD-ELEC-002-2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1771,15 +1964,27 @@
         <v>33</v>
       </c>
       <c r="M4" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-005</v>
+      </c>
+      <c r="N4" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M4,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O4" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M4,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-005</v>
-      </c>
-      <c r="N4" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D4,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-BEAU-001-v1</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q4" s="1" t="str">
+        <f t="shared" ref="Q4:Q67" si="2">_xlfn.CONCAT(G4,"-",A4,"-",P4)</f>
+        <v>JNT-REG-TRX-2024-0003-PRD-BEAU-001-v1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
@@ -1817,15 +2022,27 @@
         <v>39</v>
       </c>
       <c r="M5" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-002</v>
       </c>
       <c r="N5" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M5,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O5" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M5,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P5" s="1" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D5,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-FASH-002</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q5" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0004-PRD-FASH-002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
@@ -1863,15 +2080,27 @@
         <v>43</v>
       </c>
       <c r="M6" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-005</v>
+      </c>
+      <c r="N6" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M6,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O6" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M6,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-005</v>
-      </c>
-      <c r="N6" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D6,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-BEAU-002</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q6" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-YES-TRX-2024-0005-PRD-BEAU-002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
@@ -1909,15 +2138,27 @@
         <v>33</v>
       </c>
       <c r="M7" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-004</v>
+      </c>
+      <c r="N7" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M7,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O7" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M7,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-004</v>
-      </c>
-      <c r="N7" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D7,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-BEAU-002</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q7" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-REG-TRX-2024-0006-PRD-BEAU-002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>49</v>
       </c>
@@ -1955,15 +2196,27 @@
         <v>39</v>
       </c>
       <c r="M8" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-002</v>
+      </c>
+      <c r="N8" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M8,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O8" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M8,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-002</v>
-      </c>
-      <c r="N8" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D8,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-HOME-001-2024</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q8" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-YES-TRX-2024-0007-PRD-HOME-001-2024</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>51</v>
       </c>
@@ -2001,15 +2254,27 @@
         <v>39</v>
       </c>
       <c r="M9" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-006</v>
+      </c>
+      <c r="N9" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M9,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rina Anggraini</v>
+      </c>
+      <c r="O9" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M9,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81122334455</v>
+      </c>
+      <c r="P9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-006</v>
-      </c>
-      <c r="N9" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D9,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-BEAU-002-v1</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q9" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-EXP-TRX-2024-0008-PRD-BEAU-002-v1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>55</v>
       </c>
@@ -2047,15 +2312,27 @@
         <v>33</v>
       </c>
       <c r="M10" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-006</v>
+      </c>
+      <c r="N10" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M10,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rina Anggraini</v>
+      </c>
+      <c r="O10" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M10,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81122334455</v>
+      </c>
+      <c r="P10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-006</v>
-      </c>
-      <c r="N10" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D10,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-ELEC-004</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q10" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-REG-TRX-2024-0009-PRD-ELEC-004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>58</v>
       </c>
@@ -2093,15 +2370,27 @@
         <v>27</v>
       </c>
       <c r="M11" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-005</v>
+      </c>
+      <c r="N11" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M11,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O11" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M11,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-005</v>
-      </c>
-      <c r="N11" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D11,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-HOME-003</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q11" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-EXP-TRX-2024-0010-PRD-HOME-003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>60</v>
       </c>
@@ -2139,15 +2428,27 @@
         <v>39</v>
       </c>
       <c r="M12" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-002</v>
+      </c>
+      <c r="N12" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M12,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O12" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M12,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-002</v>
-      </c>
-      <c r="N12" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D12,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-ELEC-003-2024</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q12" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-BEST-TRX-2024-0011-PRD-ELEC-003-2024</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>63</v>
       </c>
@@ -2185,15 +2486,27 @@
         <v>43</v>
       </c>
       <c r="M13" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-001</v>
+      </c>
+      <c r="N13" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M13,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Ahmad Fauzi</v>
+      </c>
+      <c r="O13" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M13,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81234567890</v>
+      </c>
+      <c r="P13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-001</v>
-      </c>
-      <c r="N13" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D13,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-HOME-002-v1</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q13" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0012-PRD-HOME-002-v1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>66</v>
       </c>
@@ -2231,15 +2544,27 @@
         <v>43</v>
       </c>
       <c r="M14" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-001</v>
+      </c>
+      <c r="N14" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M14,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Ahmad Fauzi</v>
+      </c>
+      <c r="O14" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M14,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81234567890</v>
+      </c>
+      <c r="P14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-001</v>
-      </c>
-      <c r="N14" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D14,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-HOME-003</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q14" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0013-PRD-HOME-003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>68</v>
       </c>
@@ -2277,15 +2602,27 @@
         <v>19</v>
       </c>
       <c r="M15" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-004</v>
+      </c>
+      <c r="N15" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M15,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O15" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M15,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P15" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-004</v>
-      </c>
-      <c r="N15" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D15,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-ELEC-003-2024</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q15" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0014-PRD-ELEC-003-2024</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>71</v>
       </c>
@@ -2323,15 +2660,27 @@
         <v>43</v>
       </c>
       <c r="M16" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-006</v>
+      </c>
+      <c r="N16" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M16,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rina Anggraini</v>
+      </c>
+      <c r="O16" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M16,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81122334455</v>
+      </c>
+      <c r="P16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-006</v>
-      </c>
-      <c r="N16" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D16,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-BEAU-003</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q16" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0015-PRD-BEAU-003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>74</v>
       </c>
@@ -2369,15 +2718,27 @@
         <v>27</v>
       </c>
       <c r="M17" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-002</v>
+      </c>
+      <c r="N17" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M17,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O17" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M17,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-002</v>
-      </c>
-      <c r="N17" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D17,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-BEAU-001-2024</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q17" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-BEST-TRX-2024-0016-PRD-BEAU-001-2024</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>76</v>
       </c>
@@ -2415,15 +2776,27 @@
         <v>33</v>
       </c>
       <c r="M18" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-004</v>
+      </c>
+      <c r="N18" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M18,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O18" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M18,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-004</v>
-      </c>
-      <c r="N18" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D18,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-BEAU-003</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q18" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-BEST-TRX-2024-0017-PRD-BEAU-003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>77</v>
       </c>
@@ -2461,15 +2834,27 @@
         <v>19</v>
       </c>
       <c r="M19" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-004</v>
+      </c>
+      <c r="N19" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M19,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O19" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M19,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-004</v>
-      </c>
-      <c r="N19" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D19,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-ELEC-004</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q19" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-EXP-TRX-2024-0018-PRD-ELEC-004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>79</v>
       </c>
@@ -2507,15 +2892,27 @@
         <v>33</v>
       </c>
       <c r="M20" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-001</v>
+      </c>
+      <c r="N20" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M20,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Ahmad Fauzi</v>
+      </c>
+      <c r="O20" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M20,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81234567890</v>
+      </c>
+      <c r="P20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-001</v>
-      </c>
-      <c r="N20" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D20,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-ELEC-004-v1</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q20" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-REG-TRX-2024-0019-PRD-ELEC-004-v1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>81</v>
       </c>
@@ -2553,15 +2950,27 @@
         <v>43</v>
       </c>
       <c r="M21" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-010</v>
+      </c>
+      <c r="N21" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M21,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Valentina Rosi</v>
+      </c>
+      <c r="O21" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M21,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81377665544</v>
+      </c>
+      <c r="P21" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-010</v>
-      </c>
-      <c r="N21" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D21,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-HOME-001-2024</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q21" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0020-PRD-HOME-001-2024</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>83</v>
       </c>
@@ -2599,15 +3008,27 @@
         <v>39</v>
       </c>
       <c r="M22" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-007</v>
+      </c>
+      <c r="N22" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M22,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Eko Prasetyo</v>
+      </c>
+      <c r="O22" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M22,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8170099887</v>
+      </c>
+      <c r="P22" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-007</v>
-      </c>
-      <c r="N22" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D22,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-FASH-002</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q22" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-EXP-TRX-2024-0021-PRD-FASH-002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>86</v>
       </c>
@@ -2645,15 +3066,27 @@
         <v>27</v>
       </c>
       <c r="M23" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-004</v>
+      </c>
+      <c r="N23" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M23,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O23" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M23,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P23" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-004</v>
-      </c>
-      <c r="N23" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D23,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-FASH-004-2024</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q23" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0022-PRD-FASH-004-2024</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>88</v>
       </c>
@@ -2691,15 +3124,27 @@
         <v>39</v>
       </c>
       <c r="M24" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-001</v>
+      </c>
+      <c r="N24" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M24,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Ahmad Fauzi</v>
+      </c>
+      <c r="O24" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M24,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81234567890</v>
+      </c>
+      <c r="P24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-001</v>
-      </c>
-      <c r="N24" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D24,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-HOME-002-v1</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q24" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0023-PRD-HOME-002-v1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>89</v>
       </c>
@@ -2737,15 +3182,27 @@
         <v>39</v>
       </c>
       <c r="M25" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-007</v>
+      </c>
+      <c r="N25" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M25,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Eko Prasetyo</v>
+      </c>
+      <c r="O25" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M25,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8170099887</v>
+      </c>
+      <c r="P25" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-007</v>
-      </c>
-      <c r="N25" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D25,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-BEAU-003-2024</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q25" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0024-PRD-BEAU-003-2024</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>92</v>
       </c>
@@ -2783,15 +3240,27 @@
         <v>43</v>
       </c>
       <c r="M26" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-008</v>
+      </c>
+      <c r="N26" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M26,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Maya Indah Sari</v>
+      </c>
+      <c r="O26" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M26,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85211447788</v>
+      </c>
+      <c r="P26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-008</v>
-      </c>
-      <c r="N26" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D26,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-ELEC-003</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q26" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-EXP-TRX-2024-0025-PRD-ELEC-003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>95</v>
       </c>
@@ -2829,15 +3298,27 @@
         <v>27</v>
       </c>
       <c r="M27" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-008</v>
+      </c>
+      <c r="N27" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M27,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Maya Indah Sari</v>
+      </c>
+      <c r="O27" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M27,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85211447788</v>
+      </c>
+      <c r="P27" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-008</v>
-      </c>
-      <c r="N27" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D27,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-FASH-004</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q27" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-BEST-TRX-2024-0026-PRD-FASH-004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>97</v>
       </c>
@@ -2875,15 +3356,27 @@
         <v>19</v>
       </c>
       <c r="M28" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-004</v>
+      </c>
+      <c r="N28" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M28,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O28" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M28,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-004</v>
-      </c>
-      <c r="N28" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D28,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-FASH-002</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q28" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0027-PRD-FASH-002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>98</v>
       </c>
@@ -2921,15 +3414,27 @@
         <v>27</v>
       </c>
       <c r="M29" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-009</v>
+      </c>
+      <c r="N29" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M29,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rizky Hidayat</v>
+      </c>
+      <c r="O29" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M29,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81933221100</v>
+      </c>
+      <c r="P29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-009</v>
-      </c>
-      <c r="N29" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D29,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-FASH-001-2024</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q29" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0028-PRD-FASH-001-2024</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>101</v>
       </c>
@@ -2967,15 +3472,27 @@
         <v>27</v>
       </c>
       <c r="M30" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-002</v>
+      </c>
+      <c r="N30" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M30,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O30" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M30,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-002</v>
-      </c>
-      <c r="N30" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D30,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-ELEC-001</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q30" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-REG-TRX-2024-0029-PRD-ELEC-001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>102</v>
       </c>
@@ -3013,15 +3530,27 @@
         <v>19</v>
       </c>
       <c r="M31" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-004</v>
+      </c>
+      <c r="N31" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M31,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O31" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M31,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-004</v>
-      </c>
-      <c r="N31" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D31,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-FASH-001-2024</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q31" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0030-PRD-FASH-001-2024</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>103</v>
       </c>
@@ -3059,15 +3588,27 @@
         <v>33</v>
       </c>
       <c r="M32" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-002</v>
+      </c>
+      <c r="N32" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M32,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O32" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M32,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P32" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-002</v>
-      </c>
-      <c r="N32" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D32,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-BEAU-003</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q32" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-BEST-TRX-2024-0031-PRD-BEAU-003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>105</v>
       </c>
@@ -3105,15 +3646,27 @@
         <v>43</v>
       </c>
       <c r="M33" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CUST-006</v>
+      </c>
+      <c r="N33" s="1" t="str">
+        <f>TRIM(PROPER(VLOOKUP(M33,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rina Anggraini</v>
+      </c>
+      <c r="O33" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M33,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81122334455</v>
+      </c>
+      <c r="P33" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>CUST-006</v>
-      </c>
-      <c r="N33" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D33,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-ELEC-004</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q33" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0032-PRD-ELEC-004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>106</v>
       </c>
@@ -3151,15 +3704,27 @@
         <v>39</v>
       </c>
       <c r="M34" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-005</v>
       </c>
       <c r="N34" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D34,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M34,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O34" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M34,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P34" s="1" t="str">
+        <f t="shared" ref="P34:P65" si="3">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D34,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-ELEC-001</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q34" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-BEST-TRX-2024-0033-PRD-ELEC-001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>108</v>
       </c>
@@ -3197,15 +3762,27 @@
         <v>19</v>
       </c>
       <c r="M35" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-002</v>
       </c>
       <c r="N35" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D35,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M35,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O35" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M35,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P35" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-BEAU-003-2024</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q35" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0034-PRD-BEAU-003-2024</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>110</v>
       </c>
@@ -3243,15 +3820,27 @@
         <v>33</v>
       </c>
       <c r="M36" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-005</v>
       </c>
       <c r="N36" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D36,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M36,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O36" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M36,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P36" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-FASH-001-v1</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q36" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-BEST-TRX-2024-0035-PRD-FASH-001-v1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>112</v>
       </c>
@@ -3289,15 +3878,27 @@
         <v>39</v>
       </c>
       <c r="M37" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-003</v>
       </c>
       <c r="N37" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D37,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M37,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Budi Santoso</v>
+      </c>
+      <c r="O37" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M37,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85611223344</v>
+      </c>
+      <c r="P37" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-BEAU-001-2024</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q37" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-YES-TRX-2024-0036-PRD-BEAU-001-2024</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>114</v>
       </c>
@@ -3335,15 +3936,27 @@
         <v>33</v>
       </c>
       <c r="M38" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-002</v>
       </c>
       <c r="N38" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D38,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M38,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O38" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M38,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P38" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-FASH-002-v1</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q38" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-REG-TRX-2024-0037-PRD-FASH-002-v1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>116</v>
       </c>
@@ -3381,15 +3994,27 @@
         <v>19</v>
       </c>
       <c r="M39" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-004</v>
       </c>
       <c r="N39" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D39,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M39,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O39" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M39,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P39" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-FASH-002</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q39" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0038-PRD-FASH-002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>118</v>
       </c>
@@ -3427,15 +4052,27 @@
         <v>19</v>
       </c>
       <c r="M40" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-001</v>
       </c>
       <c r="N40" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D40,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M40,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Ahmad Fauzi</v>
+      </c>
+      <c r="O40" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M40,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81234567890</v>
+      </c>
+      <c r="P40" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-ELEC-002-2024</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q40" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-YES-TRX-2024-0039-PRD-ELEC-002-2024</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>121</v>
       </c>
@@ -3473,15 +4110,27 @@
         <v>39</v>
       </c>
       <c r="M41" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-010</v>
       </c>
       <c r="N41" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D41,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M41,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Valentina Rosi</v>
+      </c>
+      <c r="O41" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M41,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81377665544</v>
+      </c>
+      <c r="P41" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-FASH-004</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q41" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-BEST-TRX-2024-0040-PRD-FASH-004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>123</v>
       </c>
@@ -3519,15 +4168,27 @@
         <v>33</v>
       </c>
       <c r="M42" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-004</v>
       </c>
       <c r="N42" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D42,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M42,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O42" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M42,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P42" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-FASH-001-v1</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q42" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0041-PRD-FASH-001-v1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>124</v>
       </c>
@@ -3565,15 +4226,27 @@
         <v>27</v>
       </c>
       <c r="M43" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-007</v>
       </c>
       <c r="N43" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D43,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M43,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Eko Prasetyo</v>
+      </c>
+      <c r="O43" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M43,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8170099887</v>
+      </c>
+      <c r="P43" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-HOME-003</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q43" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0042-PRD-HOME-003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>126</v>
       </c>
@@ -3611,15 +4284,27 @@
         <v>33</v>
       </c>
       <c r="M44" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-001</v>
       </c>
       <c r="N44" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D44,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M44,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Ahmad Fauzi</v>
+      </c>
+      <c r="O44" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M44,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81234567890</v>
+      </c>
+      <c r="P44" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-ELEC-005-2024</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q44" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0043-PRD-ELEC-005-2024</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>128</v>
       </c>
@@ -3657,15 +4342,27 @@
         <v>19</v>
       </c>
       <c r="M45" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-004</v>
       </c>
       <c r="N45" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D45,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M45,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O45" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M45,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P45" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-FASH-004</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q45" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-EXP-TRX-2024-0044-PRD-FASH-004</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>130</v>
       </c>
@@ -3703,15 +4400,27 @@
         <v>39</v>
       </c>
       <c r="M46" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-005</v>
       </c>
       <c r="N46" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D46,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M46,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O46" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M46,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P46" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-ELEC-004-2024</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q46" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0045-PRD-ELEC-004-2024</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>132</v>
       </c>
@@ -3749,15 +4458,27 @@
         <v>27</v>
       </c>
       <c r="M47" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-010</v>
       </c>
       <c r="N47" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D47,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M47,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Valentina Rosi</v>
+      </c>
+      <c r="O47" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M47,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81377665544</v>
+      </c>
+      <c r="P47" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-ELEC-004</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q47" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-EXP-TRX-2024-0046-PRD-ELEC-004</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>134</v>
       </c>
@@ -3795,15 +4516,27 @@
         <v>43</v>
       </c>
       <c r="M48" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-003</v>
       </c>
       <c r="N48" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D48,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M48,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Budi Santoso</v>
+      </c>
+      <c r="O48" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M48,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85611223344</v>
+      </c>
+      <c r="P48" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-BEAU-001</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q48" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-REG-TRX-2024-0047-PRD-BEAU-001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>137</v>
       </c>
@@ -3841,15 +4574,27 @@
         <v>19</v>
       </c>
       <c r="M49" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-009</v>
       </c>
       <c r="N49" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D49,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M49,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rizky Hidayat</v>
+      </c>
+      <c r="O49" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M49,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81933221100</v>
+      </c>
+      <c r="P49" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-FASH-004</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q49" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-REG-TRX-2024-0048-PRD-FASH-004</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>138</v>
       </c>
@@ -3887,15 +4632,27 @@
         <v>27</v>
       </c>
       <c r="M50" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-005</v>
       </c>
       <c r="N50" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D50,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M50,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O50" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M50,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P50" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-BEAU-001</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q50" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0049-PRD-BEAU-001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>140</v>
       </c>
@@ -3933,15 +4690,27 @@
         <v>27</v>
       </c>
       <c r="M51" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-005</v>
       </c>
       <c r="N51" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D51,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M51,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O51" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M51,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P51" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-ELEC-004</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q51" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0050-PRD-ELEC-004</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>142</v>
       </c>
@@ -3979,15 +4748,27 @@
         <v>43</v>
       </c>
       <c r="M52" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-004</v>
       </c>
       <c r="N52" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D52,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M52,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O52" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M52,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P52" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-ELEC-002</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q52" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0051-PRD-ELEC-002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>144</v>
       </c>
@@ -4025,15 +4806,27 @@
         <v>33</v>
       </c>
       <c r="M53" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-010</v>
       </c>
       <c r="N53" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D53,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M53,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Valentina Rosi</v>
+      </c>
+      <c r="O53" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M53,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81377665544</v>
+      </c>
+      <c r="P53" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-HOME-003</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q53" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0052-PRD-HOME-003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>146</v>
       </c>
@@ -4071,15 +4864,27 @@
         <v>39</v>
       </c>
       <c r="M54" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-009</v>
       </c>
       <c r="N54" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D54,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M54,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rizky Hidayat</v>
+      </c>
+      <c r="O54" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M54,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81933221100</v>
+      </c>
+      <c r="P54" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-BEAU-001-2024</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q54" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0053-PRD-BEAU-001-2024</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>148</v>
       </c>
@@ -4117,15 +4922,27 @@
         <v>39</v>
       </c>
       <c r="M55" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-007</v>
       </c>
       <c r="N55" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D55,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M55,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Eko Prasetyo</v>
+      </c>
+      <c r="O55" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M55,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8170099887</v>
+      </c>
+      <c r="P55" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-HOME-003</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q55" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-EXP-TRX-2024-0054-PRD-HOME-003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>150</v>
       </c>
@@ -4163,15 +4980,27 @@
         <v>33</v>
       </c>
       <c r="M56" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-008</v>
       </c>
       <c r="N56" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D56,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M56,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Maya Indah Sari</v>
+      </c>
+      <c r="O56" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M56,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85211447788</v>
+      </c>
+      <c r="P56" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-ELEC-003</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q56" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0055-PRD-ELEC-003</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>152</v>
       </c>
@@ -4209,15 +5038,27 @@
         <v>33</v>
       </c>
       <c r="M57" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-007</v>
       </c>
       <c r="N57" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D57,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M57,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Eko Prasetyo</v>
+      </c>
+      <c r="O57" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M57,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8170099887</v>
+      </c>
+      <c r="P57" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-ELEC-005-v1</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q57" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0056-PRD-ELEC-005-v1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>154</v>
       </c>
@@ -4255,15 +5096,27 @@
         <v>27</v>
       </c>
       <c r="M58" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-001</v>
       </c>
       <c r="N58" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D58,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M58,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Ahmad Fauzi</v>
+      </c>
+      <c r="O58" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M58,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81234567890</v>
+      </c>
+      <c r="P58" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-BEAU-001-2024</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q58" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-REG-TRX-2024-0057-PRD-BEAU-001-2024</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>156</v>
       </c>
@@ -4301,15 +5154,27 @@
         <v>19</v>
       </c>
       <c r="M59" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-002</v>
       </c>
       <c r="N59" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D59,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M59,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O59" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M59,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P59" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-HOME-001</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q59" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-REG-TRX-2024-0058-PRD-HOME-001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>158</v>
       </c>
@@ -4347,15 +5212,27 @@
         <v>19</v>
       </c>
       <c r="M60" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-010</v>
       </c>
       <c r="N60" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D60,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M60,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Valentina Rosi</v>
+      </c>
+      <c r="O60" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M60,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81377665544</v>
+      </c>
+      <c r="P60" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-ELEC-001</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q60" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-EXP-TRX-2024-0059-PRD-ELEC-001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>160</v>
       </c>
@@ -4393,15 +5270,27 @@
         <v>33</v>
       </c>
       <c r="M61" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-010</v>
       </c>
       <c r="N61" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D61,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M61,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Valentina Rosi</v>
+      </c>
+      <c r="O61" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M61,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81377665544</v>
+      </c>
+      <c r="P61" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-BEAU-001</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q61" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-BEST-TRX-2024-0060-PRD-BEAU-001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>162</v>
       </c>
@@ -4439,15 +5328,27 @@
         <v>39</v>
       </c>
       <c r="M62" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-007</v>
       </c>
       <c r="N62" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D62,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M62,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Eko Prasetyo</v>
+      </c>
+      <c r="O62" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M62,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8170099887</v>
+      </c>
+      <c r="P62" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-BEAU-002-v1</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q62" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0061-PRD-BEAU-002-v1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>163</v>
       </c>
@@ -4485,15 +5386,27 @@
         <v>33</v>
       </c>
       <c r="M63" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-005</v>
       </c>
       <c r="N63" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D63,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M63,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O63" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M63,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P63" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-HOME-001</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q63" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-REG-TRX-2024-0062-PRD-HOME-001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>165</v>
       </c>
@@ -4531,15 +5444,27 @@
         <v>43</v>
       </c>
       <c r="M64" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-008</v>
       </c>
       <c r="N64" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D64,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M64,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Maya Indah Sari</v>
+      </c>
+      <c r="O64" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M64,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85211447788</v>
+      </c>
+      <c r="P64" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-ELEC-004</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q64" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-YES-TRX-2024-0063-PRD-ELEC-004</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>166</v>
       </c>
@@ -4577,15 +5502,27 @@
         <v>19</v>
       </c>
       <c r="M65" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-004</v>
       </c>
       <c r="N65" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D65,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M65,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O65" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M65,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P65" s="1" t="str">
+        <f t="shared" si="3"/>
         <v>PRD-FASH-001</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q65" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>SISEPAT-BEST-TRX-2024-0064-PRD-FASH-001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>168</v>
       </c>
@@ -4623,15 +5560,27 @@
         <v>39</v>
       </c>
       <c r="M66" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CUST-004</v>
       </c>
       <c r="N66" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D66,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M66,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O66" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M66,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P66" s="1" t="str">
+        <f t="shared" ref="P66:P101" si="4">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D66,"NEW-",""),"OLD_",""),"PROD_","")</f>
         <v>PRD-HOME-003</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q66" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNT-EXP-TRX-2024-0065-PRD-HOME-003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>169</v>
       </c>
@@ -4669,15 +5618,27 @@
         <v>39</v>
       </c>
       <c r="M67" s="1" t="str">
-        <f t="shared" ref="M67:M101" si="1">TRIM(C67)</f>
+        <f t="shared" ref="M67:M101" si="5">TRIM(C67)</f>
         <v>CUST-004</v>
       </c>
       <c r="N67" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D67,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M67,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O67" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M67,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P67" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-FASH-002-2024</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q67" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>JNE-REG-TRX-2024-0066-PRD-FASH-002-2024</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>171</v>
       </c>
@@ -4715,15 +5676,27 @@
         <v>27</v>
       </c>
       <c r="M68" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-006</v>
       </c>
       <c r="N68" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D68,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M68,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rina Anggraini</v>
+      </c>
+      <c r="O68" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M68,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81122334455</v>
+      </c>
+      <c r="P68" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-HOME-003</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q68" s="1" t="str">
+        <f t="shared" ref="Q68:Q101" si="6">_xlfn.CONCAT(G68,"-",A68,"-",P68)</f>
+        <v>JNT-EXP-TRX-2024-0067-PRD-HOME-003</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>172</v>
       </c>
@@ -4761,15 +5734,27 @@
         <v>19</v>
       </c>
       <c r="M69" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-003</v>
       </c>
       <c r="N69" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D69,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M69,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Budi Santoso</v>
+      </c>
+      <c r="O69" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M69,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85611223344</v>
+      </c>
+      <c r="P69" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-004</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q69" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-EXP-TRX-2024-0068-PRD-ELEC-004</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>174</v>
       </c>
@@ -4807,15 +5792,27 @@
         <v>33</v>
       </c>
       <c r="M70" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-004</v>
       </c>
       <c r="N70" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D70,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M70,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O70" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M70,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P70" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-FASH-001</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q70" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-EXP-TRX-2024-0069-PRD-FASH-001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>176</v>
       </c>
@@ -4853,15 +5850,27 @@
         <v>33</v>
       </c>
       <c r="M71" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-003</v>
       </c>
       <c r="N71" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D71,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M71,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Budi Santoso</v>
+      </c>
+      <c r="O71" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M71,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85611223344</v>
+      </c>
+      <c r="P71" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-HOME-002</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q71" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNE-REG-TRX-2024-0070-PRD-HOME-002</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>178</v>
       </c>
@@ -4899,15 +5908,27 @@
         <v>39</v>
       </c>
       <c r="M72" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-003</v>
       </c>
       <c r="N72" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D72,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M72,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Budi Santoso</v>
+      </c>
+      <c r="O72" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M72,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85611223344</v>
+      </c>
+      <c r="P72" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-001</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q72" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>SISEPAT-BEST-TRX-2024-0071-PRD-ELEC-001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>179</v>
       </c>
@@ -4945,15 +5966,27 @@
         <v>39</v>
       </c>
       <c r="M73" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-003</v>
       </c>
       <c r="N73" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D73,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M73,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Budi Santoso</v>
+      </c>
+      <c r="O73" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M73,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85611223344</v>
+      </c>
+      <c r="P73" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-BEAU-001</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q73" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>SISEPAT-BEST-TRX-2024-0072-PRD-BEAU-001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>180</v>
       </c>
@@ -4991,15 +6024,27 @@
         <v>43</v>
       </c>
       <c r="M74" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-008</v>
       </c>
       <c r="N74" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D74,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M74,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Maya Indah Sari</v>
+      </c>
+      <c r="O74" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M74,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85211447788</v>
+      </c>
+      <c r="P74" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-005</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q74" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-REG-TRX-2024-0073-PRD-ELEC-005</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>182</v>
       </c>
@@ -5037,15 +6082,27 @@
         <v>39</v>
       </c>
       <c r="M75" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-002</v>
       </c>
       <c r="N75" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D75,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M75,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O75" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M75,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P75" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-003-2024</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q75" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0074-PRD-ELEC-003-2024</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>184</v>
       </c>
@@ -5083,15 +6140,27 @@
         <v>27</v>
       </c>
       <c r="M76" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-005</v>
       </c>
       <c r="N76" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D76,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M76,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O76" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M76,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P76" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-001</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q76" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0075-PRD-ELEC-001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>186</v>
       </c>
@@ -5129,15 +6198,27 @@
         <v>27</v>
       </c>
       <c r="M77" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-004</v>
       </c>
       <c r="N77" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D77,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M77,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O77" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M77,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P77" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-FASH-002</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q77" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-EXP-TRX-2024-0076-PRD-FASH-002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>187</v>
       </c>
@@ -5175,15 +6256,27 @@
         <v>33</v>
       </c>
       <c r="M78" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-005</v>
       </c>
       <c r="N78" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D78,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M78,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O78" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M78,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P78" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-HOME-001</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q78" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNE-YES-TRX-2024-0077-PRD-HOME-001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>188</v>
       </c>
@@ -5221,15 +6314,27 @@
         <v>33</v>
       </c>
       <c r="M79" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-008</v>
       </c>
       <c r="N79" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D79,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M79,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Maya Indah Sari</v>
+      </c>
+      <c r="O79" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M79,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85211447788</v>
+      </c>
+      <c r="P79" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-FASH-003</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q79" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-EXP-TRX-2024-0078-PRD-FASH-003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>190</v>
       </c>
@@ -5267,15 +6372,27 @@
         <v>39</v>
       </c>
       <c r="M80" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-010</v>
       </c>
       <c r="N80" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D80,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M80,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Valentina Rosi</v>
+      </c>
+      <c r="O80" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M80,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81377665544</v>
+      </c>
+      <c r="P80" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-HOME-001</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q80" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNE-YES-TRX-2024-0079-PRD-HOME-001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>192</v>
       </c>
@@ -5313,15 +6430,27 @@
         <v>33</v>
       </c>
       <c r="M81" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-007</v>
       </c>
       <c r="N81" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D81,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M81,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Eko Prasetyo</v>
+      </c>
+      <c r="O81" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M81,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8170099887</v>
+      </c>
+      <c r="P81" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-HOME-002</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q81" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0080-PRD-HOME-002</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>193</v>
       </c>
@@ -5359,15 +6488,27 @@
         <v>43</v>
       </c>
       <c r="M82" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-003</v>
       </c>
       <c r="N82" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D82,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M82,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Budi Santoso</v>
+      </c>
+      <c r="O82" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M82,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85611223344</v>
+      </c>
+      <c r="P82" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-FASH-001</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q82" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-EXP-TRX-2024-0081-PRD-FASH-001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>194</v>
       </c>
@@ -5405,15 +6546,27 @@
         <v>39</v>
       </c>
       <c r="M83" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-006</v>
       </c>
       <c r="N83" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D83,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M83,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rina Anggraini</v>
+      </c>
+      <c r="O83" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M83,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81122334455</v>
+      </c>
+      <c r="P83" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-002</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q83" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-EXP-TRX-2024-0082-PRD-ELEC-002</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>195</v>
       </c>
@@ -5451,15 +6604,27 @@
         <v>33</v>
       </c>
       <c r="M84" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-006</v>
       </c>
       <c r="N84" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D84,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M84,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rina Anggraini</v>
+      </c>
+      <c r="O84" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M84,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81122334455</v>
+      </c>
+      <c r="P84" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-HOME-001</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q84" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNE-YES-TRX-2024-0083-PRD-HOME-001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>196</v>
       </c>
@@ -5497,15 +6662,27 @@
         <v>33</v>
       </c>
       <c r="M85" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-008</v>
       </c>
       <c r="N85" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D85,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M85,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Maya Indah Sari</v>
+      </c>
+      <c r="O85" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M85,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85211447788</v>
+      </c>
+      <c r="P85" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-002</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q85" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>SISEPAT-BEST-TRX-2024-0084-PRD-ELEC-002</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>199</v>
       </c>
@@ -5543,15 +6720,27 @@
         <v>33</v>
       </c>
       <c r="M86" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-004</v>
       </c>
       <c r="N86" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D86,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M86,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O86" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M86,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P86" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-BEAU-002</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q86" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNE-REG-TRX-2024-0085-PRD-BEAU-002</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>200</v>
       </c>
@@ -5589,15 +6778,27 @@
         <v>27</v>
       </c>
       <c r="M87" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-004</v>
       </c>
       <c r="N87" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D87,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M87,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Dewi Lestari</v>
+      </c>
+      <c r="O87" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M87,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>87855443322</v>
+      </c>
+      <c r="P87" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-FASH-003-2024</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q87" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNE-YES-TRX-2024-0086-PRD-FASH-003-2024</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>202</v>
       </c>
@@ -5635,15 +6836,27 @@
         <v>19</v>
       </c>
       <c r="M88" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-009</v>
       </c>
       <c r="N88" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D88,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M88,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rizky Hidayat</v>
+      </c>
+      <c r="O88" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M88,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81933221100</v>
+      </c>
+      <c r="P88" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-005-v1</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q88" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-REG-TRX-2024-0087-PRD-ELEC-005-v1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>203</v>
       </c>
@@ -5681,15 +6894,27 @@
         <v>27</v>
       </c>
       <c r="M89" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-008</v>
       </c>
       <c r="N89" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D89,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M89,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Maya Indah Sari</v>
+      </c>
+      <c r="O89" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M89,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85211447788</v>
+      </c>
+      <c r="P89" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-FASH-001</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q89" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>SISEPAT-BEST-TRX-2024-0088-PRD-FASH-001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>205</v>
       </c>
@@ -5727,15 +6952,27 @@
         <v>27</v>
       </c>
       <c r="M90" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-007</v>
       </c>
       <c r="N90" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D90,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M90,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Eko Prasetyo</v>
+      </c>
+      <c r="O90" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M90,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8170099887</v>
+      </c>
+      <c r="P90" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-001</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q90" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-EXP-TRX-2024-0089-PRD-ELEC-001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>206</v>
       </c>
@@ -5773,15 +7010,27 @@
         <v>43</v>
       </c>
       <c r="M91" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-010</v>
       </c>
       <c r="N91" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D91,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M91,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Valentina Rosi</v>
+      </c>
+      <c r="O91" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M91,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81377665544</v>
+      </c>
+      <c r="P91" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-FASH-001-v1</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q91" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNE-REG-TRX-2024-0090-PRD-FASH-001-v1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>207</v>
       </c>
@@ -5819,15 +7068,27 @@
         <v>33</v>
       </c>
       <c r="M92" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-008</v>
       </c>
       <c r="N92" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D92,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M92,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Maya Indah Sari</v>
+      </c>
+      <c r="O92" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M92,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85211447788</v>
+      </c>
+      <c r="P92" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-BEAU-001</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q92" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNE-YES-TRX-2024-0091-PRD-BEAU-001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>209</v>
       </c>
@@ -5865,15 +7126,27 @@
         <v>43</v>
       </c>
       <c r="M93" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-009</v>
       </c>
       <c r="N93" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D93,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M93,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rizky Hidayat</v>
+      </c>
+      <c r="O93" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M93,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81933221100</v>
+      </c>
+      <c r="P93" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-001-v1</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q93" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-EXP-TRX-2024-0092-PRD-ELEC-001-v1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>211</v>
       </c>
@@ -5911,15 +7184,27 @@
         <v>33</v>
       </c>
       <c r="M94" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-003</v>
       </c>
       <c r="N94" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D94,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M94,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Budi Santoso</v>
+      </c>
+      <c r="O94" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M94,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85611223344</v>
+      </c>
+      <c r="P94" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-HOME-003-v1</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q94" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNE-REG-TRX-2024-0093-PRD-HOME-003-v1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>213</v>
       </c>
@@ -5957,15 +7242,27 @@
         <v>19</v>
       </c>
       <c r="M95" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-009</v>
       </c>
       <c r="N95" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D95,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M95,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Rizky Hidayat</v>
+      </c>
+      <c r="O95" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M95,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81933221100</v>
+      </c>
+      <c r="P95" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-FASH-002</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q95" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>SISEPAT-BEST-TRX-2024-0094-PRD-FASH-002</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>214</v>
       </c>
@@ -6003,15 +7300,27 @@
         <v>39</v>
       </c>
       <c r="M96" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-010</v>
       </c>
       <c r="N96" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D96,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M96,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Valentina Rosi</v>
+      </c>
+      <c r="O96" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M96,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81377665544</v>
+      </c>
+      <c r="P96" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-003</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q96" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0095-PRD-ELEC-003</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>215</v>
       </c>
@@ -6049,15 +7358,27 @@
         <v>39</v>
       </c>
       <c r="M97" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-002</v>
       </c>
       <c r="N97" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D97,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M97,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Siti Nurhaliza</v>
+      </c>
+      <c r="O97" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M97,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P97" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-FASH-003</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q97" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-REG-TRX-2024-0096-PRD-FASH-003</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>217</v>
       </c>
@@ -6095,15 +7416,27 @@
         <v>33</v>
       </c>
       <c r="M98" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-008</v>
       </c>
       <c r="N98" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D98,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M98,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Maya Indah Sari</v>
+      </c>
+      <c r="O98" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M98,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85211447788</v>
+      </c>
+      <c r="P98" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-002</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q98" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0097-PRD-ELEC-002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>219</v>
       </c>
@@ -6141,15 +7474,27 @@
         <v>27</v>
       </c>
       <c r="M99" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-001</v>
       </c>
       <c r="N99" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D99,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M99,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Ahmad Fauzi</v>
+      </c>
+      <c r="O99" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M99,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>81234567890</v>
+      </c>
+      <c r="P99" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-HOME-001</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q99" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-REG-TRX-2024-0098-PRD-HOME-001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>220</v>
       </c>
@@ -6187,15 +7532,27 @@
         <v>33</v>
       </c>
       <c r="M100" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-005</v>
       </c>
       <c r="N100" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D100,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M100,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Hendra Wijaya</v>
+      </c>
+      <c r="O100" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M100,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>8189876543</v>
+      </c>
+      <c r="P100" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-HOME-002</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q100" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>JNT-EXP-TRX-2024-0099-PRD-HOME-002</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>221</v>
       </c>
@@ -6233,15 +7590,28 @@
         <v>19</v>
       </c>
       <c r="M101" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CUST-003</v>
       </c>
       <c r="N101" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D101,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>TRIM(PROPER(VLOOKUP(M101,[1]Master_Customer_Profile!$A$2:$B$11,2,0)))</f>
+        <v>Budi Santoso</v>
+      </c>
+      <c r="O101" s="4" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(VLOOKUP(M101,[1]Master_Customer_Profile!$A$2:$C$11,3,0)),"+",""),"62","")," ","")</f>
+        <v>85611223344</v>
+      </c>
+      <c r="P101" s="1" t="str">
+        <f t="shared" si="4"/>
         <v>PRD-ELEC-002</v>
+      </c>
+      <c r="Q101" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>SISEPAT-BEST-TRX-2024-0100-PRD-ELEC-002</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Exam/Excel/advanced_assessment_project/Raw_Transactions_2024_finish.xlsx
+++ b/Exam/Excel/advanced_assessment_project/Raw_Transactions_2024_finish.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\Project\Data-Analyst\Exam\Excel\advanced_assessment_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FFFBB6-6BEC-46FE-A39F-C7C56514214A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDCA227-7C3A-4975-B1E0-40A6CF023DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{56521A79-FDF7-45C8-BAA3-ABC64B3F8849}"/>
   </bookViews>
@@ -17,6 +17,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="234">
   <si>
     <t>Trx_ID</t>
   </si>
@@ -720,14 +721,33 @@
   </si>
   <si>
     <t>Tracking_Code</t>
+  </si>
+  <si>
+    <t>Product_Name</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Sub_Category</t>
+  </si>
+  <si>
+    <t>Unit_Price</t>
+  </si>
+  <si>
+    <t>Unit_COGS</t>
+  </si>
+  <si>
+    <t>Weight_KG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.E+00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.E+00"/>
+    <numFmt numFmtId="165" formatCode="&quot;Rp&quot;#,##0"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1227,12 +1247,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1410,6 +1432,368 @@
           </cell>
           <cell r="C11">
             <v>81377665544</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Master_Product_Catalog"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>PRD-ELEC-001</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>Wireless Noise Cancelling Headphones</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>Electronics</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>Audio</v>
+          </cell>
+          <cell r="E2">
+            <v>1250000</v>
+          </cell>
+          <cell r="F2">
+            <v>850000</v>
+          </cell>
+          <cell r="G2" t="str">
+            <v>0.8</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>PRD-ELEC-002</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>Smart Watch Fitness Tracker V2</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>Electronics</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>Wearables</v>
+          </cell>
+          <cell r="E3">
+            <v>850000</v>
+          </cell>
+          <cell r="F3">
+            <v>520000</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>0.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>PRD-ELEC-003</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>Mechanical Gaming Keyboard RGB</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>Electronics</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>Computer Accessories</v>
+          </cell>
+          <cell r="E4">
+            <v>950000</v>
+          </cell>
+          <cell r="F4">
+            <v>600000</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>1.2</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>PRD-ELEC-004</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>Ergonomic Wireless Mouse</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>Electronics</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Computer Accessories</v>
+          </cell>
+          <cell r="E5">
+            <v>350000</v>
+          </cell>
+          <cell r="F5">
+            <v>200000</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>0.25</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>PRD-ELEC-005</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>Ultra HD Webcam 4K Pro</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>Electronics</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>Computer Accessories</v>
+          </cell>
+          <cell r="E6">
+            <v>1100000</v>
+          </cell>
+          <cell r="F6">
+            <v>720000</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>PRD-FASH-001</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>Men Denim Jacket Vintage Blue</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>Fashion</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>Outerwear</v>
+          </cell>
+          <cell r="E7">
+            <v>450000</v>
+          </cell>
+          <cell r="F7">
+            <v>260000</v>
+          </cell>
+          <cell r="G7" t="str">
+            <v>0.9</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>PRD-FASH-002</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Women Floral Summer Dress</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>Fashion</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>Dresses</v>
+          </cell>
+          <cell r="E8">
+            <v>320000</v>
+          </cell>
+          <cell r="F8">
+            <v>180000</v>
+          </cell>
+          <cell r="G8" t="str">
+            <v>0.35</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>PRD-FASH-003</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Unisex Canvas Sneakers White</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>Fashion</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>Footwear</v>
+          </cell>
+          <cell r="E9">
+            <v>520000</v>
+          </cell>
+          <cell r="F9">
+            <v>310000</v>
+          </cell>
+          <cell r="G9" t="str">
+            <v>1.1</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>PRD-FASH-004</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>Leather Minimalist Wallet</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>Fashion</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>Accessories</v>
+          </cell>
+          <cell r="E10">
+            <v>220000</v>
+          </cell>
+          <cell r="F10">
+            <v>110000</v>
+          </cell>
+          <cell r="G10" t="str">
+            <v>0.15</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>PRD-HOME-001</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>Automatic Coffee Espresso Machine</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>Home &amp; Living</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>Kitchen Appliances</v>
+          </cell>
+          <cell r="E11">
+            <v>2400000</v>
+          </cell>
+          <cell r="F11">
+            <v>1650000</v>
+          </cell>
+          <cell r="G11" t="str">
+            <v>4.5</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>PRD-HOME-002</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>Air Purifier HEPA Filter H13</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>Home &amp; Living</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v>Home Appliances</v>
+          </cell>
+          <cell r="E12">
+            <v>1750000</v>
+          </cell>
+          <cell r="F12">
+            <v>1150000</v>
+          </cell>
+          <cell r="G12" t="str">
+            <v>3.2</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>PRD-HOME-003</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>Stainless Steel Cookware Set 5pcs</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>Home &amp; Living</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>Kitchenware</v>
+          </cell>
+          <cell r="E13">
+            <v>880000</v>
+          </cell>
+          <cell r="F13">
+            <v>540000</v>
+          </cell>
+          <cell r="G13" t="str">
+            <v>3.8</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>PRD-BEAU-001</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>Hydrating Serum Vitamin C 50ml</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>Beauty &amp; Health</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v>Skincare</v>
+          </cell>
+          <cell r="E14">
+            <v>185000</v>
+          </cell>
+          <cell r="F14">
+            <v>85000</v>
+          </cell>
+          <cell r="G14" t="str">
+            <v>0.1</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>PRD-BEAU-002</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>Organic Sunscreen SPF 50 PA++++</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>Beauty &amp; Health</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v>Skincare</v>
+          </cell>
+          <cell r="E15">
+            <v>145000</v>
+          </cell>
+          <cell r="F15">
+            <v>65000</v>
+          </cell>
+          <cell r="G15" t="str">
+            <v>0.12</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>PRD-BEAU-003</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>Sonic Electric Toothbrush Pro</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>Beauty &amp; Health</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v>Personal Care</v>
+          </cell>
+          <cell r="E16">
+            <v>490000</v>
+          </cell>
+          <cell r="F16">
+            <v>290000</v>
+          </cell>
+          <cell r="G16" t="str">
+            <v>0.4</v>
           </cell>
         </row>
       </sheetData>
@@ -1735,7 +2119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A4B63D-0D46-44D9-8B15-778A85DACDCF}">
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:W101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -1753,11 +2137,16 @@
     <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1809,8 +2198,26 @@
       <c r="Q1" s="3" t="s">
         <v>227</v>
       </c>
+      <c r="R1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>233</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -1860,15 +2267,39 @@
         <v>8189876543</v>
       </c>
       <c r="P2" s="1" t="str">
-        <f t="shared" ref="P2:P33" si="0">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D2,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D2,"NEW-",""),"OLD_",""),"PROD_",""),"-2024",""),"-v1","")</f>
         <v>PRD-ELEC-001</v>
       </c>
       <c r="Q2" s="1" t="str">
         <f>_xlfn.CONCAT(G2,"-",A2,"-",P2)</f>
         <v>SISEPAT-BEST-TRX-2024-0001-PRD-ELEC-001</v>
       </c>
+      <c r="R2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P2,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Wireless Noise Cancelling Headphones</v>
+      </c>
+      <c r="S2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P2,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P2,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Audio</v>
+      </c>
+      <c r="U2" s="5">
+        <f>_xlfn.XLOOKUP(P2,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1250000</v>
+      </c>
+      <c r="V2" s="6">
+        <f>_xlfn.XLOOKUP(P2,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="W2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P2,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1906,7 +2337,7 @@
         <v>27</v>
       </c>
       <c r="M3" s="1" t="str">
-        <f t="shared" ref="M3:M66" si="1">TRIM(C3)</f>
+        <f t="shared" ref="M3:M66" si="0">TRIM(C3)</f>
         <v>CUST-001</v>
       </c>
       <c r="N3" s="1" t="str">
@@ -1918,15 +2349,39 @@
         <v>81234567890</v>
       </c>
       <c r="P3" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-ELEC-002-2024</v>
+        <f t="shared" ref="P3:P66" si="1">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D3,"NEW-",""),"OLD_",""),"PROD_",""),"-2024",""),"-v1","")</f>
+        <v>PRD-ELEC-002</v>
       </c>
       <c r="Q3" s="1" t="str">
         <f>_xlfn.CONCAT(G3,"-",A3,"-",P3)</f>
-        <v>JNT-REG-TRX-2024-0002-PRD-ELEC-002-2024</v>
+        <v>JNT-REG-TRX-2024-0002-PRD-ELEC-002</v>
+      </c>
+      <c r="R3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P3,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Smart Watch Fitness Tracker V2</v>
+      </c>
+      <c r="S3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P3,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P3,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Wearables</v>
+      </c>
+      <c r="U3" s="5">
+        <f>_xlfn.XLOOKUP(P3,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="V3" s="6">
+        <f>_xlfn.XLOOKUP(P3,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>520000</v>
+      </c>
+      <c r="W3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P3,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1964,7 +2419,7 @@
         <v>33</v>
       </c>
       <c r="M4" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-005</v>
       </c>
       <c r="N4" s="1" t="str">
@@ -1976,15 +2431,39 @@
         <v>8189876543</v>
       </c>
       <c r="P4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-BEAU-001-v1</v>
+        <f t="shared" si="1"/>
+        <v>PRD-BEAU-001</v>
       </c>
       <c r="Q4" s="1" t="str">
         <f t="shared" ref="Q4:Q67" si="2">_xlfn.CONCAT(G4,"-",A4,"-",P4)</f>
-        <v>JNT-REG-TRX-2024-0003-PRD-BEAU-001-v1</v>
+        <v>JNT-REG-TRX-2024-0003-PRD-BEAU-001</v>
+      </c>
+      <c r="R4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P4,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Hydrating Serum Vitamin C 50ml</v>
+      </c>
+      <c r="S4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P4,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P4,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U4" s="5">
+        <f>_xlfn.XLOOKUP(P4,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>185000</v>
+      </c>
+      <c r="V4" s="6">
+        <f>_xlfn.XLOOKUP(P4,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>85000</v>
+      </c>
+      <c r="W4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P4,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
@@ -2022,7 +2501,7 @@
         <v>39</v>
       </c>
       <c r="M5" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-002</v>
       </c>
       <c r="N5" s="1" t="str">
@@ -2034,15 +2513,39 @@
         <v>8189876543</v>
       </c>
       <c r="P5" s="1" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D5,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f t="shared" si="1"/>
         <v>PRD-FASH-002</v>
       </c>
       <c r="Q5" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNE-REG-TRX-2024-0004-PRD-FASH-002</v>
       </c>
+      <c r="R5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P5,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Women Floral Summer Dress</v>
+      </c>
+      <c r="S5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P5,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P5,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Dresses</v>
+      </c>
+      <c r="U5" s="5">
+        <f>_xlfn.XLOOKUP(P5,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>320000</v>
+      </c>
+      <c r="V5" s="6">
+        <f>_xlfn.XLOOKUP(P5,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>180000</v>
+      </c>
+      <c r="W5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P5,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.35</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
@@ -2080,7 +2583,7 @@
         <v>43</v>
       </c>
       <c r="M6" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-005</v>
       </c>
       <c r="N6" s="1" t="str">
@@ -2092,15 +2595,39 @@
         <v>8189876543</v>
       </c>
       <c r="P6" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-BEAU-002</v>
       </c>
       <c r="Q6" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNE-YES-TRX-2024-0005-PRD-BEAU-002</v>
       </c>
+      <c r="R6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P6,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Organic Sunscreen SPF 50 PA++++</v>
+      </c>
+      <c r="S6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P6,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P6,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U6" s="5">
+        <f>_xlfn.XLOOKUP(P6,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>145000</v>
+      </c>
+      <c r="V6" s="6">
+        <f>_xlfn.XLOOKUP(P6,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>65000</v>
+      </c>
+      <c r="W6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P6,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.12</v>
+      </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
@@ -2138,7 +2665,7 @@
         <v>33</v>
       </c>
       <c r="M7" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N7" s="1" t="str">
@@ -2150,15 +2677,39 @@
         <v>87855443322</v>
       </c>
       <c r="P7" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-BEAU-002</v>
       </c>
       <c r="Q7" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-REG-TRX-2024-0006-PRD-BEAU-002</v>
       </c>
+      <c r="R7" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P7,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Organic Sunscreen SPF 50 PA++++</v>
+      </c>
+      <c r="S7" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P7,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T7" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P7,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U7" s="5">
+        <f>_xlfn.XLOOKUP(P7,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>145000</v>
+      </c>
+      <c r="V7" s="6">
+        <f>_xlfn.XLOOKUP(P7,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>65000</v>
+      </c>
+      <c r="W7" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P7,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.12</v>
+      </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>49</v>
       </c>
@@ -2196,7 +2747,7 @@
         <v>39</v>
       </c>
       <c r="M8" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-002</v>
       </c>
       <c r="N8" s="1" t="str">
@@ -2208,15 +2759,39 @@
         <v>8189876543</v>
       </c>
       <c r="P8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-HOME-001-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-HOME-001</v>
       </c>
       <c r="Q8" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-YES-TRX-2024-0007-PRD-HOME-001-2024</v>
+        <v>JNE-YES-TRX-2024-0007-PRD-HOME-001</v>
+      </c>
+      <c r="R8" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P8,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Automatic Coffee Espresso Machine</v>
+      </c>
+      <c r="S8" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P8,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T8" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P8,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchen Appliances</v>
+      </c>
+      <c r="U8" s="5">
+        <f>_xlfn.XLOOKUP(P8,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>2400000</v>
+      </c>
+      <c r="V8" s="6">
+        <f>_xlfn.XLOOKUP(P8,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1650000</v>
+      </c>
+      <c r="W8" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P8,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>4.5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>51</v>
       </c>
@@ -2254,7 +2829,7 @@
         <v>39</v>
       </c>
       <c r="M9" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-006</v>
       </c>
       <c r="N9" s="1" t="str">
@@ -2266,15 +2841,39 @@
         <v>81122334455</v>
       </c>
       <c r="P9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-BEAU-002-v1</v>
+        <f t="shared" si="1"/>
+        <v>PRD-BEAU-002</v>
       </c>
       <c r="Q9" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNT-EXP-TRX-2024-0008-PRD-BEAU-002-v1</v>
+        <v>JNT-EXP-TRX-2024-0008-PRD-BEAU-002</v>
+      </c>
+      <c r="R9" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P9,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Organic Sunscreen SPF 50 PA++++</v>
+      </c>
+      <c r="S9" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P9,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T9" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P9,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U9" s="5">
+        <f>_xlfn.XLOOKUP(P9,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>145000</v>
+      </c>
+      <c r="V9" s="6">
+        <f>_xlfn.XLOOKUP(P9,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>65000</v>
+      </c>
+      <c r="W9" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P9,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>55</v>
       </c>
@@ -2312,7 +2911,7 @@
         <v>33</v>
       </c>
       <c r="M10" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-006</v>
       </c>
       <c r="N10" s="1" t="str">
@@ -2324,15 +2923,39 @@
         <v>81122334455</v>
       </c>
       <c r="P10" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-004</v>
       </c>
       <c r="Q10" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-REG-TRX-2024-0009-PRD-ELEC-004</v>
       </c>
+      <c r="R10" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P10,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ergonomic Wireless Mouse</v>
+      </c>
+      <c r="S10" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P10,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T10" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P10,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U10" s="5">
+        <f>_xlfn.XLOOKUP(P10,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>350000</v>
+      </c>
+      <c r="V10" s="6">
+        <f>_xlfn.XLOOKUP(P10,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>200000</v>
+      </c>
+      <c r="W10" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P10,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.25</v>
+      </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>58</v>
       </c>
@@ -2370,7 +2993,7 @@
         <v>27</v>
       </c>
       <c r="M11" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-005</v>
       </c>
       <c r="N11" s="1" t="str">
@@ -2382,15 +3005,39 @@
         <v>8189876543</v>
       </c>
       <c r="P11" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-HOME-003</v>
       </c>
       <c r="Q11" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-EXP-TRX-2024-0010-PRD-HOME-003</v>
       </c>
+      <c r="R11" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P11,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Stainless Steel Cookware Set 5pcs</v>
+      </c>
+      <c r="S11" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P11,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T11" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P11,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchenware</v>
+      </c>
+      <c r="U11" s="5">
+        <f>_xlfn.XLOOKUP(P11,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>880000</v>
+      </c>
+      <c r="V11" s="6">
+        <f>_xlfn.XLOOKUP(P11,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>540000</v>
+      </c>
+      <c r="W11" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P11,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>60</v>
       </c>
@@ -2428,7 +3075,7 @@
         <v>39</v>
       </c>
       <c r="M12" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-002</v>
       </c>
       <c r="N12" s="1" t="str">
@@ -2440,15 +3087,39 @@
         <v>8189876543</v>
       </c>
       <c r="P12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-ELEC-003-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-ELEC-003</v>
       </c>
       <c r="Q12" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>SISEPAT-BEST-TRX-2024-0011-PRD-ELEC-003-2024</v>
+        <v>SISEPAT-BEST-TRX-2024-0011-PRD-ELEC-003</v>
+      </c>
+      <c r="R12" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P12,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Mechanical Gaming Keyboard RGB</v>
+      </c>
+      <c r="S12" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P12,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T12" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P12,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U12" s="5">
+        <f>_xlfn.XLOOKUP(P12,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>950000</v>
+      </c>
+      <c r="V12" s="6">
+        <f>_xlfn.XLOOKUP(P12,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>600000</v>
+      </c>
+      <c r="W12" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P12,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>1.2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>63</v>
       </c>
@@ -2486,7 +3157,7 @@
         <v>43</v>
       </c>
       <c r="M13" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-001</v>
       </c>
       <c r="N13" s="1" t="str">
@@ -2498,15 +3169,39 @@
         <v>81234567890</v>
       </c>
       <c r="P13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-HOME-002-v1</v>
+        <f t="shared" si="1"/>
+        <v>PRD-HOME-002</v>
       </c>
       <c r="Q13" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-REG-TRX-2024-0012-PRD-HOME-002-v1</v>
+        <v>JNE-REG-TRX-2024-0012-PRD-HOME-002</v>
+      </c>
+      <c r="R13" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P13,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Air Purifier HEPA Filter H13</v>
+      </c>
+      <c r="S13" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P13,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T13" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P13,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Home Appliances</v>
+      </c>
+      <c r="U13" s="5">
+        <f>_xlfn.XLOOKUP(P13,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1750000</v>
+      </c>
+      <c r="V13" s="6">
+        <f>_xlfn.XLOOKUP(P13,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1150000</v>
+      </c>
+      <c r="W13" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P13,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>66</v>
       </c>
@@ -2544,7 +3239,7 @@
         <v>43</v>
       </c>
       <c r="M14" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-001</v>
       </c>
       <c r="N14" s="1" t="str">
@@ -2556,15 +3251,39 @@
         <v>81234567890</v>
       </c>
       <c r="P14" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-HOME-003</v>
       </c>
       <c r="Q14" s="1" t="str">
         <f t="shared" si="2"/>
         <v>SISEPAT-GOKIL-TRX-2024-0013-PRD-HOME-003</v>
       </c>
+      <c r="R14" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P14,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Stainless Steel Cookware Set 5pcs</v>
+      </c>
+      <c r="S14" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P14,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T14" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P14,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchenware</v>
+      </c>
+      <c r="U14" s="5">
+        <f>_xlfn.XLOOKUP(P14,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>880000</v>
+      </c>
+      <c r="V14" s="6">
+        <f>_xlfn.XLOOKUP(P14,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>540000</v>
+      </c>
+      <c r="W14" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P14,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>68</v>
       </c>
@@ -2602,7 +3321,7 @@
         <v>19</v>
       </c>
       <c r="M15" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N15" s="1" t="str">
@@ -2614,15 +3333,39 @@
         <v>87855443322</v>
       </c>
       <c r="P15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-ELEC-003-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-ELEC-003</v>
       </c>
       <c r="Q15" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-REG-TRX-2024-0014-PRD-ELEC-003-2024</v>
+        <v>JNE-REG-TRX-2024-0014-PRD-ELEC-003</v>
+      </c>
+      <c r="R15" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P15,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Mechanical Gaming Keyboard RGB</v>
+      </c>
+      <c r="S15" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P15,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T15" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P15,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U15" s="5">
+        <f>_xlfn.XLOOKUP(P15,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>950000</v>
+      </c>
+      <c r="V15" s="6">
+        <f>_xlfn.XLOOKUP(P15,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>600000</v>
+      </c>
+      <c r="W15" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P15,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>1.2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>71</v>
       </c>
@@ -2660,7 +3403,7 @@
         <v>43</v>
       </c>
       <c r="M16" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-006</v>
       </c>
       <c r="N16" s="1" t="str">
@@ -2672,15 +3415,39 @@
         <v>81122334455</v>
       </c>
       <c r="P16" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-BEAU-003</v>
       </c>
       <c r="Q16" s="1" t="str">
         <f t="shared" si="2"/>
         <v>SISEPAT-GOKIL-TRX-2024-0015-PRD-BEAU-003</v>
       </c>
+      <c r="R16" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P16,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Sonic Electric Toothbrush Pro</v>
+      </c>
+      <c r="S16" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P16,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T16" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P16,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Personal Care</v>
+      </c>
+      <c r="U16" s="5">
+        <f>_xlfn.XLOOKUP(P16,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>490000</v>
+      </c>
+      <c r="V16" s="6">
+        <f>_xlfn.XLOOKUP(P16,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>290000</v>
+      </c>
+      <c r="W16" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P16,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.4</v>
+      </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,7 +3485,7 @@
         <v>27</v>
       </c>
       <c r="M17" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-002</v>
       </c>
       <c r="N17" s="1" t="str">
@@ -2730,15 +3497,39 @@
         <v>8189876543</v>
       </c>
       <c r="P17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-BEAU-001-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-BEAU-001</v>
       </c>
       <c r="Q17" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>SISEPAT-BEST-TRX-2024-0016-PRD-BEAU-001-2024</v>
+        <v>SISEPAT-BEST-TRX-2024-0016-PRD-BEAU-001</v>
+      </c>
+      <c r="R17" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P17,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Hydrating Serum Vitamin C 50ml</v>
+      </c>
+      <c r="S17" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P17,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T17" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P17,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U17" s="5">
+        <f>_xlfn.XLOOKUP(P17,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>185000</v>
+      </c>
+      <c r="V17" s="6">
+        <f>_xlfn.XLOOKUP(P17,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>85000</v>
+      </c>
+      <c r="W17" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P17,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,7 +3567,7 @@
         <v>33</v>
       </c>
       <c r="M18" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N18" s="1" t="str">
@@ -2788,15 +3579,39 @@
         <v>87855443322</v>
       </c>
       <c r="P18" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-BEAU-003</v>
       </c>
       <c r="Q18" s="1" t="str">
         <f t="shared" si="2"/>
         <v>SISEPAT-BEST-TRX-2024-0017-PRD-BEAU-003</v>
       </c>
+      <c r="R18" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P18,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Sonic Electric Toothbrush Pro</v>
+      </c>
+      <c r="S18" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P18,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T18" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P18,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Personal Care</v>
+      </c>
+      <c r="U18" s="5">
+        <f>_xlfn.XLOOKUP(P18,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>490000</v>
+      </c>
+      <c r="V18" s="6">
+        <f>_xlfn.XLOOKUP(P18,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>290000</v>
+      </c>
+      <c r="W18" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P18,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.4</v>
+      </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>77</v>
       </c>
@@ -2834,7 +3649,7 @@
         <v>19</v>
       </c>
       <c r="M19" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N19" s="1" t="str">
@@ -2846,15 +3661,39 @@
         <v>87855443322</v>
       </c>
       <c r="P19" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-004</v>
       </c>
       <c r="Q19" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-EXP-TRX-2024-0018-PRD-ELEC-004</v>
       </c>
+      <c r="R19" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P19,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ergonomic Wireless Mouse</v>
+      </c>
+      <c r="S19" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P19,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T19" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P19,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U19" s="5">
+        <f>_xlfn.XLOOKUP(P19,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>350000</v>
+      </c>
+      <c r="V19" s="6">
+        <f>_xlfn.XLOOKUP(P19,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>200000</v>
+      </c>
+      <c r="W19" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P19,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.25</v>
+      </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>79</v>
       </c>
@@ -2892,7 +3731,7 @@
         <v>33</v>
       </c>
       <c r="M20" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-001</v>
       </c>
       <c r="N20" s="1" t="str">
@@ -2904,15 +3743,39 @@
         <v>81234567890</v>
       </c>
       <c r="P20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-ELEC-004-v1</v>
+        <f t="shared" si="1"/>
+        <v>PRD-ELEC-004</v>
       </c>
       <c r="Q20" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNT-REG-TRX-2024-0019-PRD-ELEC-004-v1</v>
+        <v>JNT-REG-TRX-2024-0019-PRD-ELEC-004</v>
+      </c>
+      <c r="R20" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P20,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ergonomic Wireless Mouse</v>
+      </c>
+      <c r="S20" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P20,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T20" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P20,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U20" s="5">
+        <f>_xlfn.XLOOKUP(P20,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>350000</v>
+      </c>
+      <c r="V20" s="6">
+        <f>_xlfn.XLOOKUP(P20,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>200000</v>
+      </c>
+      <c r="W20" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P20,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>81</v>
       </c>
@@ -2950,7 +3813,7 @@
         <v>43</v>
       </c>
       <c r="M21" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-010</v>
       </c>
       <c r="N21" s="1" t="str">
@@ -2962,15 +3825,39 @@
         <v>81377665544</v>
       </c>
       <c r="P21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-HOME-001-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-HOME-001</v>
       </c>
       <c r="Q21" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>SISEPAT-GOKIL-TRX-2024-0020-PRD-HOME-001-2024</v>
+        <v>SISEPAT-GOKIL-TRX-2024-0020-PRD-HOME-001</v>
+      </c>
+      <c r="R21" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P21,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Automatic Coffee Espresso Machine</v>
+      </c>
+      <c r="S21" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P21,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T21" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P21,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchen Appliances</v>
+      </c>
+      <c r="U21" s="5">
+        <f>_xlfn.XLOOKUP(P21,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>2400000</v>
+      </c>
+      <c r="V21" s="6">
+        <f>_xlfn.XLOOKUP(P21,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1650000</v>
+      </c>
+      <c r="W21" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P21,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>4.5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>83</v>
       </c>
@@ -3008,7 +3895,7 @@
         <v>39</v>
       </c>
       <c r="M22" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-007</v>
       </c>
       <c r="N22" s="1" t="str">
@@ -3020,15 +3907,39 @@
         <v>8170099887</v>
       </c>
       <c r="P22" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-FASH-002</v>
       </c>
       <c r="Q22" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-EXP-TRX-2024-0021-PRD-FASH-002</v>
       </c>
+      <c r="R22" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P22,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Women Floral Summer Dress</v>
+      </c>
+      <c r="S22" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P22,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T22" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P22,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Dresses</v>
+      </c>
+      <c r="U22" s="5">
+        <f>_xlfn.XLOOKUP(P22,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>320000</v>
+      </c>
+      <c r="V22" s="6">
+        <f>_xlfn.XLOOKUP(P22,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>180000</v>
+      </c>
+      <c r="W22" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P22,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.35</v>
+      </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>86</v>
       </c>
@@ -3066,7 +3977,7 @@
         <v>27</v>
       </c>
       <c r="M23" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N23" s="1" t="str">
@@ -3078,15 +3989,39 @@
         <v>87855443322</v>
       </c>
       <c r="P23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-FASH-004-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-FASH-004</v>
       </c>
       <c r="Q23" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-REG-TRX-2024-0022-PRD-FASH-004-2024</v>
+        <v>JNE-REG-TRX-2024-0022-PRD-FASH-004</v>
+      </c>
+      <c r="R23" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P23,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Leather Minimalist Wallet</v>
+      </c>
+      <c r="S23" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P23,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T23" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P23,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Accessories</v>
+      </c>
+      <c r="U23" s="5">
+        <f>_xlfn.XLOOKUP(P23,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>220000</v>
+      </c>
+      <c r="V23" s="6">
+        <f>_xlfn.XLOOKUP(P23,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>110000</v>
+      </c>
+      <c r="W23" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P23,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>88</v>
       </c>
@@ -3124,7 +4059,7 @@
         <v>39</v>
       </c>
       <c r="M24" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-001</v>
       </c>
       <c r="N24" s="1" t="str">
@@ -3136,15 +4071,39 @@
         <v>81234567890</v>
       </c>
       <c r="P24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-HOME-002-v1</v>
+        <f t="shared" si="1"/>
+        <v>PRD-HOME-002</v>
       </c>
       <c r="Q24" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-REG-TRX-2024-0023-PRD-HOME-002-v1</v>
+        <v>JNE-REG-TRX-2024-0023-PRD-HOME-002</v>
+      </c>
+      <c r="R24" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P24,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Air Purifier HEPA Filter H13</v>
+      </c>
+      <c r="S24" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P24,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T24" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P24,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Home Appliances</v>
+      </c>
+      <c r="U24" s="5">
+        <f>_xlfn.XLOOKUP(P24,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1750000</v>
+      </c>
+      <c r="V24" s="6">
+        <f>_xlfn.XLOOKUP(P24,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1150000</v>
+      </c>
+      <c r="W24" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P24,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.2</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>89</v>
       </c>
@@ -3182,7 +4141,7 @@
         <v>39</v>
       </c>
       <c r="M25" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-007</v>
       </c>
       <c r="N25" s="1" t="str">
@@ -3194,15 +4153,39 @@
         <v>8170099887</v>
       </c>
       <c r="P25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-BEAU-003-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-BEAU-003</v>
       </c>
       <c r="Q25" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-REG-TRX-2024-0024-PRD-BEAU-003-2024</v>
+        <v>JNE-REG-TRX-2024-0024-PRD-BEAU-003</v>
+      </c>
+      <c r="R25" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P25,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Sonic Electric Toothbrush Pro</v>
+      </c>
+      <c r="S25" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P25,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T25" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P25,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Personal Care</v>
+      </c>
+      <c r="U25" s="5">
+        <f>_xlfn.XLOOKUP(P25,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>490000</v>
+      </c>
+      <c r="V25" s="6">
+        <f>_xlfn.XLOOKUP(P25,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>290000</v>
+      </c>
+      <c r="W25" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P25,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>92</v>
       </c>
@@ -3240,7 +4223,7 @@
         <v>43</v>
       </c>
       <c r="M26" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-008</v>
       </c>
       <c r="N26" s="1" t="str">
@@ -3252,15 +4235,39 @@
         <v>85211447788</v>
       </c>
       <c r="P26" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-003</v>
       </c>
       <c r="Q26" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-EXP-TRX-2024-0025-PRD-ELEC-003</v>
       </c>
+      <c r="R26" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P26,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Mechanical Gaming Keyboard RGB</v>
+      </c>
+      <c r="S26" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P26,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T26" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P26,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U26" s="5">
+        <f>_xlfn.XLOOKUP(P26,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>950000</v>
+      </c>
+      <c r="V26" s="6">
+        <f>_xlfn.XLOOKUP(P26,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>600000</v>
+      </c>
+      <c r="W26" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P26,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>95</v>
       </c>
@@ -3298,7 +4305,7 @@
         <v>27</v>
       </c>
       <c r="M27" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-008</v>
       </c>
       <c r="N27" s="1" t="str">
@@ -3310,15 +4317,39 @@
         <v>85211447788</v>
       </c>
       <c r="P27" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-FASH-004</v>
       </c>
       <c r="Q27" s="1" t="str">
         <f t="shared" si="2"/>
         <v>SISEPAT-BEST-TRX-2024-0026-PRD-FASH-004</v>
       </c>
+      <c r="R27" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P27,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Leather Minimalist Wallet</v>
+      </c>
+      <c r="S27" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P27,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T27" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P27,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Accessories</v>
+      </c>
+      <c r="U27" s="5">
+        <f>_xlfn.XLOOKUP(P27,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>220000</v>
+      </c>
+      <c r="V27" s="6">
+        <f>_xlfn.XLOOKUP(P27,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>110000</v>
+      </c>
+      <c r="W27" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P27,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.15</v>
+      </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>97</v>
       </c>
@@ -3356,7 +4387,7 @@
         <v>19</v>
       </c>
       <c r="M28" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N28" s="1" t="str">
@@ -3368,15 +4399,39 @@
         <v>87855443322</v>
       </c>
       <c r="P28" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-FASH-002</v>
       </c>
       <c r="Q28" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNE-REG-TRX-2024-0027-PRD-FASH-002</v>
       </c>
+      <c r="R28" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P28,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Women Floral Summer Dress</v>
+      </c>
+      <c r="S28" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P28,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T28" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P28,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Dresses</v>
+      </c>
+      <c r="U28" s="5">
+        <f>_xlfn.XLOOKUP(P28,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>320000</v>
+      </c>
+      <c r="V28" s="6">
+        <f>_xlfn.XLOOKUP(P28,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>180000</v>
+      </c>
+      <c r="W28" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P28,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.35</v>
+      </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>98</v>
       </c>
@@ -3414,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="M29" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-009</v>
       </c>
       <c r="N29" s="1" t="str">
@@ -3426,15 +4481,39 @@
         <v>81933221100</v>
       </c>
       <c r="P29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-FASH-001-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-FASH-001</v>
       </c>
       <c r="Q29" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-REG-TRX-2024-0028-PRD-FASH-001-2024</v>
+        <v>JNE-REG-TRX-2024-0028-PRD-FASH-001</v>
+      </c>
+      <c r="R29" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P29,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Men Denim Jacket Vintage Blue</v>
+      </c>
+      <c r="S29" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P29,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T29" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P29,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Outerwear</v>
+      </c>
+      <c r="U29" s="5">
+        <f>_xlfn.XLOOKUP(P29,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>450000</v>
+      </c>
+      <c r="V29" s="6">
+        <f>_xlfn.XLOOKUP(P29,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>260000</v>
+      </c>
+      <c r="W29" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P29,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.9</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>101</v>
       </c>
@@ -3472,7 +4551,7 @@
         <v>27</v>
       </c>
       <c r="M30" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-002</v>
       </c>
       <c r="N30" s="1" t="str">
@@ -3484,15 +4563,39 @@
         <v>8189876543</v>
       </c>
       <c r="P30" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-001</v>
       </c>
       <c r="Q30" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-REG-TRX-2024-0029-PRD-ELEC-001</v>
       </c>
+      <c r="R30" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P30,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Wireless Noise Cancelling Headphones</v>
+      </c>
+      <c r="S30" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P30,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T30" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P30,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Audio</v>
+      </c>
+      <c r="U30" s="5">
+        <f>_xlfn.XLOOKUP(P30,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1250000</v>
+      </c>
+      <c r="V30" s="6">
+        <f>_xlfn.XLOOKUP(P30,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="W30" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P30,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>102</v>
       </c>
@@ -3530,7 +4633,7 @@
         <v>19</v>
       </c>
       <c r="M31" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N31" s="1" t="str">
@@ -3542,15 +4645,39 @@
         <v>87855443322</v>
       </c>
       <c r="P31" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PRD-FASH-001-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-FASH-001</v>
       </c>
       <c r="Q31" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>SISEPAT-GOKIL-TRX-2024-0030-PRD-FASH-001-2024</v>
+        <v>SISEPAT-GOKIL-TRX-2024-0030-PRD-FASH-001</v>
+      </c>
+      <c r="R31" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P31,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Men Denim Jacket Vintage Blue</v>
+      </c>
+      <c r="S31" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P31,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T31" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P31,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Outerwear</v>
+      </c>
+      <c r="U31" s="5">
+        <f>_xlfn.XLOOKUP(P31,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>450000</v>
+      </c>
+      <c r="V31" s="6">
+        <f>_xlfn.XLOOKUP(P31,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>260000</v>
+      </c>
+      <c r="W31" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P31,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.9</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>103</v>
       </c>
@@ -3588,7 +4715,7 @@
         <v>33</v>
       </c>
       <c r="M32" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-002</v>
       </c>
       <c r="N32" s="1" t="str">
@@ -3600,15 +4727,39 @@
         <v>8189876543</v>
       </c>
       <c r="P32" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-BEAU-003</v>
       </c>
       <c r="Q32" s="1" t="str">
         <f t="shared" si="2"/>
         <v>SISEPAT-BEST-TRX-2024-0031-PRD-BEAU-003</v>
       </c>
+      <c r="R32" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P32,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Sonic Electric Toothbrush Pro</v>
+      </c>
+      <c r="S32" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P32,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T32" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P32,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Personal Care</v>
+      </c>
+      <c r="U32" s="5">
+        <f>_xlfn.XLOOKUP(P32,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>490000</v>
+      </c>
+      <c r="V32" s="6">
+        <f>_xlfn.XLOOKUP(P32,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>290000</v>
+      </c>
+      <c r="W32" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P32,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.4</v>
+      </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>105</v>
       </c>
@@ -3646,7 +4797,7 @@
         <v>43</v>
       </c>
       <c r="M33" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-006</v>
       </c>
       <c r="N33" s="1" t="str">
@@ -3658,15 +4809,39 @@
         <v>81122334455</v>
       </c>
       <c r="P33" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-004</v>
       </c>
       <c r="Q33" s="1" t="str">
         <f t="shared" si="2"/>
         <v>SISEPAT-GOKIL-TRX-2024-0032-PRD-ELEC-004</v>
       </c>
+      <c r="R33" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P33,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ergonomic Wireless Mouse</v>
+      </c>
+      <c r="S33" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P33,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T33" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P33,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U33" s="5">
+        <f>_xlfn.XLOOKUP(P33,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>350000</v>
+      </c>
+      <c r="V33" s="6">
+        <f>_xlfn.XLOOKUP(P33,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>200000</v>
+      </c>
+      <c r="W33" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P33,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.25</v>
+      </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>106</v>
       </c>
@@ -3704,7 +4879,7 @@
         <v>39</v>
       </c>
       <c r="M34" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-005</v>
       </c>
       <c r="N34" s="1" t="str">
@@ -3716,15 +4891,39 @@
         <v>8189876543</v>
       </c>
       <c r="P34" s="1" t="str">
-        <f t="shared" ref="P34:P65" si="3">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D34,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-001</v>
       </c>
       <c r="Q34" s="1" t="str">
         <f t="shared" si="2"/>
         <v>SISEPAT-BEST-TRX-2024-0033-PRD-ELEC-001</v>
       </c>
+      <c r="R34" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P34,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Wireless Noise Cancelling Headphones</v>
+      </c>
+      <c r="S34" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P34,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T34" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P34,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Audio</v>
+      </c>
+      <c r="U34" s="5">
+        <f>_xlfn.XLOOKUP(P34,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1250000</v>
+      </c>
+      <c r="V34" s="6">
+        <f>_xlfn.XLOOKUP(P34,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="W34" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P34,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>108</v>
       </c>
@@ -3762,7 +4961,7 @@
         <v>19</v>
       </c>
       <c r="M35" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-002</v>
       </c>
       <c r="N35" s="1" t="str">
@@ -3774,15 +4973,39 @@
         <v>8189876543</v>
       </c>
       <c r="P35" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-BEAU-003-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-BEAU-003</v>
       </c>
       <c r="Q35" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-REG-TRX-2024-0034-PRD-BEAU-003-2024</v>
+        <v>JNE-REG-TRX-2024-0034-PRD-BEAU-003</v>
+      </c>
+      <c r="R35" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P35,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Sonic Electric Toothbrush Pro</v>
+      </c>
+      <c r="S35" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P35,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T35" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P35,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Personal Care</v>
+      </c>
+      <c r="U35" s="5">
+        <f>_xlfn.XLOOKUP(P35,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>490000</v>
+      </c>
+      <c r="V35" s="6">
+        <f>_xlfn.XLOOKUP(P35,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>290000</v>
+      </c>
+      <c r="W35" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P35,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.4</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>110</v>
       </c>
@@ -3820,7 +5043,7 @@
         <v>33</v>
       </c>
       <c r="M36" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-005</v>
       </c>
       <c r="N36" s="1" t="str">
@@ -3832,15 +5055,39 @@
         <v>8189876543</v>
       </c>
       <c r="P36" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-FASH-001-v1</v>
+        <f t="shared" si="1"/>
+        <v>PRD-FASH-001</v>
       </c>
       <c r="Q36" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>SISEPAT-BEST-TRX-2024-0035-PRD-FASH-001-v1</v>
+        <v>SISEPAT-BEST-TRX-2024-0035-PRD-FASH-001</v>
+      </c>
+      <c r="R36" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P36,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Men Denim Jacket Vintage Blue</v>
+      </c>
+      <c r="S36" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P36,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T36" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P36,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Outerwear</v>
+      </c>
+      <c r="U36" s="5">
+        <f>_xlfn.XLOOKUP(P36,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>450000</v>
+      </c>
+      <c r="V36" s="6">
+        <f>_xlfn.XLOOKUP(P36,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>260000</v>
+      </c>
+      <c r="W36" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P36,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.9</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>112</v>
       </c>
@@ -3878,7 +5125,7 @@
         <v>39</v>
       </c>
       <c r="M37" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-003</v>
       </c>
       <c r="N37" s="1" t="str">
@@ -3890,15 +5137,39 @@
         <v>85611223344</v>
       </c>
       <c r="P37" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-BEAU-001-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-BEAU-001</v>
       </c>
       <c r="Q37" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-YES-TRX-2024-0036-PRD-BEAU-001-2024</v>
+        <v>JNE-YES-TRX-2024-0036-PRD-BEAU-001</v>
+      </c>
+      <c r="R37" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P37,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Hydrating Serum Vitamin C 50ml</v>
+      </c>
+      <c r="S37" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P37,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T37" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P37,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U37" s="5">
+        <f>_xlfn.XLOOKUP(P37,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>185000</v>
+      </c>
+      <c r="V37" s="6">
+        <f>_xlfn.XLOOKUP(P37,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>85000</v>
+      </c>
+      <c r="W37" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P37,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>114</v>
       </c>
@@ -3936,7 +5207,7 @@
         <v>33</v>
       </c>
       <c r="M38" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-002</v>
       </c>
       <c r="N38" s="1" t="str">
@@ -3948,15 +5219,39 @@
         <v>8189876543</v>
       </c>
       <c r="P38" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-FASH-002-v1</v>
+        <f t="shared" si="1"/>
+        <v>PRD-FASH-002</v>
       </c>
       <c r="Q38" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNT-REG-TRX-2024-0037-PRD-FASH-002-v1</v>
+        <v>JNT-REG-TRX-2024-0037-PRD-FASH-002</v>
+      </c>
+      <c r="R38" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P38,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Women Floral Summer Dress</v>
+      </c>
+      <c r="S38" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P38,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T38" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P38,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Dresses</v>
+      </c>
+      <c r="U38" s="5">
+        <f>_xlfn.XLOOKUP(P38,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>320000</v>
+      </c>
+      <c r="V38" s="6">
+        <f>_xlfn.XLOOKUP(P38,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>180000</v>
+      </c>
+      <c r="W38" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P38,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.35</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>116</v>
       </c>
@@ -3994,7 +5289,7 @@
         <v>19</v>
       </c>
       <c r="M39" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N39" s="1" t="str">
@@ -4006,15 +5301,39 @@
         <v>87855443322</v>
       </c>
       <c r="P39" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-FASH-002</v>
       </c>
       <c r="Q39" s="1" t="str">
         <f t="shared" si="2"/>
         <v>SISEPAT-GOKIL-TRX-2024-0038-PRD-FASH-002</v>
       </c>
+      <c r="R39" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P39,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Women Floral Summer Dress</v>
+      </c>
+      <c r="S39" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P39,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T39" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P39,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Dresses</v>
+      </c>
+      <c r="U39" s="5">
+        <f>_xlfn.XLOOKUP(P39,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>320000</v>
+      </c>
+      <c r="V39" s="6">
+        <f>_xlfn.XLOOKUP(P39,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>180000</v>
+      </c>
+      <c r="W39" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P39,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.35</v>
+      </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>118</v>
       </c>
@@ -4052,7 +5371,7 @@
         <v>19</v>
       </c>
       <c r="M40" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-001</v>
       </c>
       <c r="N40" s="1" t="str">
@@ -4064,15 +5383,39 @@
         <v>81234567890</v>
       </c>
       <c r="P40" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-ELEC-002-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-ELEC-002</v>
       </c>
       <c r="Q40" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-YES-TRX-2024-0039-PRD-ELEC-002-2024</v>
+        <v>JNE-YES-TRX-2024-0039-PRD-ELEC-002</v>
+      </c>
+      <c r="R40" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P40,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Smart Watch Fitness Tracker V2</v>
+      </c>
+      <c r="S40" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P40,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T40" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P40,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Wearables</v>
+      </c>
+      <c r="U40" s="5">
+        <f>_xlfn.XLOOKUP(P40,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="V40" s="6">
+        <f>_xlfn.XLOOKUP(P40,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>520000</v>
+      </c>
+      <c r="W40" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P40,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.3</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>121</v>
       </c>
@@ -4110,7 +5453,7 @@
         <v>39</v>
       </c>
       <c r="M41" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-010</v>
       </c>
       <c r="N41" s="1" t="str">
@@ -4122,15 +5465,39 @@
         <v>81377665544</v>
       </c>
       <c r="P41" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-FASH-004</v>
       </c>
       <c r="Q41" s="1" t="str">
         <f t="shared" si="2"/>
         <v>SISEPAT-BEST-TRX-2024-0040-PRD-FASH-004</v>
       </c>
+      <c r="R41" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P41,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Leather Minimalist Wallet</v>
+      </c>
+      <c r="S41" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P41,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T41" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P41,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Accessories</v>
+      </c>
+      <c r="U41" s="5">
+        <f>_xlfn.XLOOKUP(P41,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>220000</v>
+      </c>
+      <c r="V41" s="6">
+        <f>_xlfn.XLOOKUP(P41,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>110000</v>
+      </c>
+      <c r="W41" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P41,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.15</v>
+      </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>123</v>
       </c>
@@ -4168,7 +5535,7 @@
         <v>33</v>
       </c>
       <c r="M42" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N42" s="1" t="str">
@@ -4180,15 +5547,39 @@
         <v>87855443322</v>
       </c>
       <c r="P42" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-FASH-001-v1</v>
+        <f t="shared" si="1"/>
+        <v>PRD-FASH-001</v>
       </c>
       <c r="Q42" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>SISEPAT-GOKIL-TRX-2024-0041-PRD-FASH-001-v1</v>
+        <v>SISEPAT-GOKIL-TRX-2024-0041-PRD-FASH-001</v>
+      </c>
+      <c r="R42" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P42,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Men Denim Jacket Vintage Blue</v>
+      </c>
+      <c r="S42" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P42,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T42" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P42,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Outerwear</v>
+      </c>
+      <c r="U42" s="5">
+        <f>_xlfn.XLOOKUP(P42,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>450000</v>
+      </c>
+      <c r="V42" s="6">
+        <f>_xlfn.XLOOKUP(P42,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>260000</v>
+      </c>
+      <c r="W42" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P42,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.9</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>124</v>
       </c>
@@ -4226,7 +5617,7 @@
         <v>27</v>
       </c>
       <c r="M43" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-007</v>
       </c>
       <c r="N43" s="1" t="str">
@@ -4238,15 +5629,39 @@
         <v>8170099887</v>
       </c>
       <c r="P43" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-HOME-003</v>
       </c>
       <c r="Q43" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNE-REG-TRX-2024-0042-PRD-HOME-003</v>
       </c>
+      <c r="R43" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P43,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Stainless Steel Cookware Set 5pcs</v>
+      </c>
+      <c r="S43" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P43,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T43" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P43,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchenware</v>
+      </c>
+      <c r="U43" s="5">
+        <f>_xlfn.XLOOKUP(P43,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>880000</v>
+      </c>
+      <c r="V43" s="6">
+        <f>_xlfn.XLOOKUP(P43,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>540000</v>
+      </c>
+      <c r="W43" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P43,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>126</v>
       </c>
@@ -4284,7 +5699,7 @@
         <v>33</v>
       </c>
       <c r="M44" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-001</v>
       </c>
       <c r="N44" s="1" t="str">
@@ -4296,15 +5711,39 @@
         <v>81234567890</v>
       </c>
       <c r="P44" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-ELEC-005-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-ELEC-005</v>
       </c>
       <c r="Q44" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-REG-TRX-2024-0043-PRD-ELEC-005-2024</v>
+        <v>JNE-REG-TRX-2024-0043-PRD-ELEC-005</v>
+      </c>
+      <c r="R44" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P44,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ultra HD Webcam 4K Pro</v>
+      </c>
+      <c r="S44" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P44,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T44" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P44,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U44" s="5">
+        <f>_xlfn.XLOOKUP(P44,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1100000</v>
+      </c>
+      <c r="V44" s="6">
+        <f>_xlfn.XLOOKUP(P44,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>720000</v>
+      </c>
+      <c r="W44" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P44,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.4</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>128</v>
       </c>
@@ -4342,7 +5781,7 @@
         <v>19</v>
       </c>
       <c r="M45" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N45" s="1" t="str">
@@ -4354,15 +5793,39 @@
         <v>87855443322</v>
       </c>
       <c r="P45" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-FASH-004</v>
       </c>
       <c r="Q45" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-EXP-TRX-2024-0044-PRD-FASH-004</v>
       </c>
+      <c r="R45" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P45,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Leather Minimalist Wallet</v>
+      </c>
+      <c r="S45" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P45,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T45" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P45,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Accessories</v>
+      </c>
+      <c r="U45" s="5">
+        <f>_xlfn.XLOOKUP(P45,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>220000</v>
+      </c>
+      <c r="V45" s="6">
+        <f>_xlfn.XLOOKUP(P45,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>110000</v>
+      </c>
+      <c r="W45" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P45,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.15</v>
+      </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>130</v>
       </c>
@@ -4400,7 +5863,7 @@
         <v>39</v>
       </c>
       <c r="M46" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-005</v>
       </c>
       <c r="N46" s="1" t="str">
@@ -4412,15 +5875,39 @@
         <v>8189876543</v>
       </c>
       <c r="P46" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-ELEC-004-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-ELEC-004</v>
       </c>
       <c r="Q46" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-REG-TRX-2024-0045-PRD-ELEC-004-2024</v>
+        <v>JNE-REG-TRX-2024-0045-PRD-ELEC-004</v>
+      </c>
+      <c r="R46" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P46,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ergonomic Wireless Mouse</v>
+      </c>
+      <c r="S46" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P46,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T46" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P46,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U46" s="5">
+        <f>_xlfn.XLOOKUP(P46,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>350000</v>
+      </c>
+      <c r="V46" s="6">
+        <f>_xlfn.XLOOKUP(P46,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>200000</v>
+      </c>
+      <c r="W46" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P46,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.25</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>132</v>
       </c>
@@ -4458,7 +5945,7 @@
         <v>27</v>
       </c>
       <c r="M47" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-010</v>
       </c>
       <c r="N47" s="1" t="str">
@@ -4470,15 +5957,39 @@
         <v>81377665544</v>
       </c>
       <c r="P47" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-004</v>
       </c>
       <c r="Q47" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-EXP-TRX-2024-0046-PRD-ELEC-004</v>
       </c>
+      <c r="R47" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P47,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ergonomic Wireless Mouse</v>
+      </c>
+      <c r="S47" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P47,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T47" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P47,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U47" s="5">
+        <f>_xlfn.XLOOKUP(P47,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>350000</v>
+      </c>
+      <c r="V47" s="6">
+        <f>_xlfn.XLOOKUP(P47,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>200000</v>
+      </c>
+      <c r="W47" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P47,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.25</v>
+      </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>134</v>
       </c>
@@ -4516,7 +6027,7 @@
         <v>43</v>
       </c>
       <c r="M48" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-003</v>
       </c>
       <c r="N48" s="1" t="str">
@@ -4528,15 +6039,39 @@
         <v>85611223344</v>
       </c>
       <c r="P48" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-BEAU-001</v>
       </c>
       <c r="Q48" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-REG-TRX-2024-0047-PRD-BEAU-001</v>
       </c>
+      <c r="R48" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P48,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Hydrating Serum Vitamin C 50ml</v>
+      </c>
+      <c r="S48" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P48,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T48" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P48,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U48" s="5">
+        <f>_xlfn.XLOOKUP(P48,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>185000</v>
+      </c>
+      <c r="V48" s="6">
+        <f>_xlfn.XLOOKUP(P48,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>85000</v>
+      </c>
+      <c r="W48" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P48,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.1</v>
+      </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>137</v>
       </c>
@@ -4574,7 +6109,7 @@
         <v>19</v>
       </c>
       <c r="M49" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-009</v>
       </c>
       <c r="N49" s="1" t="str">
@@ -4586,15 +6121,39 @@
         <v>81933221100</v>
       </c>
       <c r="P49" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-FASH-004</v>
       </c>
       <c r="Q49" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-REG-TRX-2024-0048-PRD-FASH-004</v>
       </c>
+      <c r="R49" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P49,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Leather Minimalist Wallet</v>
+      </c>
+      <c r="S49" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P49,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T49" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P49,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Accessories</v>
+      </c>
+      <c r="U49" s="5">
+        <f>_xlfn.XLOOKUP(P49,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>220000</v>
+      </c>
+      <c r="V49" s="6">
+        <f>_xlfn.XLOOKUP(P49,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>110000</v>
+      </c>
+      <c r="W49" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P49,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.15</v>
+      </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>138</v>
       </c>
@@ -4632,7 +6191,7 @@
         <v>27</v>
       </c>
       <c r="M50" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-005</v>
       </c>
       <c r="N50" s="1" t="str">
@@ -4644,15 +6203,39 @@
         <v>8189876543</v>
       </c>
       <c r="P50" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-BEAU-001</v>
       </c>
       <c r="Q50" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNE-REG-TRX-2024-0049-PRD-BEAU-001</v>
       </c>
+      <c r="R50" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P50,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Hydrating Serum Vitamin C 50ml</v>
+      </c>
+      <c r="S50" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P50,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T50" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P50,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U50" s="5">
+        <f>_xlfn.XLOOKUP(P50,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>185000</v>
+      </c>
+      <c r="V50" s="6">
+        <f>_xlfn.XLOOKUP(P50,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>85000</v>
+      </c>
+      <c r="W50" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P50,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.1</v>
+      </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>140</v>
       </c>
@@ -4690,7 +6273,7 @@
         <v>27</v>
       </c>
       <c r="M51" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-005</v>
       </c>
       <c r="N51" s="1" t="str">
@@ -4702,15 +6285,39 @@
         <v>8189876543</v>
       </c>
       <c r="P51" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-004</v>
       </c>
       <c r="Q51" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNE-REG-TRX-2024-0050-PRD-ELEC-004</v>
       </c>
+      <c r="R51" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P51,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ergonomic Wireless Mouse</v>
+      </c>
+      <c r="S51" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P51,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T51" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P51,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U51" s="5">
+        <f>_xlfn.XLOOKUP(P51,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>350000</v>
+      </c>
+      <c r="V51" s="6">
+        <f>_xlfn.XLOOKUP(P51,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>200000</v>
+      </c>
+      <c r="W51" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P51,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.25</v>
+      </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>142</v>
       </c>
@@ -4748,7 +6355,7 @@
         <v>43</v>
       </c>
       <c r="M52" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N52" s="1" t="str">
@@ -4760,15 +6367,39 @@
         <v>87855443322</v>
       </c>
       <c r="P52" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-002</v>
       </c>
       <c r="Q52" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNE-REG-TRX-2024-0051-PRD-ELEC-002</v>
       </c>
+      <c r="R52" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P52,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Smart Watch Fitness Tracker V2</v>
+      </c>
+      <c r="S52" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P52,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T52" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P52,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Wearables</v>
+      </c>
+      <c r="U52" s="5">
+        <f>_xlfn.XLOOKUP(P52,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="V52" s="6">
+        <f>_xlfn.XLOOKUP(P52,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>520000</v>
+      </c>
+      <c r="W52" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P52,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.3</v>
+      </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>144</v>
       </c>
@@ -4806,7 +6437,7 @@
         <v>33</v>
       </c>
       <c r="M53" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-010</v>
       </c>
       <c r="N53" s="1" t="str">
@@ -4818,15 +6449,39 @@
         <v>81377665544</v>
       </c>
       <c r="P53" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-HOME-003</v>
       </c>
       <c r="Q53" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNE-REG-TRX-2024-0052-PRD-HOME-003</v>
       </c>
+      <c r="R53" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P53,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Stainless Steel Cookware Set 5pcs</v>
+      </c>
+      <c r="S53" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P53,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T53" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P53,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchenware</v>
+      </c>
+      <c r="U53" s="5">
+        <f>_xlfn.XLOOKUP(P53,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>880000</v>
+      </c>
+      <c r="V53" s="6">
+        <f>_xlfn.XLOOKUP(P53,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>540000</v>
+      </c>
+      <c r="W53" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P53,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>146</v>
       </c>
@@ -4864,7 +6519,7 @@
         <v>39</v>
       </c>
       <c r="M54" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-009</v>
       </c>
       <c r="N54" s="1" t="str">
@@ -4876,15 +6531,39 @@
         <v>81933221100</v>
       </c>
       <c r="P54" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-BEAU-001-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-BEAU-001</v>
       </c>
       <c r="Q54" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-REG-TRX-2024-0053-PRD-BEAU-001-2024</v>
+        <v>JNE-REG-TRX-2024-0053-PRD-BEAU-001</v>
+      </c>
+      <c r="R54" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P54,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Hydrating Serum Vitamin C 50ml</v>
+      </c>
+      <c r="S54" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P54,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T54" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P54,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U54" s="5">
+        <f>_xlfn.XLOOKUP(P54,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>185000</v>
+      </c>
+      <c r="V54" s="6">
+        <f>_xlfn.XLOOKUP(P54,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>85000</v>
+      </c>
+      <c r="W54" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P54,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>148</v>
       </c>
@@ -4922,7 +6601,7 @@
         <v>39</v>
       </c>
       <c r="M55" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-007</v>
       </c>
       <c r="N55" s="1" t="str">
@@ -4934,15 +6613,39 @@
         <v>8170099887</v>
       </c>
       <c r="P55" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-HOME-003</v>
       </c>
       <c r="Q55" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-EXP-TRX-2024-0054-PRD-HOME-003</v>
       </c>
+      <c r="R55" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P55,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Stainless Steel Cookware Set 5pcs</v>
+      </c>
+      <c r="S55" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P55,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T55" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P55,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchenware</v>
+      </c>
+      <c r="U55" s="5">
+        <f>_xlfn.XLOOKUP(P55,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>880000</v>
+      </c>
+      <c r="V55" s="6">
+        <f>_xlfn.XLOOKUP(P55,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>540000</v>
+      </c>
+      <c r="W55" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P55,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>150</v>
       </c>
@@ -4980,7 +6683,7 @@
         <v>33</v>
       </c>
       <c r="M56" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-008</v>
       </c>
       <c r="N56" s="1" t="str">
@@ -4992,15 +6695,39 @@
         <v>85211447788</v>
       </c>
       <c r="P56" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-003</v>
       </c>
       <c r="Q56" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNE-REG-TRX-2024-0055-PRD-ELEC-003</v>
       </c>
+      <c r="R56" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P56,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Mechanical Gaming Keyboard RGB</v>
+      </c>
+      <c r="S56" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P56,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T56" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P56,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U56" s="5">
+        <f>_xlfn.XLOOKUP(P56,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>950000</v>
+      </c>
+      <c r="V56" s="6">
+        <f>_xlfn.XLOOKUP(P56,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>600000</v>
+      </c>
+      <c r="W56" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P56,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>152</v>
       </c>
@@ -5038,7 +6765,7 @@
         <v>33</v>
       </c>
       <c r="M57" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-007</v>
       </c>
       <c r="N57" s="1" t="str">
@@ -5050,15 +6777,39 @@
         <v>8170099887</v>
       </c>
       <c r="P57" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-ELEC-005-v1</v>
+        <f t="shared" si="1"/>
+        <v>PRD-ELEC-005</v>
       </c>
       <c r="Q57" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>SISEPAT-GOKIL-TRX-2024-0056-PRD-ELEC-005-v1</v>
+        <v>SISEPAT-GOKIL-TRX-2024-0056-PRD-ELEC-005</v>
+      </c>
+      <c r="R57" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P57,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ultra HD Webcam 4K Pro</v>
+      </c>
+      <c r="S57" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P57,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T57" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P57,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U57" s="5">
+        <f>_xlfn.XLOOKUP(P57,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1100000</v>
+      </c>
+      <c r="V57" s="6">
+        <f>_xlfn.XLOOKUP(P57,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>720000</v>
+      </c>
+      <c r="W57" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P57,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.4</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>154</v>
       </c>
@@ -5096,7 +6847,7 @@
         <v>27</v>
       </c>
       <c r="M58" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-001</v>
       </c>
       <c r="N58" s="1" t="str">
@@ -5108,15 +6859,39 @@
         <v>81234567890</v>
       </c>
       <c r="P58" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-BEAU-001-2024</v>
+        <f t="shared" si="1"/>
+        <v>PRD-BEAU-001</v>
       </c>
       <c r="Q58" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNT-REG-TRX-2024-0057-PRD-BEAU-001-2024</v>
+        <v>JNT-REG-TRX-2024-0057-PRD-BEAU-001</v>
+      </c>
+      <c r="R58" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P58,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Hydrating Serum Vitamin C 50ml</v>
+      </c>
+      <c r="S58" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P58,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T58" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P58,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U58" s="5">
+        <f>_xlfn.XLOOKUP(P58,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>185000</v>
+      </c>
+      <c r="V58" s="6">
+        <f>_xlfn.XLOOKUP(P58,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>85000</v>
+      </c>
+      <c r="W58" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P58,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>156</v>
       </c>
@@ -5154,7 +6929,7 @@
         <v>19</v>
       </c>
       <c r="M59" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-002</v>
       </c>
       <c r="N59" s="1" t="str">
@@ -5166,15 +6941,39 @@
         <v>8189876543</v>
       </c>
       <c r="P59" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-HOME-001</v>
       </c>
       <c r="Q59" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-REG-TRX-2024-0058-PRD-HOME-001</v>
       </c>
+      <c r="R59" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P59,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Automatic Coffee Espresso Machine</v>
+      </c>
+      <c r="S59" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P59,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T59" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P59,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchen Appliances</v>
+      </c>
+      <c r="U59" s="5">
+        <f>_xlfn.XLOOKUP(P59,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>2400000</v>
+      </c>
+      <c r="V59" s="6">
+        <f>_xlfn.XLOOKUP(P59,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1650000</v>
+      </c>
+      <c r="W59" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P59,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>4.5</v>
+      </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>158</v>
       </c>
@@ -5212,7 +7011,7 @@
         <v>19</v>
       </c>
       <c r="M60" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-010</v>
       </c>
       <c r="N60" s="1" t="str">
@@ -5224,15 +7023,39 @@
         <v>81377665544</v>
       </c>
       <c r="P60" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-001</v>
       </c>
       <c r="Q60" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-EXP-TRX-2024-0059-PRD-ELEC-001</v>
       </c>
+      <c r="R60" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P60,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Wireless Noise Cancelling Headphones</v>
+      </c>
+      <c r="S60" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P60,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T60" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P60,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Audio</v>
+      </c>
+      <c r="U60" s="5">
+        <f>_xlfn.XLOOKUP(P60,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1250000</v>
+      </c>
+      <c r="V60" s="6">
+        <f>_xlfn.XLOOKUP(P60,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="W60" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P60,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>160</v>
       </c>
@@ -5270,7 +7093,7 @@
         <v>33</v>
       </c>
       <c r="M61" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-010</v>
       </c>
       <c r="N61" s="1" t="str">
@@ -5282,15 +7105,39 @@
         <v>81377665544</v>
       </c>
       <c r="P61" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-BEAU-001</v>
       </c>
       <c r="Q61" s="1" t="str">
         <f t="shared" si="2"/>
         <v>SISEPAT-BEST-TRX-2024-0060-PRD-BEAU-001</v>
       </c>
+      <c r="R61" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P61,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Hydrating Serum Vitamin C 50ml</v>
+      </c>
+      <c r="S61" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P61,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T61" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P61,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U61" s="5">
+        <f>_xlfn.XLOOKUP(P61,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>185000</v>
+      </c>
+      <c r="V61" s="6">
+        <f>_xlfn.XLOOKUP(P61,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>85000</v>
+      </c>
+      <c r="W61" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P61,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.1</v>
+      </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>162</v>
       </c>
@@ -5328,7 +7175,7 @@
         <v>39</v>
       </c>
       <c r="M62" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-007</v>
       </c>
       <c r="N62" s="1" t="str">
@@ -5340,15 +7187,39 @@
         <v>8170099887</v>
       </c>
       <c r="P62" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>PRD-BEAU-002-v1</v>
+        <f t="shared" si="1"/>
+        <v>PRD-BEAU-002</v>
       </c>
       <c r="Q62" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>SISEPAT-GOKIL-TRX-2024-0061-PRD-BEAU-002-v1</v>
+        <v>SISEPAT-GOKIL-TRX-2024-0061-PRD-BEAU-002</v>
+      </c>
+      <c r="R62" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P62,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Organic Sunscreen SPF 50 PA++++</v>
+      </c>
+      <c r="S62" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P62,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T62" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P62,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U62" s="5">
+        <f>_xlfn.XLOOKUP(P62,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>145000</v>
+      </c>
+      <c r="V62" s="6">
+        <f>_xlfn.XLOOKUP(P62,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>65000</v>
+      </c>
+      <c r="W62" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P62,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.12</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>163</v>
       </c>
@@ -5386,7 +7257,7 @@
         <v>33</v>
       </c>
       <c r="M63" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-005</v>
       </c>
       <c r="N63" s="1" t="str">
@@ -5398,15 +7269,39 @@
         <v>8189876543</v>
       </c>
       <c r="P63" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-HOME-001</v>
       </c>
       <c r="Q63" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-REG-TRX-2024-0062-PRD-HOME-001</v>
       </c>
+      <c r="R63" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P63,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Automatic Coffee Espresso Machine</v>
+      </c>
+      <c r="S63" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P63,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T63" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P63,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchen Appliances</v>
+      </c>
+      <c r="U63" s="5">
+        <f>_xlfn.XLOOKUP(P63,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>2400000</v>
+      </c>
+      <c r="V63" s="6">
+        <f>_xlfn.XLOOKUP(P63,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1650000</v>
+      </c>
+      <c r="W63" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P63,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>4.5</v>
+      </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>165</v>
       </c>
@@ -5444,7 +7339,7 @@
         <v>43</v>
       </c>
       <c r="M64" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-008</v>
       </c>
       <c r="N64" s="1" t="str">
@@ -5456,15 +7351,39 @@
         <v>85211447788</v>
       </c>
       <c r="P64" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-ELEC-004</v>
       </c>
       <c r="Q64" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNE-YES-TRX-2024-0063-PRD-ELEC-004</v>
       </c>
+      <c r="R64" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P64,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ergonomic Wireless Mouse</v>
+      </c>
+      <c r="S64" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P64,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T64" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P64,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U64" s="5">
+        <f>_xlfn.XLOOKUP(P64,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>350000</v>
+      </c>
+      <c r="V64" s="6">
+        <f>_xlfn.XLOOKUP(P64,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>200000</v>
+      </c>
+      <c r="W64" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P64,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.25</v>
+      </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>166</v>
       </c>
@@ -5502,7 +7421,7 @@
         <v>19</v>
       </c>
       <c r="M65" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N65" s="1" t="str">
@@ -5514,15 +7433,39 @@
         <v>87855443322</v>
       </c>
       <c r="P65" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PRD-FASH-001</v>
       </c>
       <c r="Q65" s="1" t="str">
         <f t="shared" si="2"/>
         <v>SISEPAT-BEST-TRX-2024-0064-PRD-FASH-001</v>
       </c>
+      <c r="R65" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P65,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Men Denim Jacket Vintage Blue</v>
+      </c>
+      <c r="S65" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P65,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T65" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P65,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Outerwear</v>
+      </c>
+      <c r="U65" s="5">
+        <f>_xlfn.XLOOKUP(P65,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>450000</v>
+      </c>
+      <c r="V65" s="6">
+        <f>_xlfn.XLOOKUP(P65,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>260000</v>
+      </c>
+      <c r="W65" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P65,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.9</v>
+      </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>168</v>
       </c>
@@ -5560,7 +7503,7 @@
         <v>39</v>
       </c>
       <c r="M66" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>CUST-004</v>
       </c>
       <c r="N66" s="1" t="str">
@@ -5572,15 +7515,39 @@
         <v>87855443322</v>
       </c>
       <c r="P66" s="1" t="str">
-        <f t="shared" ref="P66:P101" si="4">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D66,"NEW-",""),"OLD_",""),"PROD_","")</f>
+        <f t="shared" si="1"/>
         <v>PRD-HOME-003</v>
       </c>
       <c r="Q66" s="1" t="str">
         <f t="shared" si="2"/>
         <v>JNT-EXP-TRX-2024-0065-PRD-HOME-003</v>
       </c>
+      <c r="R66" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P66,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Stainless Steel Cookware Set 5pcs</v>
+      </c>
+      <c r="S66" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P66,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T66" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P66,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchenware</v>
+      </c>
+      <c r="U66" s="5">
+        <f>_xlfn.XLOOKUP(P66,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>880000</v>
+      </c>
+      <c r="V66" s="6">
+        <f>_xlfn.XLOOKUP(P66,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>540000</v>
+      </c>
+      <c r="W66" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P66,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>169</v>
       </c>
@@ -5618,7 +7585,7 @@
         <v>39</v>
       </c>
       <c r="M67" s="1" t="str">
-        <f t="shared" ref="M67:M101" si="5">TRIM(C67)</f>
+        <f t="shared" ref="M67:M101" si="3">TRIM(C67)</f>
         <v>CUST-004</v>
       </c>
       <c r="N67" s="1" t="str">
@@ -5630,15 +7597,39 @@
         <v>87855443322</v>
       </c>
       <c r="P67" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>PRD-FASH-002-2024</v>
+        <f t="shared" ref="P67:P101" si="4">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D67,"NEW-",""),"OLD_",""),"PROD_",""),"-2024",""),"-v1","")</f>
+        <v>PRD-FASH-002</v>
       </c>
       <c r="Q67" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>JNE-REG-TRX-2024-0066-PRD-FASH-002-2024</v>
+        <v>JNE-REG-TRX-2024-0066-PRD-FASH-002</v>
+      </c>
+      <c r="R67" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P67,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Women Floral Summer Dress</v>
+      </c>
+      <c r="S67" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P67,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T67" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P67,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Dresses</v>
+      </c>
+      <c r="U67" s="5">
+        <f>_xlfn.XLOOKUP(P67,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>320000</v>
+      </c>
+      <c r="V67" s="6">
+        <f>_xlfn.XLOOKUP(P67,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>180000</v>
+      </c>
+      <c r="W67" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P67,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.35</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>171</v>
       </c>
@@ -5676,7 +7667,7 @@
         <v>27</v>
       </c>
       <c r="M68" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-006</v>
       </c>
       <c r="N68" s="1" t="str">
@@ -5692,11 +7683,35 @@
         <v>PRD-HOME-003</v>
       </c>
       <c r="Q68" s="1" t="str">
-        <f t="shared" ref="Q68:Q101" si="6">_xlfn.CONCAT(G68,"-",A68,"-",P68)</f>
+        <f t="shared" ref="Q68:Q101" si="5">_xlfn.CONCAT(G68,"-",A68,"-",P68)</f>
         <v>JNT-EXP-TRX-2024-0067-PRD-HOME-003</v>
       </c>
+      <c r="R68" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P68,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Stainless Steel Cookware Set 5pcs</v>
+      </c>
+      <c r="S68" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P68,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T68" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P68,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchenware</v>
+      </c>
+      <c r="U68" s="5">
+        <f>_xlfn.XLOOKUP(P68,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>880000</v>
+      </c>
+      <c r="V68" s="6">
+        <f>_xlfn.XLOOKUP(P68,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>540000</v>
+      </c>
+      <c r="W68" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P68,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>172</v>
       </c>
@@ -5734,7 +7749,7 @@
         <v>19</v>
       </c>
       <c r="M69" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-003</v>
       </c>
       <c r="N69" s="1" t="str">
@@ -5750,11 +7765,35 @@
         <v>PRD-ELEC-004</v>
       </c>
       <c r="Q69" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNT-EXP-TRX-2024-0068-PRD-ELEC-004</v>
       </c>
+      <c r="R69" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P69,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ergonomic Wireless Mouse</v>
+      </c>
+      <c r="S69" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P69,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T69" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P69,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U69" s="5">
+        <f>_xlfn.XLOOKUP(P69,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>350000</v>
+      </c>
+      <c r="V69" s="6">
+        <f>_xlfn.XLOOKUP(P69,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>200000</v>
+      </c>
+      <c r="W69" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P69,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.25</v>
+      </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>174</v>
       </c>
@@ -5792,7 +7831,7 @@
         <v>33</v>
       </c>
       <c r="M70" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-004</v>
       </c>
       <c r="N70" s="1" t="str">
@@ -5808,11 +7847,35 @@
         <v>PRD-FASH-001</v>
       </c>
       <c r="Q70" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNT-EXP-TRX-2024-0069-PRD-FASH-001</v>
       </c>
+      <c r="R70" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P70,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Men Denim Jacket Vintage Blue</v>
+      </c>
+      <c r="S70" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P70,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T70" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P70,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Outerwear</v>
+      </c>
+      <c r="U70" s="5">
+        <f>_xlfn.XLOOKUP(P70,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>450000</v>
+      </c>
+      <c r="V70" s="6">
+        <f>_xlfn.XLOOKUP(P70,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>260000</v>
+      </c>
+      <c r="W70" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P70,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.9</v>
+      </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>176</v>
       </c>
@@ -5850,7 +7913,7 @@
         <v>33</v>
       </c>
       <c r="M71" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-003</v>
       </c>
       <c r="N71" s="1" t="str">
@@ -5866,11 +7929,35 @@
         <v>PRD-HOME-002</v>
       </c>
       <c r="Q71" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNE-REG-TRX-2024-0070-PRD-HOME-002</v>
       </c>
+      <c r="R71" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P71,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Air Purifier HEPA Filter H13</v>
+      </c>
+      <c r="S71" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P71,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T71" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P71,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Home Appliances</v>
+      </c>
+      <c r="U71" s="5">
+        <f>_xlfn.XLOOKUP(P71,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1750000</v>
+      </c>
+      <c r="V71" s="6">
+        <f>_xlfn.XLOOKUP(P71,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1150000</v>
+      </c>
+      <c r="W71" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P71,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.2</v>
+      </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>178</v>
       </c>
@@ -5908,7 +7995,7 @@
         <v>39</v>
       </c>
       <c r="M72" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-003</v>
       </c>
       <c r="N72" s="1" t="str">
@@ -5924,11 +8011,35 @@
         <v>PRD-ELEC-001</v>
       </c>
       <c r="Q72" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>SISEPAT-BEST-TRX-2024-0071-PRD-ELEC-001</v>
       </c>
+      <c r="R72" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P72,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Wireless Noise Cancelling Headphones</v>
+      </c>
+      <c r="S72" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P72,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T72" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P72,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Audio</v>
+      </c>
+      <c r="U72" s="5">
+        <f>_xlfn.XLOOKUP(P72,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1250000</v>
+      </c>
+      <c r="V72" s="6">
+        <f>_xlfn.XLOOKUP(P72,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="W72" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P72,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>179</v>
       </c>
@@ -5966,7 +8077,7 @@
         <v>39</v>
       </c>
       <c r="M73" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-003</v>
       </c>
       <c r="N73" s="1" t="str">
@@ -5982,11 +8093,35 @@
         <v>PRD-BEAU-001</v>
       </c>
       <c r="Q73" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>SISEPAT-BEST-TRX-2024-0072-PRD-BEAU-001</v>
       </c>
+      <c r="R73" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P73,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Hydrating Serum Vitamin C 50ml</v>
+      </c>
+      <c r="S73" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P73,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T73" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P73,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U73" s="5">
+        <f>_xlfn.XLOOKUP(P73,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>185000</v>
+      </c>
+      <c r="V73" s="6">
+        <f>_xlfn.XLOOKUP(P73,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>85000</v>
+      </c>
+      <c r="W73" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P73,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.1</v>
+      </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>180</v>
       </c>
@@ -6024,7 +8159,7 @@
         <v>43</v>
       </c>
       <c r="M74" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-008</v>
       </c>
       <c r="N74" s="1" t="str">
@@ -6040,11 +8175,35 @@
         <v>PRD-ELEC-005</v>
       </c>
       <c r="Q74" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNT-REG-TRX-2024-0073-PRD-ELEC-005</v>
       </c>
+      <c r="R74" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P74,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ultra HD Webcam 4K Pro</v>
+      </c>
+      <c r="S74" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P74,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T74" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P74,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U74" s="5">
+        <f>_xlfn.XLOOKUP(P74,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1100000</v>
+      </c>
+      <c r="V74" s="6">
+        <f>_xlfn.XLOOKUP(P74,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>720000</v>
+      </c>
+      <c r="W74" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P74,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.4</v>
+      </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>182</v>
       </c>
@@ -6082,7 +8241,7 @@
         <v>39</v>
       </c>
       <c r="M75" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-002</v>
       </c>
       <c r="N75" s="1" t="str">
@@ -6095,14 +8254,38 @@
       </c>
       <c r="P75" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>PRD-ELEC-003-2024</v>
+        <v>PRD-ELEC-003</v>
       </c>
       <c r="Q75" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>SISEPAT-GOKIL-TRX-2024-0074-PRD-ELEC-003-2024</v>
+        <f t="shared" si="5"/>
+        <v>SISEPAT-GOKIL-TRX-2024-0074-PRD-ELEC-003</v>
+      </c>
+      <c r="R75" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P75,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Mechanical Gaming Keyboard RGB</v>
+      </c>
+      <c r="S75" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P75,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T75" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P75,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U75" s="5">
+        <f>_xlfn.XLOOKUP(P75,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>950000</v>
+      </c>
+      <c r="V75" s="6">
+        <f>_xlfn.XLOOKUP(P75,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>600000</v>
+      </c>
+      <c r="W75" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P75,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>1.2</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>184</v>
       </c>
@@ -6140,7 +8323,7 @@
         <v>27</v>
       </c>
       <c r="M76" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-005</v>
       </c>
       <c r="N76" s="1" t="str">
@@ -6156,11 +8339,35 @@
         <v>PRD-ELEC-001</v>
       </c>
       <c r="Q76" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>SISEPAT-GOKIL-TRX-2024-0075-PRD-ELEC-001</v>
       </c>
+      <c r="R76" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P76,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Wireless Noise Cancelling Headphones</v>
+      </c>
+      <c r="S76" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P76,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T76" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P76,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Audio</v>
+      </c>
+      <c r="U76" s="5">
+        <f>_xlfn.XLOOKUP(P76,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1250000</v>
+      </c>
+      <c r="V76" s="6">
+        <f>_xlfn.XLOOKUP(P76,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="W76" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P76,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>186</v>
       </c>
@@ -6198,7 +8405,7 @@
         <v>27</v>
       </c>
       <c r="M77" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-004</v>
       </c>
       <c r="N77" s="1" t="str">
@@ -6214,11 +8421,35 @@
         <v>PRD-FASH-002</v>
       </c>
       <c r="Q77" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNT-EXP-TRX-2024-0076-PRD-FASH-002</v>
       </c>
+      <c r="R77" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P77,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Women Floral Summer Dress</v>
+      </c>
+      <c r="S77" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P77,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T77" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P77,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Dresses</v>
+      </c>
+      <c r="U77" s="5">
+        <f>_xlfn.XLOOKUP(P77,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>320000</v>
+      </c>
+      <c r="V77" s="6">
+        <f>_xlfn.XLOOKUP(P77,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>180000</v>
+      </c>
+      <c r="W77" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P77,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.35</v>
+      </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>187</v>
       </c>
@@ -6256,7 +8487,7 @@
         <v>33</v>
       </c>
       <c r="M78" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-005</v>
       </c>
       <c r="N78" s="1" t="str">
@@ -6272,11 +8503,35 @@
         <v>PRD-HOME-001</v>
       </c>
       <c r="Q78" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNE-YES-TRX-2024-0077-PRD-HOME-001</v>
       </c>
+      <c r="R78" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P78,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Automatic Coffee Espresso Machine</v>
+      </c>
+      <c r="S78" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P78,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T78" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P78,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchen Appliances</v>
+      </c>
+      <c r="U78" s="5">
+        <f>_xlfn.XLOOKUP(P78,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>2400000</v>
+      </c>
+      <c r="V78" s="6">
+        <f>_xlfn.XLOOKUP(P78,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1650000</v>
+      </c>
+      <c r="W78" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P78,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>4.5</v>
+      </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>188</v>
       </c>
@@ -6314,7 +8569,7 @@
         <v>33</v>
       </c>
       <c r="M79" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-008</v>
       </c>
       <c r="N79" s="1" t="str">
@@ -6330,11 +8585,35 @@
         <v>PRD-FASH-003</v>
       </c>
       <c r="Q79" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNT-EXP-TRX-2024-0078-PRD-FASH-003</v>
       </c>
+      <c r="R79" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P79,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Unisex Canvas Sneakers White</v>
+      </c>
+      <c r="S79" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P79,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T79" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P79,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Footwear</v>
+      </c>
+      <c r="U79" s="5">
+        <f>_xlfn.XLOOKUP(P79,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>520000</v>
+      </c>
+      <c r="V79" s="6">
+        <f>_xlfn.XLOOKUP(P79,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>310000</v>
+      </c>
+      <c r="W79" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P79,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>1.1</v>
+      </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>190</v>
       </c>
@@ -6372,7 +8651,7 @@
         <v>39</v>
       </c>
       <c r="M80" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-010</v>
       </c>
       <c r="N80" s="1" t="str">
@@ -6388,11 +8667,35 @@
         <v>PRD-HOME-001</v>
       </c>
       <c r="Q80" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNE-YES-TRX-2024-0079-PRD-HOME-001</v>
       </c>
+      <c r="R80" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P80,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Automatic Coffee Espresso Machine</v>
+      </c>
+      <c r="S80" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P80,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T80" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P80,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchen Appliances</v>
+      </c>
+      <c r="U80" s="5">
+        <f>_xlfn.XLOOKUP(P80,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>2400000</v>
+      </c>
+      <c r="V80" s="6">
+        <f>_xlfn.XLOOKUP(P80,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1650000</v>
+      </c>
+      <c r="W80" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P80,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>4.5</v>
+      </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>192</v>
       </c>
@@ -6430,7 +8733,7 @@
         <v>33</v>
       </c>
       <c r="M81" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-007</v>
       </c>
       <c r="N81" s="1" t="str">
@@ -6446,11 +8749,35 @@
         <v>PRD-HOME-002</v>
       </c>
       <c r="Q81" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>SISEPAT-GOKIL-TRX-2024-0080-PRD-HOME-002</v>
       </c>
+      <c r="R81" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P81,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Air Purifier HEPA Filter H13</v>
+      </c>
+      <c r="S81" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P81,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T81" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P81,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Home Appliances</v>
+      </c>
+      <c r="U81" s="5">
+        <f>_xlfn.XLOOKUP(P81,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1750000</v>
+      </c>
+      <c r="V81" s="6">
+        <f>_xlfn.XLOOKUP(P81,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1150000</v>
+      </c>
+      <c r="W81" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P81,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.2</v>
+      </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>193</v>
       </c>
@@ -6488,7 +8815,7 @@
         <v>43</v>
       </c>
       <c r="M82" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-003</v>
       </c>
       <c r="N82" s="1" t="str">
@@ -6504,11 +8831,35 @@
         <v>PRD-FASH-001</v>
       </c>
       <c r="Q82" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNT-EXP-TRX-2024-0081-PRD-FASH-001</v>
       </c>
+      <c r="R82" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P82,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Men Denim Jacket Vintage Blue</v>
+      </c>
+      <c r="S82" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P82,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T82" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P82,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Outerwear</v>
+      </c>
+      <c r="U82" s="5">
+        <f>_xlfn.XLOOKUP(P82,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>450000</v>
+      </c>
+      <c r="V82" s="6">
+        <f>_xlfn.XLOOKUP(P82,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>260000</v>
+      </c>
+      <c r="W82" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P82,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.9</v>
+      </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>194</v>
       </c>
@@ -6546,7 +8897,7 @@
         <v>39</v>
       </c>
       <c r="M83" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-006</v>
       </c>
       <c r="N83" s="1" t="str">
@@ -6562,11 +8913,35 @@
         <v>PRD-ELEC-002</v>
       </c>
       <c r="Q83" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNT-EXP-TRX-2024-0082-PRD-ELEC-002</v>
       </c>
+      <c r="R83" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P83,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Smart Watch Fitness Tracker V2</v>
+      </c>
+      <c r="S83" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P83,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T83" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P83,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Wearables</v>
+      </c>
+      <c r="U83" s="5">
+        <f>_xlfn.XLOOKUP(P83,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="V83" s="6">
+        <f>_xlfn.XLOOKUP(P83,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>520000</v>
+      </c>
+      <c r="W83" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P83,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.3</v>
+      </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>195</v>
       </c>
@@ -6604,7 +8979,7 @@
         <v>33</v>
       </c>
       <c r="M84" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-006</v>
       </c>
       <c r="N84" s="1" t="str">
@@ -6620,11 +8995,35 @@
         <v>PRD-HOME-001</v>
       </c>
       <c r="Q84" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNE-YES-TRX-2024-0083-PRD-HOME-001</v>
       </c>
+      <c r="R84" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P84,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Automatic Coffee Espresso Machine</v>
+      </c>
+      <c r="S84" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P84,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T84" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P84,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchen Appliances</v>
+      </c>
+      <c r="U84" s="5">
+        <f>_xlfn.XLOOKUP(P84,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>2400000</v>
+      </c>
+      <c r="V84" s="6">
+        <f>_xlfn.XLOOKUP(P84,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1650000</v>
+      </c>
+      <c r="W84" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P84,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>4.5</v>
+      </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>196</v>
       </c>
@@ -6662,7 +9061,7 @@
         <v>33</v>
       </c>
       <c r="M85" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-008</v>
       </c>
       <c r="N85" s="1" t="str">
@@ -6678,11 +9077,35 @@
         <v>PRD-ELEC-002</v>
       </c>
       <c r="Q85" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>SISEPAT-BEST-TRX-2024-0084-PRD-ELEC-002</v>
       </c>
+      <c r="R85" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P85,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Smart Watch Fitness Tracker V2</v>
+      </c>
+      <c r="S85" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P85,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T85" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P85,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Wearables</v>
+      </c>
+      <c r="U85" s="5">
+        <f>_xlfn.XLOOKUP(P85,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="V85" s="6">
+        <f>_xlfn.XLOOKUP(P85,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>520000</v>
+      </c>
+      <c r="W85" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P85,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.3</v>
+      </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>199</v>
       </c>
@@ -6720,7 +9143,7 @@
         <v>33</v>
       </c>
       <c r="M86" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-004</v>
       </c>
       <c r="N86" s="1" t="str">
@@ -6736,11 +9159,35 @@
         <v>PRD-BEAU-002</v>
       </c>
       <c r="Q86" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNE-REG-TRX-2024-0085-PRD-BEAU-002</v>
       </c>
+      <c r="R86" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P86,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Organic Sunscreen SPF 50 PA++++</v>
+      </c>
+      <c r="S86" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P86,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T86" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P86,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U86" s="5">
+        <f>_xlfn.XLOOKUP(P86,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>145000</v>
+      </c>
+      <c r="V86" s="6">
+        <f>_xlfn.XLOOKUP(P86,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>65000</v>
+      </c>
+      <c r="W86" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P86,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.12</v>
+      </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>200</v>
       </c>
@@ -6778,7 +9225,7 @@
         <v>27</v>
       </c>
       <c r="M87" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-004</v>
       </c>
       <c r="N87" s="1" t="str">
@@ -6791,14 +9238,38 @@
       </c>
       <c r="P87" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>PRD-FASH-003-2024</v>
+        <v>PRD-FASH-003</v>
       </c>
       <c r="Q87" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>JNE-YES-TRX-2024-0086-PRD-FASH-003-2024</v>
+        <f t="shared" si="5"/>
+        <v>JNE-YES-TRX-2024-0086-PRD-FASH-003</v>
+      </c>
+      <c r="R87" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P87,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Unisex Canvas Sneakers White</v>
+      </c>
+      <c r="S87" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P87,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T87" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P87,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Footwear</v>
+      </c>
+      <c r="U87" s="5">
+        <f>_xlfn.XLOOKUP(P87,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>520000</v>
+      </c>
+      <c r="V87" s="6">
+        <f>_xlfn.XLOOKUP(P87,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>310000</v>
+      </c>
+      <c r="W87" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P87,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>1.1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>202</v>
       </c>
@@ -6836,7 +9307,7 @@
         <v>19</v>
       </c>
       <c r="M88" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-009</v>
       </c>
       <c r="N88" s="1" t="str">
@@ -6849,14 +9320,38 @@
       </c>
       <c r="P88" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>PRD-ELEC-005-v1</v>
+        <v>PRD-ELEC-005</v>
       </c>
       <c r="Q88" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>JNT-REG-TRX-2024-0087-PRD-ELEC-005-v1</v>
+        <f t="shared" si="5"/>
+        <v>JNT-REG-TRX-2024-0087-PRD-ELEC-005</v>
+      </c>
+      <c r="R88" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P88,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Ultra HD Webcam 4K Pro</v>
+      </c>
+      <c r="S88" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P88,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T88" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P88,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U88" s="5">
+        <f>_xlfn.XLOOKUP(P88,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1100000</v>
+      </c>
+      <c r="V88" s="6">
+        <f>_xlfn.XLOOKUP(P88,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>720000</v>
+      </c>
+      <c r="W88" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P88,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.4</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>203</v>
       </c>
@@ -6894,7 +9389,7 @@
         <v>27</v>
       </c>
       <c r="M89" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-008</v>
       </c>
       <c r="N89" s="1" t="str">
@@ -6910,11 +9405,35 @@
         <v>PRD-FASH-001</v>
       </c>
       <c r="Q89" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>SISEPAT-BEST-TRX-2024-0088-PRD-FASH-001</v>
       </c>
+      <c r="R89" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P89,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Men Denim Jacket Vintage Blue</v>
+      </c>
+      <c r="S89" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P89,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T89" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P89,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Outerwear</v>
+      </c>
+      <c r="U89" s="5">
+        <f>_xlfn.XLOOKUP(P89,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>450000</v>
+      </c>
+      <c r="V89" s="6">
+        <f>_xlfn.XLOOKUP(P89,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>260000</v>
+      </c>
+      <c r="W89" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P89,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.9</v>
+      </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>205</v>
       </c>
@@ -6952,7 +9471,7 @@
         <v>27</v>
       </c>
       <c r="M90" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-007</v>
       </c>
       <c r="N90" s="1" t="str">
@@ -6968,11 +9487,35 @@
         <v>PRD-ELEC-001</v>
       </c>
       <c r="Q90" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNT-EXP-TRX-2024-0089-PRD-ELEC-001</v>
       </c>
+      <c r="R90" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P90,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Wireless Noise Cancelling Headphones</v>
+      </c>
+      <c r="S90" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P90,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T90" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P90,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Audio</v>
+      </c>
+      <c r="U90" s="5">
+        <f>_xlfn.XLOOKUP(P90,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1250000</v>
+      </c>
+      <c r="V90" s="6">
+        <f>_xlfn.XLOOKUP(P90,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="W90" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P90,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>206</v>
       </c>
@@ -7010,7 +9553,7 @@
         <v>43</v>
       </c>
       <c r="M91" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-010</v>
       </c>
       <c r="N91" s="1" t="str">
@@ -7023,14 +9566,38 @@
       </c>
       <c r="P91" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>PRD-FASH-001-v1</v>
+        <v>PRD-FASH-001</v>
       </c>
       <c r="Q91" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>JNE-REG-TRX-2024-0090-PRD-FASH-001-v1</v>
+        <f t="shared" si="5"/>
+        <v>JNE-REG-TRX-2024-0090-PRD-FASH-001</v>
+      </c>
+      <c r="R91" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P91,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Men Denim Jacket Vintage Blue</v>
+      </c>
+      <c r="S91" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P91,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T91" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P91,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Outerwear</v>
+      </c>
+      <c r="U91" s="5">
+        <f>_xlfn.XLOOKUP(P91,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>450000</v>
+      </c>
+      <c r="V91" s="6">
+        <f>_xlfn.XLOOKUP(P91,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>260000</v>
+      </c>
+      <c r="W91" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P91,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.9</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>207</v>
       </c>
@@ -7068,7 +9635,7 @@
         <v>33</v>
       </c>
       <c r="M92" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-008</v>
       </c>
       <c r="N92" s="1" t="str">
@@ -7084,11 +9651,35 @@
         <v>PRD-BEAU-001</v>
       </c>
       <c r="Q92" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNE-YES-TRX-2024-0091-PRD-BEAU-001</v>
       </c>
+      <c r="R92" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P92,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Hydrating Serum Vitamin C 50ml</v>
+      </c>
+      <c r="S92" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P92,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Beauty &amp; Health</v>
+      </c>
+      <c r="T92" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P92,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Skincare</v>
+      </c>
+      <c r="U92" s="5">
+        <f>_xlfn.XLOOKUP(P92,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>185000</v>
+      </c>
+      <c r="V92" s="6">
+        <f>_xlfn.XLOOKUP(P92,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>85000</v>
+      </c>
+      <c r="W92" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P92,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.1</v>
+      </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>209</v>
       </c>
@@ -7126,7 +9717,7 @@
         <v>43</v>
       </c>
       <c r="M93" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-009</v>
       </c>
       <c r="N93" s="1" t="str">
@@ -7139,14 +9730,38 @@
       </c>
       <c r="P93" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>PRD-ELEC-001-v1</v>
+        <v>PRD-ELEC-001</v>
       </c>
       <c r="Q93" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>JNT-EXP-TRX-2024-0092-PRD-ELEC-001-v1</v>
+        <f t="shared" si="5"/>
+        <v>JNT-EXP-TRX-2024-0092-PRD-ELEC-001</v>
+      </c>
+      <c r="R93" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P93,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Wireless Noise Cancelling Headphones</v>
+      </c>
+      <c r="S93" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P93,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T93" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P93,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Audio</v>
+      </c>
+      <c r="U93" s="5">
+        <f>_xlfn.XLOOKUP(P93,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1250000</v>
+      </c>
+      <c r="V93" s="6">
+        <f>_xlfn.XLOOKUP(P93,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="W93" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P93,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.8</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>211</v>
       </c>
@@ -7184,7 +9799,7 @@
         <v>33</v>
       </c>
       <c r="M94" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-003</v>
       </c>
       <c r="N94" s="1" t="str">
@@ -7197,14 +9812,38 @@
       </c>
       <c r="P94" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>PRD-HOME-003-v1</v>
+        <v>PRD-HOME-003</v>
       </c>
       <c r="Q94" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>JNE-REG-TRX-2024-0093-PRD-HOME-003-v1</v>
+        <f t="shared" si="5"/>
+        <v>JNE-REG-TRX-2024-0093-PRD-HOME-003</v>
+      </c>
+      <c r="R94" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P94,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Stainless Steel Cookware Set 5pcs</v>
+      </c>
+      <c r="S94" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P94,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T94" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P94,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchenware</v>
+      </c>
+      <c r="U94" s="5">
+        <f>_xlfn.XLOOKUP(P94,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>880000</v>
+      </c>
+      <c r="V94" s="6">
+        <f>_xlfn.XLOOKUP(P94,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>540000</v>
+      </c>
+      <c r="W94" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P94,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.8</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>213</v>
       </c>
@@ -7242,7 +9881,7 @@
         <v>19</v>
       </c>
       <c r="M95" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-009</v>
       </c>
       <c r="N95" s="1" t="str">
@@ -7258,11 +9897,35 @@
         <v>PRD-FASH-002</v>
       </c>
       <c r="Q95" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>SISEPAT-BEST-TRX-2024-0094-PRD-FASH-002</v>
       </c>
+      <c r="R95" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P95,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Women Floral Summer Dress</v>
+      </c>
+      <c r="S95" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P95,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T95" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P95,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Dresses</v>
+      </c>
+      <c r="U95" s="5">
+        <f>_xlfn.XLOOKUP(P95,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>320000</v>
+      </c>
+      <c r="V95" s="6">
+        <f>_xlfn.XLOOKUP(P95,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>180000</v>
+      </c>
+      <c r="W95" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P95,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.35</v>
+      </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>214</v>
       </c>
@@ -7300,7 +9963,7 @@
         <v>39</v>
       </c>
       <c r="M96" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-010</v>
       </c>
       <c r="N96" s="1" t="str">
@@ -7316,11 +9979,35 @@
         <v>PRD-ELEC-003</v>
       </c>
       <c r="Q96" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>SISEPAT-GOKIL-TRX-2024-0095-PRD-ELEC-003</v>
       </c>
+      <c r="R96" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P96,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Mechanical Gaming Keyboard RGB</v>
+      </c>
+      <c r="S96" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P96,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T96" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P96,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Computer Accessories</v>
+      </c>
+      <c r="U96" s="5">
+        <f>_xlfn.XLOOKUP(P96,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>950000</v>
+      </c>
+      <c r="V96" s="6">
+        <f>_xlfn.XLOOKUP(P96,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>600000</v>
+      </c>
+      <c r="W96" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P96,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>215</v>
       </c>
@@ -7358,7 +10045,7 @@
         <v>39</v>
       </c>
       <c r="M97" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-002</v>
       </c>
       <c r="N97" s="1" t="str">
@@ -7374,11 +10061,35 @@
         <v>PRD-FASH-003</v>
       </c>
       <c r="Q97" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNT-REG-TRX-2024-0096-PRD-FASH-003</v>
       </c>
+      <c r="R97" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P97,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Unisex Canvas Sneakers White</v>
+      </c>
+      <c r="S97" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P97,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Fashion</v>
+      </c>
+      <c r="T97" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P97,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Footwear</v>
+      </c>
+      <c r="U97" s="5">
+        <f>_xlfn.XLOOKUP(P97,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>520000</v>
+      </c>
+      <c r="V97" s="6">
+        <f>_xlfn.XLOOKUP(P97,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>310000</v>
+      </c>
+      <c r="W97" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P97,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>1.1</v>
+      </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>217</v>
       </c>
@@ -7416,7 +10127,7 @@
         <v>33</v>
       </c>
       <c r="M98" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-008</v>
       </c>
       <c r="N98" s="1" t="str">
@@ -7432,11 +10143,35 @@
         <v>PRD-ELEC-002</v>
       </c>
       <c r="Q98" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>SISEPAT-GOKIL-TRX-2024-0097-PRD-ELEC-002</v>
       </c>
+      <c r="R98" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P98,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Smart Watch Fitness Tracker V2</v>
+      </c>
+      <c r="S98" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P98,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T98" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P98,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Wearables</v>
+      </c>
+      <c r="U98" s="5">
+        <f>_xlfn.XLOOKUP(P98,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="V98" s="6">
+        <f>_xlfn.XLOOKUP(P98,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>520000</v>
+      </c>
+      <c r="W98" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P98,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.3</v>
+      </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>219</v>
       </c>
@@ -7474,7 +10209,7 @@
         <v>27</v>
       </c>
       <c r="M99" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-001</v>
       </c>
       <c r="N99" s="1" t="str">
@@ -7490,11 +10225,35 @@
         <v>PRD-HOME-001</v>
       </c>
       <c r="Q99" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNT-REG-TRX-2024-0098-PRD-HOME-001</v>
       </c>
+      <c r="R99" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P99,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Automatic Coffee Espresso Machine</v>
+      </c>
+      <c r="S99" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P99,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T99" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P99,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Kitchen Appliances</v>
+      </c>
+      <c r="U99" s="5">
+        <f>_xlfn.XLOOKUP(P99,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>2400000</v>
+      </c>
+      <c r="V99" s="6">
+        <f>_xlfn.XLOOKUP(P99,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1650000</v>
+      </c>
+      <c r="W99" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P99,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>4.5</v>
+      </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>220</v>
       </c>
@@ -7532,7 +10291,7 @@
         <v>33</v>
       </c>
       <c r="M100" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-005</v>
       </c>
       <c r="N100" s="1" t="str">
@@ -7548,11 +10307,35 @@
         <v>PRD-HOME-002</v>
       </c>
       <c r="Q100" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JNT-EXP-TRX-2024-0099-PRD-HOME-002</v>
       </c>
+      <c r="R100" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P100,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Air Purifier HEPA Filter H13</v>
+      </c>
+      <c r="S100" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P100,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Home &amp; Living</v>
+      </c>
+      <c r="T100" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P100,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Home Appliances</v>
+      </c>
+      <c r="U100" s="5">
+        <f>_xlfn.XLOOKUP(P100,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>1750000</v>
+      </c>
+      <c r="V100" s="6">
+        <f>_xlfn.XLOOKUP(P100,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>1150000</v>
+      </c>
+      <c r="W100" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P100,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>3.2</v>
+      </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>221</v>
       </c>
@@ -7590,7 +10373,7 @@
         <v>19</v>
       </c>
       <c r="M101" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>CUST-003</v>
       </c>
       <c r="N101" s="1" t="str">
@@ -7606,8 +10389,32 @@
         <v>PRD-ELEC-002</v>
       </c>
       <c r="Q101" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>SISEPAT-BEST-TRX-2024-0100-PRD-ELEC-002</v>
+      </c>
+      <c r="R101" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P101,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$B$2:$B$16,"",3,1)</f>
+        <v>Smart Watch Fitness Tracker V2</v>
+      </c>
+      <c r="S101" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P101,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$C$2:$C$16,"Nothing")</f>
+        <v>Electronics</v>
+      </c>
+      <c r="T101" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P101,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$D$2:$D$16,"Nothing")</f>
+        <v>Wearables</v>
+      </c>
+      <c r="U101" s="5">
+        <f>_xlfn.XLOOKUP(P101,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$E$2:$E$16,"Nothing")</f>
+        <v>850000</v>
+      </c>
+      <c r="V101" s="6">
+        <f>_xlfn.XLOOKUP(P101,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$F$2:$F$16,"Nothing")</f>
+        <v>520000</v>
+      </c>
+      <c r="W101" s="1" t="str">
+        <f>_xlfn.XLOOKUP(P101,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/Excel/advanced_assessment_project/Raw_Transactions_2024_finish.xlsx
+++ b/Exam/Excel/advanced_assessment_project/Raw_Transactions_2024_finish.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\Project\Data-Analyst\Exam\Excel\advanced_assessment_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDCA227-7C3A-4975-B1E0-40A6CF023DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A8E13B-F97A-4E0D-B2F6-BDDED7910EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{56521A79-FDF7-45C8-BAA3-ABC64B3F8849}"/>
   </bookViews>
@@ -18,6 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="241">
   <si>
     <t>Trx_ID</t>
   </si>
@@ -739,13 +762,35 @@
   </si>
   <si>
     <t>Weight_KG</t>
+  </si>
+  <si>
+    <t>Customer_Region</t>
+  </si>
+  <si>
+    <t>Membership_Tier</t>
+  </si>
+  <si>
+    <t>Courier_Name</t>
+  </si>
+  <si>
+    <t>Service_Type</t>
+  </si>
+  <si>
+    <t>SLA_Days</t>
+  </si>
+  <si>
+    <t>Base_Rate_Per_KG</t>
+  </si>
+  <si>
+    <t>Sales_Commission_Rate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.E+00"/>
     <numFmt numFmtId="165" formatCode="&quot;Rp&quot;#,##0"/>
   </numFmts>
@@ -1247,7 +1292,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1255,6 +1300,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1334,6 +1380,12 @@
           <cell r="C2">
             <v>81234567890</v>
           </cell>
+          <cell r="D2" t="str">
+            <v>Jawa Barat</v>
+          </cell>
+          <cell r="G2" t="str">
+            <v>VIP</v>
+          </cell>
         </row>
         <row r="3">
           <cell r="A3" t="str">
@@ -1345,6 +1397,12 @@
           <cell r="C3">
             <v>628189876543</v>
           </cell>
+          <cell r="D3" t="str">
+            <v>DKI Jakarta</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>Gold</v>
+          </cell>
         </row>
         <row r="4">
           <cell r="A4" t="str">
@@ -1356,6 +1414,12 @@
           <cell r="C4">
             <v>6285611223344</v>
           </cell>
+          <cell r="D4" t="str">
+            <v>Jawa Tengah</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>Platinum</v>
+          </cell>
         </row>
         <row r="5">
           <cell r="A5" t="str">
@@ -1367,6 +1431,12 @@
           <cell r="C5">
             <v>87855443322</v>
           </cell>
+          <cell r="D5" t="str">
+            <v>Jawa Timur</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>Silver</v>
+          </cell>
         </row>
         <row r="6">
           <cell r="A6" t="str">
@@ -1378,6 +1448,12 @@
           <cell r="C6" t="str">
             <v>8189876543</v>
           </cell>
+          <cell r="D6" t="str">
+            <v>DKI Jakarta</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>Gold</v>
+          </cell>
         </row>
         <row r="7">
           <cell r="A7" t="str">
@@ -1389,6 +1465,12 @@
           <cell r="C7">
             <v>81122334455</v>
           </cell>
+          <cell r="D7" t="str">
+            <v>Banten</v>
+          </cell>
+          <cell r="G7" t="str">
+            <v>Silver</v>
+          </cell>
         </row>
         <row r="8">
           <cell r="A8" t="str">
@@ -1400,6 +1482,12 @@
           <cell r="C8">
             <v>628170099887</v>
           </cell>
+          <cell r="D8" t="str">
+            <v>DI Yogyakarta</v>
+          </cell>
+          <cell r="G8" t="str">
+            <v>Platinum</v>
+          </cell>
         </row>
         <row r="9">
           <cell r="A9" t="str">
@@ -1411,6 +1499,12 @@
           <cell r="C9">
             <v>85211447788</v>
           </cell>
+          <cell r="D9" t="str">
+            <v>Sumatera Utara</v>
+          </cell>
+          <cell r="G9" t="str">
+            <v>Gold</v>
+          </cell>
         </row>
         <row r="10">
           <cell r="A10" t="str">
@@ -1422,6 +1516,12 @@
           <cell r="C10" t="str">
             <v>+62 819 3322 1100</v>
           </cell>
+          <cell r="D10" t="str">
+            <v>Sulawesi Selatan</v>
+          </cell>
+          <cell r="G10" t="str">
+            <v>Silver</v>
+          </cell>
         </row>
         <row r="11">
           <cell r="A11" t="str">
@@ -1432,6 +1532,12 @@
           </cell>
           <cell r="C11">
             <v>81377665544</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>Bali</v>
+          </cell>
+          <cell r="G11" t="str">
+            <v>VIP</v>
           </cell>
         </row>
       </sheetData>
@@ -1794,6 +1900,125 @@
           </cell>
           <cell r="G16" t="str">
             <v>0.4</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Master_SLA_Shipping"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>JNT-EXP</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>J&amp;T Express</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>Express</v>
+          </cell>
+          <cell r="D2">
+            <v>2</v>
+          </cell>
+          <cell r="E2">
+            <v>15000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>JNT-REG</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>J&amp;T Express</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>Regular</v>
+          </cell>
+          <cell r="D3">
+            <v>4</v>
+          </cell>
+          <cell r="E3">
+            <v>10000</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>JNE-YES</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>JNE</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>Overnight</v>
+          </cell>
+          <cell r="D4">
+            <v>1</v>
+          </cell>
+          <cell r="E4">
+            <v>25000</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>JNE-REG</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>JNE</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>Regular</v>
+          </cell>
+          <cell r="D5">
+            <v>3</v>
+          </cell>
+          <cell r="E5">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>SISEPAT-BEST</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>SiCepat</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>Express</v>
+          </cell>
+          <cell r="D6">
+            <v>2</v>
+          </cell>
+          <cell r="E6">
+            <v>16000</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>SISEPAT-GOKIL</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>SiCepat</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>Cargo</v>
+          </cell>
+          <cell r="D7">
+            <v>5</v>
+          </cell>
+          <cell r="E7">
+            <v>8000</v>
           </cell>
         </row>
       </sheetData>
@@ -2119,7 +2344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A4B63D-0D46-44D9-8B15-778A85DACDCF}">
-  <dimension ref="A1:W101"/>
+  <dimension ref="A1:AD101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -2144,9 +2369,15 @@
     <col min="20" max="20" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2216,8 +2447,29 @@
       <c r="W1" s="3" t="s">
         <v>233</v>
       </c>
+      <c r="X1" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>240</v>
+      </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -2298,8 +2550,36 @@
         <f>_xlfn.XLOOKUP(P2,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.8</v>
       </c>
+      <c r="X2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M2,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M2,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G2,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G2,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB2" s="1">
+        <f>_xlfn.XLOOKUP(G2,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC2" s="7">
+        <f>_xlfn.XLOOKUP(G2,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD2" s="1" t="e" cm="1">
+        <f t="array" ref="AD2:AD101">INDEX(MATCH(S2,S2:S101,0),MATCH(Y2:Y101,0))</f>
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -2380,8 +2660,35 @@
         <f>_xlfn.XLOOKUP(P3,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.3</v>
       </c>
+      <c r="X3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M3,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Barat</v>
+      </c>
+      <c r="Y3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M3,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G3,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G3,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB3" s="1">
+        <f>_xlfn.XLOOKUP(G3,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC3" s="7">
+        <f>_xlfn.XLOOKUP(G3,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD3" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -2462,8 +2769,35 @@
         <f>_xlfn.XLOOKUP(P4,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.1</v>
       </c>
+      <c r="X4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M4,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M4,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G4,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G4,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB4" s="1">
+        <f>_xlfn.XLOOKUP(G4,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC4" s="7">
+        <f>_xlfn.XLOOKUP(G4,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD4" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
@@ -2544,8 +2878,35 @@
         <f>_xlfn.XLOOKUP(P5,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.35</v>
       </c>
+      <c r="X5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M5,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M5,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G5,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G5,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB5" s="1">
+        <f>_xlfn.XLOOKUP(G5,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC5" s="7">
+        <f>_xlfn.XLOOKUP(G5,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD5" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
@@ -2626,8 +2987,35 @@
         <f>_xlfn.XLOOKUP(P6,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.12</v>
       </c>
+      <c r="X6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M6,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M6,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G6,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G6,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Overnight</v>
+      </c>
+      <c r="AB6" s="1">
+        <f>_xlfn.XLOOKUP(G6,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>1</v>
+      </c>
+      <c r="AC6" s="7">
+        <f>_xlfn.XLOOKUP(G6,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>25000</v>
+      </c>
+      <c r="AD6" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
@@ -2708,8 +3096,35 @@
         <f>_xlfn.XLOOKUP(P7,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.12</v>
       </c>
+      <c r="X7" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M7,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y7" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M7,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z7" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G7,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA7" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G7,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB7" s="1">
+        <f>_xlfn.XLOOKUP(G7,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC7" s="7">
+        <f>_xlfn.XLOOKUP(G7,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD7" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>49</v>
       </c>
@@ -2790,8 +3205,35 @@
         <f>_xlfn.XLOOKUP(P8,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>4.5</v>
       </c>
+      <c r="X8" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M8,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y8" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M8,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z8" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G8,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA8" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G8,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Overnight</v>
+      </c>
+      <c r="AB8" s="1">
+        <f>_xlfn.XLOOKUP(G8,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>1</v>
+      </c>
+      <c r="AC8" s="7">
+        <f>_xlfn.XLOOKUP(G8,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>25000</v>
+      </c>
+      <c r="AD8" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>51</v>
       </c>
@@ -2872,8 +3314,35 @@
         <f>_xlfn.XLOOKUP(P9,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.12</v>
       </c>
+      <c r="X9" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M9,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Banten</v>
+      </c>
+      <c r="Y9" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M9,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z9" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G9,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA9" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G9,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB9" s="1">
+        <f>_xlfn.XLOOKUP(G9,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC9" s="7">
+        <f>_xlfn.XLOOKUP(G9,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD9" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>55</v>
       </c>
@@ -2954,8 +3423,35 @@
         <f>_xlfn.XLOOKUP(P10,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.25</v>
       </c>
+      <c r="X10" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M10,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Banten</v>
+      </c>
+      <c r="Y10" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M10,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z10" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G10,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA10" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G10,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB10" s="1">
+        <f>_xlfn.XLOOKUP(G10,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC10" s="7">
+        <f>_xlfn.XLOOKUP(G10,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD10" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>58</v>
       </c>
@@ -3036,8 +3532,35 @@
         <f>_xlfn.XLOOKUP(P11,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.8</v>
       </c>
+      <c r="X11" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M11,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y11" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M11,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z11" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G11,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA11" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G11,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB11" s="1">
+        <f>_xlfn.XLOOKUP(G11,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC11" s="7">
+        <f>_xlfn.XLOOKUP(G11,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD11" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3641,35 @@
         <f>_xlfn.XLOOKUP(P12,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>1.2</v>
       </c>
+      <c r="X12" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M12,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y12" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M12,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z12" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G12,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA12" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G12,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB12" s="1">
+        <f>_xlfn.XLOOKUP(G12,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC12" s="7">
+        <f>_xlfn.XLOOKUP(G12,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD12" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>63</v>
       </c>
@@ -3200,8 +3750,35 @@
         <f>_xlfn.XLOOKUP(P13,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.2</v>
       </c>
+      <c r="X13" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M13,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Barat</v>
+      </c>
+      <c r="Y13" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M13,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z13" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G13,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA13" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G13,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB13" s="1">
+        <f>_xlfn.XLOOKUP(G13,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC13" s="7">
+        <f>_xlfn.XLOOKUP(G13,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD13" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>66</v>
       </c>
@@ -3282,8 +3859,35 @@
         <f>_xlfn.XLOOKUP(P14,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.8</v>
       </c>
+      <c r="X14" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M14,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Barat</v>
+      </c>
+      <c r="Y14" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M14,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z14" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G14,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA14" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G14,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB14" s="1">
+        <f>_xlfn.XLOOKUP(G14,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC14" s="7">
+        <f>_xlfn.XLOOKUP(G14,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD14" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>68</v>
       </c>
@@ -3364,8 +3968,35 @@
         <f>_xlfn.XLOOKUP(P15,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>1.2</v>
       </c>
+      <c r="X15" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M15,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y15" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M15,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z15" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G15,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA15" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G15,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB15" s="1">
+        <f>_xlfn.XLOOKUP(G15,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC15" s="7">
+        <f>_xlfn.XLOOKUP(G15,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD15" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>71</v>
       </c>
@@ -3446,8 +4077,35 @@
         <f>_xlfn.XLOOKUP(P16,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.4</v>
       </c>
+      <c r="X16" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M16,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Banten</v>
+      </c>
+      <c r="Y16" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M16,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z16" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G16,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA16" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G16,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB16" s="1">
+        <f>_xlfn.XLOOKUP(G16,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC16" s="7">
+        <f>_xlfn.XLOOKUP(G16,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD16" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>74</v>
       </c>
@@ -3528,8 +4186,35 @@
         <f>_xlfn.XLOOKUP(P17,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.1</v>
       </c>
+      <c r="X17" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M17,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y17" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M17,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z17" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G17,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA17" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G17,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB17" s="1">
+        <f>_xlfn.XLOOKUP(G17,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC17" s="7">
+        <f>_xlfn.XLOOKUP(G17,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD17" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>76</v>
       </c>
@@ -3610,8 +4295,35 @@
         <f>_xlfn.XLOOKUP(P18,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.4</v>
       </c>
+      <c r="X18" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M18,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y18" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M18,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z18" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G18,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA18" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G18,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB18" s="1">
+        <f>_xlfn.XLOOKUP(G18,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC18" s="7">
+        <f>_xlfn.XLOOKUP(G18,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD18" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>77</v>
       </c>
@@ -3692,8 +4404,35 @@
         <f>_xlfn.XLOOKUP(P19,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.25</v>
       </c>
+      <c r="X19" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M19,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y19" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M19,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z19" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G19,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA19" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G19,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB19" s="1">
+        <f>_xlfn.XLOOKUP(G19,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC19" s="7">
+        <f>_xlfn.XLOOKUP(G19,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD19" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>79</v>
       </c>
@@ -3774,8 +4513,35 @@
         <f>_xlfn.XLOOKUP(P20,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.25</v>
       </c>
+      <c r="X20" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M20,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Barat</v>
+      </c>
+      <c r="Y20" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M20,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z20" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G20,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA20" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G20,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB20" s="1">
+        <f>_xlfn.XLOOKUP(G20,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC20" s="7">
+        <f>_xlfn.XLOOKUP(G20,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD20" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>81</v>
       </c>
@@ -3856,8 +4622,35 @@
         <f>_xlfn.XLOOKUP(P21,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>4.5</v>
       </c>
+      <c r="X21" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M21,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Bali</v>
+      </c>
+      <c r="Y21" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M21,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z21" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G21,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA21" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G21,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB21" s="1">
+        <f>_xlfn.XLOOKUP(G21,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC21" s="7">
+        <f>_xlfn.XLOOKUP(G21,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD21" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>83</v>
       </c>
@@ -3938,8 +4731,35 @@
         <f>_xlfn.XLOOKUP(P22,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.35</v>
       </c>
+      <c r="X22" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M22,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DI Yogyakarta</v>
+      </c>
+      <c r="Y22" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M22,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z22" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G22,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA22" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G22,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB22" s="1">
+        <f>_xlfn.XLOOKUP(G22,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC22" s="7">
+        <f>_xlfn.XLOOKUP(G22,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD22" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>86</v>
       </c>
@@ -4020,8 +4840,35 @@
         <f>_xlfn.XLOOKUP(P23,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.15</v>
       </c>
+      <c r="X23" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M23,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y23" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M23,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z23" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G23,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA23" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G23,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB23" s="1">
+        <f>_xlfn.XLOOKUP(G23,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC23" s="7">
+        <f>_xlfn.XLOOKUP(G23,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD23" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>88</v>
       </c>
@@ -4102,8 +4949,35 @@
         <f>_xlfn.XLOOKUP(P24,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.2</v>
       </c>
+      <c r="X24" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M24,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Barat</v>
+      </c>
+      <c r="Y24" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M24,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z24" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G24,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA24" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G24,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB24" s="1">
+        <f>_xlfn.XLOOKUP(G24,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC24" s="7">
+        <f>_xlfn.XLOOKUP(G24,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD24" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>89</v>
       </c>
@@ -4184,8 +5058,35 @@
         <f>_xlfn.XLOOKUP(P25,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.4</v>
       </c>
+      <c r="X25" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M25,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DI Yogyakarta</v>
+      </c>
+      <c r="Y25" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M25,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z25" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G25,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA25" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G25,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB25" s="1">
+        <f>_xlfn.XLOOKUP(G25,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC25" s="7">
+        <f>_xlfn.XLOOKUP(G25,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD25" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>92</v>
       </c>
@@ -4266,8 +5167,35 @@
         <f>_xlfn.XLOOKUP(P26,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>1.2</v>
       </c>
+      <c r="X26" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M26,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sumatera Utara</v>
+      </c>
+      <c r="Y26" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M26,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z26" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G26,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA26" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G26,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB26" s="1">
+        <f>_xlfn.XLOOKUP(G26,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC26" s="7">
+        <f>_xlfn.XLOOKUP(G26,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD26" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>95</v>
       </c>
@@ -4348,8 +5276,35 @@
         <f>_xlfn.XLOOKUP(P27,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.15</v>
       </c>
+      <c r="X27" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M27,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sumatera Utara</v>
+      </c>
+      <c r="Y27" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M27,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z27" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G27,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA27" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G27,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB27" s="1">
+        <f>_xlfn.XLOOKUP(G27,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC27" s="7">
+        <f>_xlfn.XLOOKUP(G27,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD27" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>97</v>
       </c>
@@ -4430,8 +5385,35 @@
         <f>_xlfn.XLOOKUP(P28,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.35</v>
       </c>
+      <c r="X28" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M28,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y28" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M28,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z28" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G28,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA28" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G28,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB28" s="1">
+        <f>_xlfn.XLOOKUP(G28,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC28" s="7">
+        <f>_xlfn.XLOOKUP(G28,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD28" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>98</v>
       </c>
@@ -4512,8 +5494,35 @@
         <f>_xlfn.XLOOKUP(P29,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.9</v>
       </c>
+      <c r="X29" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M29,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sulawesi Selatan</v>
+      </c>
+      <c r="Y29" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M29,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z29" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G29,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA29" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G29,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB29" s="1">
+        <f>_xlfn.XLOOKUP(G29,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC29" s="7">
+        <f>_xlfn.XLOOKUP(G29,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD29" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>101</v>
       </c>
@@ -4594,8 +5603,35 @@
         <f>_xlfn.XLOOKUP(P30,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.8</v>
       </c>
+      <c r="X30" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M30,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y30" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M30,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z30" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G30,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA30" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G30,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB30" s="1">
+        <f>_xlfn.XLOOKUP(G30,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC30" s="7">
+        <f>_xlfn.XLOOKUP(G30,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD30" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>102</v>
       </c>
@@ -4676,8 +5712,35 @@
         <f>_xlfn.XLOOKUP(P31,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.9</v>
       </c>
+      <c r="X31" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M31,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y31" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M31,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z31" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G31,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA31" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G31,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB31" s="1">
+        <f>_xlfn.XLOOKUP(G31,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC31" s="7">
+        <f>_xlfn.XLOOKUP(G31,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD31" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>103</v>
       </c>
@@ -4758,8 +5821,35 @@
         <f>_xlfn.XLOOKUP(P32,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.4</v>
       </c>
+      <c r="X32" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M32,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y32" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M32,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z32" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G32,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA32" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G32,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB32" s="1">
+        <f>_xlfn.XLOOKUP(G32,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC32" s="7">
+        <f>_xlfn.XLOOKUP(G32,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD32" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>105</v>
       </c>
@@ -4840,8 +5930,35 @@
         <f>_xlfn.XLOOKUP(P33,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.25</v>
       </c>
+      <c r="X33" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M33,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Banten</v>
+      </c>
+      <c r="Y33" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M33,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z33" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G33,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA33" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G33,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB33" s="1">
+        <f>_xlfn.XLOOKUP(G33,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC33" s="7">
+        <f>_xlfn.XLOOKUP(G33,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD33" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>106</v>
       </c>
@@ -4922,8 +6039,35 @@
         <f>_xlfn.XLOOKUP(P34,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.8</v>
       </c>
+      <c r="X34" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M34,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y34" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M34,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z34" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G34,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA34" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G34,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB34" s="1">
+        <f>_xlfn.XLOOKUP(G34,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC34" s="7">
+        <f>_xlfn.XLOOKUP(G34,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD34" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>108</v>
       </c>
@@ -5004,8 +6148,35 @@
         <f>_xlfn.XLOOKUP(P35,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.4</v>
       </c>
+      <c r="X35" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M35,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y35" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M35,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z35" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G35,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA35" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G35,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB35" s="1">
+        <f>_xlfn.XLOOKUP(G35,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC35" s="7">
+        <f>_xlfn.XLOOKUP(G35,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD35" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>110</v>
       </c>
@@ -5086,8 +6257,35 @@
         <f>_xlfn.XLOOKUP(P36,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.9</v>
       </c>
+      <c r="X36" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M36,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y36" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M36,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z36" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G36,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA36" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G36,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB36" s="1">
+        <f>_xlfn.XLOOKUP(G36,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC36" s="7">
+        <f>_xlfn.XLOOKUP(G36,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD36" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>112</v>
       </c>
@@ -5168,8 +6366,35 @@
         <f>_xlfn.XLOOKUP(P37,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.1</v>
       </c>
+      <c r="X37" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M37,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Tengah</v>
+      </c>
+      <c r="Y37" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M37,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z37" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G37,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA37" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G37,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Overnight</v>
+      </c>
+      <c r="AB37" s="1">
+        <f>_xlfn.XLOOKUP(G37,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>1</v>
+      </c>
+      <c r="AC37" s="7">
+        <f>_xlfn.XLOOKUP(G37,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>25000</v>
+      </c>
+      <c r="AD37" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>114</v>
       </c>
@@ -5250,8 +6475,35 @@
         <f>_xlfn.XLOOKUP(P38,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.35</v>
       </c>
+      <c r="X38" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M38,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y38" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M38,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z38" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G38,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA38" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G38,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB38" s="1">
+        <f>_xlfn.XLOOKUP(G38,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC38" s="7">
+        <f>_xlfn.XLOOKUP(G38,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD38" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>116</v>
       </c>
@@ -5332,8 +6584,35 @@
         <f>_xlfn.XLOOKUP(P39,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.35</v>
       </c>
+      <c r="X39" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M39,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y39" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M39,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z39" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G39,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA39" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G39,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB39" s="1">
+        <f>_xlfn.XLOOKUP(G39,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC39" s="7">
+        <f>_xlfn.XLOOKUP(G39,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD39" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>118</v>
       </c>
@@ -5414,8 +6693,35 @@
         <f>_xlfn.XLOOKUP(P40,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.3</v>
       </c>
+      <c r="X40" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M40,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Barat</v>
+      </c>
+      <c r="Y40" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M40,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z40" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G40,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA40" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G40,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Overnight</v>
+      </c>
+      <c r="AB40" s="1">
+        <f>_xlfn.XLOOKUP(G40,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>1</v>
+      </c>
+      <c r="AC40" s="7">
+        <f>_xlfn.XLOOKUP(G40,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>25000</v>
+      </c>
+      <c r="AD40" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>121</v>
       </c>
@@ -5496,8 +6802,35 @@
         <f>_xlfn.XLOOKUP(P41,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.15</v>
       </c>
+      <c r="X41" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M41,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Bali</v>
+      </c>
+      <c r="Y41" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M41,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z41" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G41,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA41" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G41,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB41" s="1">
+        <f>_xlfn.XLOOKUP(G41,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC41" s="7">
+        <f>_xlfn.XLOOKUP(G41,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD41" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>123</v>
       </c>
@@ -5578,8 +6911,35 @@
         <f>_xlfn.XLOOKUP(P42,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.9</v>
       </c>
+      <c r="X42" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M42,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y42" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M42,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z42" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G42,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA42" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G42,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB42" s="1">
+        <f>_xlfn.XLOOKUP(G42,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC42" s="7">
+        <f>_xlfn.XLOOKUP(G42,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD42" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>124</v>
       </c>
@@ -5660,8 +7020,35 @@
         <f>_xlfn.XLOOKUP(P43,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.8</v>
       </c>
+      <c r="X43" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M43,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DI Yogyakarta</v>
+      </c>
+      <c r="Y43" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M43,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z43" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G43,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA43" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G43,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB43" s="1">
+        <f>_xlfn.XLOOKUP(G43,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC43" s="7">
+        <f>_xlfn.XLOOKUP(G43,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD43" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>126</v>
       </c>
@@ -5742,8 +7129,35 @@
         <f>_xlfn.XLOOKUP(P44,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.4</v>
       </c>
+      <c r="X44" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M44,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Barat</v>
+      </c>
+      <c r="Y44" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M44,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z44" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G44,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA44" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G44,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB44" s="1">
+        <f>_xlfn.XLOOKUP(G44,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC44" s="7">
+        <f>_xlfn.XLOOKUP(G44,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD44" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>128</v>
       </c>
@@ -5824,8 +7238,35 @@
         <f>_xlfn.XLOOKUP(P45,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.15</v>
       </c>
+      <c r="X45" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M45,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y45" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M45,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z45" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G45,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA45" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G45,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB45" s="1">
+        <f>_xlfn.XLOOKUP(G45,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC45" s="7">
+        <f>_xlfn.XLOOKUP(G45,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD45" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>130</v>
       </c>
@@ -5906,8 +7347,35 @@
         <f>_xlfn.XLOOKUP(P46,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.25</v>
       </c>
+      <c r="X46" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M46,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y46" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M46,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z46" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G46,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA46" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G46,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB46" s="1">
+        <f>_xlfn.XLOOKUP(G46,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC46" s="7">
+        <f>_xlfn.XLOOKUP(G46,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD46" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>132</v>
       </c>
@@ -5988,8 +7456,35 @@
         <f>_xlfn.XLOOKUP(P47,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.25</v>
       </c>
+      <c r="X47" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M47,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Bali</v>
+      </c>
+      <c r="Y47" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M47,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z47" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G47,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA47" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G47,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB47" s="1">
+        <f>_xlfn.XLOOKUP(G47,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC47" s="7">
+        <f>_xlfn.XLOOKUP(G47,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD47" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>134</v>
       </c>
@@ -6070,8 +7565,35 @@
         <f>_xlfn.XLOOKUP(P48,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.1</v>
       </c>
+      <c r="X48" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M48,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Tengah</v>
+      </c>
+      <c r="Y48" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M48,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z48" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G48,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA48" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G48,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB48" s="1">
+        <f>_xlfn.XLOOKUP(G48,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC48" s="7">
+        <f>_xlfn.XLOOKUP(G48,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD48" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>137</v>
       </c>
@@ -6152,8 +7674,35 @@
         <f>_xlfn.XLOOKUP(P49,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.15</v>
       </c>
+      <c r="X49" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M49,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sulawesi Selatan</v>
+      </c>
+      <c r="Y49" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M49,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z49" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G49,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA49" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G49,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB49" s="1">
+        <f>_xlfn.XLOOKUP(G49,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC49" s="7">
+        <f>_xlfn.XLOOKUP(G49,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD49" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>138</v>
       </c>
@@ -6234,8 +7783,35 @@
         <f>_xlfn.XLOOKUP(P50,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.1</v>
       </c>
+      <c r="X50" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M50,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y50" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M50,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z50" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G50,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA50" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G50,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB50" s="1">
+        <f>_xlfn.XLOOKUP(G50,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC50" s="7">
+        <f>_xlfn.XLOOKUP(G50,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD50" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>140</v>
       </c>
@@ -6316,8 +7892,35 @@
         <f>_xlfn.XLOOKUP(P51,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.25</v>
       </c>
+      <c r="X51" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M51,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y51" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M51,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z51" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G51,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA51" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G51,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB51" s="1">
+        <f>_xlfn.XLOOKUP(G51,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC51" s="7">
+        <f>_xlfn.XLOOKUP(G51,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD51" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>142</v>
       </c>
@@ -6398,8 +8001,35 @@
         <f>_xlfn.XLOOKUP(P52,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.3</v>
       </c>
+      <c r="X52" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M52,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y52" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M52,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z52" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G52,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA52" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G52,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB52" s="1">
+        <f>_xlfn.XLOOKUP(G52,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC52" s="7">
+        <f>_xlfn.XLOOKUP(G52,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD52" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>144</v>
       </c>
@@ -6480,8 +8110,35 @@
         <f>_xlfn.XLOOKUP(P53,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.8</v>
       </c>
+      <c r="X53" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M53,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Bali</v>
+      </c>
+      <c r="Y53" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M53,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z53" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G53,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA53" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G53,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB53" s="1">
+        <f>_xlfn.XLOOKUP(G53,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC53" s="7">
+        <f>_xlfn.XLOOKUP(G53,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD53" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>146</v>
       </c>
@@ -6562,8 +8219,35 @@
         <f>_xlfn.XLOOKUP(P54,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.1</v>
       </c>
+      <c r="X54" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M54,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sulawesi Selatan</v>
+      </c>
+      <c r="Y54" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M54,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z54" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G54,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA54" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G54,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB54" s="1">
+        <f>_xlfn.XLOOKUP(G54,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC54" s="7">
+        <f>_xlfn.XLOOKUP(G54,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD54" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>148</v>
       </c>
@@ -6644,8 +8328,35 @@
         <f>_xlfn.XLOOKUP(P55,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.8</v>
       </c>
+      <c r="X55" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M55,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DI Yogyakarta</v>
+      </c>
+      <c r="Y55" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M55,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z55" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G55,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA55" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G55,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB55" s="1">
+        <f>_xlfn.XLOOKUP(G55,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC55" s="7">
+        <f>_xlfn.XLOOKUP(G55,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD55" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>150</v>
       </c>
@@ -6726,8 +8437,35 @@
         <f>_xlfn.XLOOKUP(P56,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>1.2</v>
       </c>
+      <c r="X56" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M56,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sumatera Utara</v>
+      </c>
+      <c r="Y56" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M56,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z56" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G56,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA56" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G56,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB56" s="1">
+        <f>_xlfn.XLOOKUP(G56,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC56" s="7">
+        <f>_xlfn.XLOOKUP(G56,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD56" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>152</v>
       </c>
@@ -6808,8 +8546,35 @@
         <f>_xlfn.XLOOKUP(P57,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.4</v>
       </c>
+      <c r="X57" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M57,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DI Yogyakarta</v>
+      </c>
+      <c r="Y57" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M57,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z57" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G57,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA57" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G57,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB57" s="1">
+        <f>_xlfn.XLOOKUP(G57,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC57" s="7">
+        <f>_xlfn.XLOOKUP(G57,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD57" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>154</v>
       </c>
@@ -6890,8 +8655,35 @@
         <f>_xlfn.XLOOKUP(P58,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.1</v>
       </c>
+      <c r="X58" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M58,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Barat</v>
+      </c>
+      <c r="Y58" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M58,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z58" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G58,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA58" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G58,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB58" s="1">
+        <f>_xlfn.XLOOKUP(G58,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC58" s="7">
+        <f>_xlfn.XLOOKUP(G58,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD58" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>156</v>
       </c>
@@ -6972,8 +8764,35 @@
         <f>_xlfn.XLOOKUP(P59,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>4.5</v>
       </c>
+      <c r="X59" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M59,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y59" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M59,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z59" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G59,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA59" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G59,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB59" s="1">
+        <f>_xlfn.XLOOKUP(G59,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC59" s="7">
+        <f>_xlfn.XLOOKUP(G59,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD59" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>158</v>
       </c>
@@ -7054,8 +8873,35 @@
         <f>_xlfn.XLOOKUP(P60,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.8</v>
       </c>
+      <c r="X60" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M60,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Bali</v>
+      </c>
+      <c r="Y60" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M60,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z60" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G60,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA60" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G60,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB60" s="1">
+        <f>_xlfn.XLOOKUP(G60,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC60" s="7">
+        <f>_xlfn.XLOOKUP(G60,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD60" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>160</v>
       </c>
@@ -7136,8 +8982,35 @@
         <f>_xlfn.XLOOKUP(P61,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.1</v>
       </c>
+      <c r="X61" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M61,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Bali</v>
+      </c>
+      <c r="Y61" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M61,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z61" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G61,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA61" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G61,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB61" s="1">
+        <f>_xlfn.XLOOKUP(G61,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC61" s="7">
+        <f>_xlfn.XLOOKUP(G61,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD61" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>162</v>
       </c>
@@ -7218,8 +9091,35 @@
         <f>_xlfn.XLOOKUP(P62,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.12</v>
       </c>
+      <c r="X62" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M62,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DI Yogyakarta</v>
+      </c>
+      <c r="Y62" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M62,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z62" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G62,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA62" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G62,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB62" s="1">
+        <f>_xlfn.XLOOKUP(G62,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC62" s="7">
+        <f>_xlfn.XLOOKUP(G62,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD62" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>163</v>
       </c>
@@ -7300,8 +9200,35 @@
         <f>_xlfn.XLOOKUP(P63,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>4.5</v>
       </c>
+      <c r="X63" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M63,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y63" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M63,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z63" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G63,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA63" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G63,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB63" s="1">
+        <f>_xlfn.XLOOKUP(G63,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC63" s="7">
+        <f>_xlfn.XLOOKUP(G63,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD63" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>165</v>
       </c>
@@ -7382,8 +9309,35 @@
         <f>_xlfn.XLOOKUP(P64,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.25</v>
       </c>
+      <c r="X64" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M64,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sumatera Utara</v>
+      </c>
+      <c r="Y64" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M64,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z64" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G64,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA64" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G64,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Overnight</v>
+      </c>
+      <c r="AB64" s="1">
+        <f>_xlfn.XLOOKUP(G64,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>1</v>
+      </c>
+      <c r="AC64" s="7">
+        <f>_xlfn.XLOOKUP(G64,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>25000</v>
+      </c>
+      <c r="AD64" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>166</v>
       </c>
@@ -7464,8 +9418,35 @@
         <f>_xlfn.XLOOKUP(P65,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.9</v>
       </c>
+      <c r="X65" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M65,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y65" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M65,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z65" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G65,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA65" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G65,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB65" s="1">
+        <f>_xlfn.XLOOKUP(G65,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC65" s="7">
+        <f>_xlfn.XLOOKUP(G65,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD65" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>168</v>
       </c>
@@ -7546,8 +9527,35 @@
         <f>_xlfn.XLOOKUP(P66,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.8</v>
       </c>
+      <c r="X66" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M66,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y66" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M66,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z66" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G66,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA66" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G66,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB66" s="1">
+        <f>_xlfn.XLOOKUP(G66,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC66" s="7">
+        <f>_xlfn.XLOOKUP(G66,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD66" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>169</v>
       </c>
@@ -7628,8 +9636,35 @@
         <f>_xlfn.XLOOKUP(P67,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.35</v>
       </c>
+      <c r="X67" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M67,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y67" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M67,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z67" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G67,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA67" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G67,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB67" s="1">
+        <f>_xlfn.XLOOKUP(G67,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC67" s="7">
+        <f>_xlfn.XLOOKUP(G67,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD67" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>171</v>
       </c>
@@ -7710,8 +9745,35 @@
         <f>_xlfn.XLOOKUP(P68,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.8</v>
       </c>
+      <c r="X68" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M68,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Banten</v>
+      </c>
+      <c r="Y68" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M68,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z68" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G68,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA68" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G68,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB68" s="1">
+        <f>_xlfn.XLOOKUP(G68,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC68" s="7">
+        <f>_xlfn.XLOOKUP(G68,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD68" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>172</v>
       </c>
@@ -7792,8 +9854,35 @@
         <f>_xlfn.XLOOKUP(P69,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.25</v>
       </c>
+      <c r="X69" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M69,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Tengah</v>
+      </c>
+      <c r="Y69" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M69,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z69" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G69,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA69" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G69,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB69" s="1">
+        <f>_xlfn.XLOOKUP(G69,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC69" s="7">
+        <f>_xlfn.XLOOKUP(G69,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD69" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>174</v>
       </c>
@@ -7874,8 +9963,35 @@
         <f>_xlfn.XLOOKUP(P70,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.9</v>
       </c>
+      <c r="X70" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M70,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y70" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M70,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z70" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G70,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA70" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G70,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB70" s="1">
+        <f>_xlfn.XLOOKUP(G70,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC70" s="7">
+        <f>_xlfn.XLOOKUP(G70,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD70" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>176</v>
       </c>
@@ -7956,8 +10072,35 @@
         <f>_xlfn.XLOOKUP(P71,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.2</v>
       </c>
+      <c r="X71" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M71,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Tengah</v>
+      </c>
+      <c r="Y71" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M71,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z71" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G71,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA71" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G71,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB71" s="1">
+        <f>_xlfn.XLOOKUP(G71,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC71" s="7">
+        <f>_xlfn.XLOOKUP(G71,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD71" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>178</v>
       </c>
@@ -8038,8 +10181,35 @@
         <f>_xlfn.XLOOKUP(P72,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.8</v>
       </c>
+      <c r="X72" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M72,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Tengah</v>
+      </c>
+      <c r="Y72" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M72,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z72" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G72,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA72" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G72,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB72" s="1">
+        <f>_xlfn.XLOOKUP(G72,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC72" s="7">
+        <f>_xlfn.XLOOKUP(G72,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD72" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>179</v>
       </c>
@@ -8120,8 +10290,35 @@
         <f>_xlfn.XLOOKUP(P73,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.1</v>
       </c>
+      <c r="X73" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M73,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Tengah</v>
+      </c>
+      <c r="Y73" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M73,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z73" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G73,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA73" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G73,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB73" s="1">
+        <f>_xlfn.XLOOKUP(G73,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC73" s="7">
+        <f>_xlfn.XLOOKUP(G73,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD73" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>180</v>
       </c>
@@ -8202,8 +10399,35 @@
         <f>_xlfn.XLOOKUP(P74,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.4</v>
       </c>
+      <c r="X74" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M74,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sumatera Utara</v>
+      </c>
+      <c r="Y74" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M74,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z74" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G74,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA74" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G74,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB74" s="1">
+        <f>_xlfn.XLOOKUP(G74,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC74" s="7">
+        <f>_xlfn.XLOOKUP(G74,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD74" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>182</v>
       </c>
@@ -8284,8 +10508,35 @@
         <f>_xlfn.XLOOKUP(P75,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>1.2</v>
       </c>
+      <c r="X75" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M75,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y75" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M75,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z75" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G75,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA75" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G75,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB75" s="1">
+        <f>_xlfn.XLOOKUP(G75,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC75" s="7">
+        <f>_xlfn.XLOOKUP(G75,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD75" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>184</v>
       </c>
@@ -8366,8 +10617,35 @@
         <f>_xlfn.XLOOKUP(P76,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.8</v>
       </c>
+      <c r="X76" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M76,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y76" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M76,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z76" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G76,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA76" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G76,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB76" s="1">
+        <f>_xlfn.XLOOKUP(G76,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC76" s="7">
+        <f>_xlfn.XLOOKUP(G76,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD76" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>186</v>
       </c>
@@ -8448,8 +10726,35 @@
         <f>_xlfn.XLOOKUP(P77,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.35</v>
       </c>
+      <c r="X77" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M77,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y77" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M77,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z77" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G77,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA77" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G77,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB77" s="1">
+        <f>_xlfn.XLOOKUP(G77,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC77" s="7">
+        <f>_xlfn.XLOOKUP(G77,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD77" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>187</v>
       </c>
@@ -8530,8 +10835,35 @@
         <f>_xlfn.XLOOKUP(P78,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>4.5</v>
       </c>
+      <c r="X78" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M78,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y78" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M78,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z78" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G78,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA78" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G78,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Overnight</v>
+      </c>
+      <c r="AB78" s="1">
+        <f>_xlfn.XLOOKUP(G78,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>1</v>
+      </c>
+      <c r="AC78" s="7">
+        <f>_xlfn.XLOOKUP(G78,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>25000</v>
+      </c>
+      <c r="AD78" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>188</v>
       </c>
@@ -8612,8 +10944,35 @@
         <f>_xlfn.XLOOKUP(P79,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>1.1</v>
       </c>
+      <c r="X79" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M79,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sumatera Utara</v>
+      </c>
+      <c r="Y79" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M79,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z79" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G79,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA79" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G79,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB79" s="1">
+        <f>_xlfn.XLOOKUP(G79,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC79" s="7">
+        <f>_xlfn.XLOOKUP(G79,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD79" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>190</v>
       </c>
@@ -8694,8 +11053,35 @@
         <f>_xlfn.XLOOKUP(P80,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>4.5</v>
       </c>
+      <c r="X80" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M80,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Bali</v>
+      </c>
+      <c r="Y80" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M80,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z80" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G80,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA80" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G80,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Overnight</v>
+      </c>
+      <c r="AB80" s="1">
+        <f>_xlfn.XLOOKUP(G80,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>1</v>
+      </c>
+      <c r="AC80" s="7">
+        <f>_xlfn.XLOOKUP(G80,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>25000</v>
+      </c>
+      <c r="AD80" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>192</v>
       </c>
@@ -8776,8 +11162,35 @@
         <f>_xlfn.XLOOKUP(P81,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.2</v>
       </c>
+      <c r="X81" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M81,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DI Yogyakarta</v>
+      </c>
+      <c r="Y81" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M81,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z81" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G81,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA81" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G81,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB81" s="1">
+        <f>_xlfn.XLOOKUP(G81,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC81" s="7">
+        <f>_xlfn.XLOOKUP(G81,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD81" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>193</v>
       </c>
@@ -8858,8 +11271,35 @@
         <f>_xlfn.XLOOKUP(P82,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.9</v>
       </c>
+      <c r="X82" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M82,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Tengah</v>
+      </c>
+      <c r="Y82" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M82,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z82" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G82,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA82" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G82,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB82" s="1">
+        <f>_xlfn.XLOOKUP(G82,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC82" s="7">
+        <f>_xlfn.XLOOKUP(G82,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD82" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>194</v>
       </c>
@@ -8940,8 +11380,35 @@
         <f>_xlfn.XLOOKUP(P83,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.3</v>
       </c>
+      <c r="X83" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M83,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Banten</v>
+      </c>
+      <c r="Y83" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M83,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z83" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G83,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA83" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G83,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB83" s="1">
+        <f>_xlfn.XLOOKUP(G83,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC83" s="7">
+        <f>_xlfn.XLOOKUP(G83,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD83" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>195</v>
       </c>
@@ -9022,8 +11489,35 @@
         <f>_xlfn.XLOOKUP(P84,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>4.5</v>
       </c>
+      <c r="X84" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M84,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Banten</v>
+      </c>
+      <c r="Y84" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M84,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z84" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G84,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA84" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G84,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Overnight</v>
+      </c>
+      <c r="AB84" s="1">
+        <f>_xlfn.XLOOKUP(G84,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>1</v>
+      </c>
+      <c r="AC84" s="7">
+        <f>_xlfn.XLOOKUP(G84,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>25000</v>
+      </c>
+      <c r="AD84" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>196</v>
       </c>
@@ -9104,8 +11598,35 @@
         <f>_xlfn.XLOOKUP(P85,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.3</v>
       </c>
+      <c r="X85" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M85,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sumatera Utara</v>
+      </c>
+      <c r="Y85" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M85,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z85" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G85,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA85" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G85,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB85" s="1">
+        <f>_xlfn.XLOOKUP(G85,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC85" s="7">
+        <f>_xlfn.XLOOKUP(G85,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD85" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>199</v>
       </c>
@@ -9186,8 +11707,35 @@
         <f>_xlfn.XLOOKUP(P86,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.12</v>
       </c>
+      <c r="X86" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M86,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y86" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M86,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z86" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G86,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA86" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G86,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB86" s="1">
+        <f>_xlfn.XLOOKUP(G86,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC86" s="7">
+        <f>_xlfn.XLOOKUP(G86,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD86" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>200</v>
       </c>
@@ -9268,8 +11816,35 @@
         <f>_xlfn.XLOOKUP(P87,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>1.1</v>
       </c>
+      <c r="X87" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M87,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Timur</v>
+      </c>
+      <c r="Y87" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M87,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z87" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G87,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA87" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G87,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Overnight</v>
+      </c>
+      <c r="AB87" s="1">
+        <f>_xlfn.XLOOKUP(G87,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>1</v>
+      </c>
+      <c r="AC87" s="7">
+        <f>_xlfn.XLOOKUP(G87,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>25000</v>
+      </c>
+      <c r="AD87" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>202</v>
       </c>
@@ -9350,8 +11925,35 @@
         <f>_xlfn.XLOOKUP(P88,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.4</v>
       </c>
+      <c r="X88" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M88,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sulawesi Selatan</v>
+      </c>
+      <c r="Y88" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M88,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z88" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G88,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA88" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G88,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB88" s="1">
+        <f>_xlfn.XLOOKUP(G88,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC88" s="7">
+        <f>_xlfn.XLOOKUP(G88,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD88" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>203</v>
       </c>
@@ -9432,8 +12034,35 @@
         <f>_xlfn.XLOOKUP(P89,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.9</v>
       </c>
+      <c r="X89" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M89,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sumatera Utara</v>
+      </c>
+      <c r="Y89" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M89,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z89" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G89,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA89" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G89,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB89" s="1">
+        <f>_xlfn.XLOOKUP(G89,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC89" s="7">
+        <f>_xlfn.XLOOKUP(G89,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD89" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>205</v>
       </c>
@@ -9514,8 +12143,35 @@
         <f>_xlfn.XLOOKUP(P90,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.8</v>
       </c>
+      <c r="X90" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M90,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DI Yogyakarta</v>
+      </c>
+      <c r="Y90" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M90,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z90" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G90,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA90" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G90,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB90" s="1">
+        <f>_xlfn.XLOOKUP(G90,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC90" s="7">
+        <f>_xlfn.XLOOKUP(G90,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD90" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>206</v>
       </c>
@@ -9596,8 +12252,35 @@
         <f>_xlfn.XLOOKUP(P91,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.9</v>
       </c>
+      <c r="X91" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M91,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Bali</v>
+      </c>
+      <c r="Y91" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M91,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z91" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G91,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA91" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G91,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB91" s="1">
+        <f>_xlfn.XLOOKUP(G91,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC91" s="7">
+        <f>_xlfn.XLOOKUP(G91,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD91" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>207</v>
       </c>
@@ -9678,8 +12361,35 @@
         <f>_xlfn.XLOOKUP(P92,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.1</v>
       </c>
+      <c r="X92" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M92,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sumatera Utara</v>
+      </c>
+      <c r="Y92" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M92,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z92" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G92,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA92" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G92,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Overnight</v>
+      </c>
+      <c r="AB92" s="1">
+        <f>_xlfn.XLOOKUP(G92,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>1</v>
+      </c>
+      <c r="AC92" s="7">
+        <f>_xlfn.XLOOKUP(G92,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>25000</v>
+      </c>
+      <c r="AD92" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>209</v>
       </c>
@@ -9760,8 +12470,35 @@
         <f>_xlfn.XLOOKUP(P93,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.8</v>
       </c>
+      <c r="X93" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M93,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sulawesi Selatan</v>
+      </c>
+      <c r="Y93" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M93,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z93" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G93,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA93" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G93,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB93" s="1">
+        <f>_xlfn.XLOOKUP(G93,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC93" s="7">
+        <f>_xlfn.XLOOKUP(G93,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD93" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>211</v>
       </c>
@@ -9842,8 +12579,35 @@
         <f>_xlfn.XLOOKUP(P94,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.8</v>
       </c>
+      <c r="X94" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M94,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Tengah</v>
+      </c>
+      <c r="Y94" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M94,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z94" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G94,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>JNE</v>
+      </c>
+      <c r="AA94" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G94,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB94" s="1">
+        <f>_xlfn.XLOOKUP(G94,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC94" s="7">
+        <f>_xlfn.XLOOKUP(G94,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>12000</v>
+      </c>
+      <c r="AD94" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>213</v>
       </c>
@@ -9924,8 +12688,35 @@
         <f>_xlfn.XLOOKUP(P95,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.35</v>
       </c>
+      <c r="X95" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M95,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sulawesi Selatan</v>
+      </c>
+      <c r="Y95" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M95,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Silver</v>
+      </c>
+      <c r="Z95" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G95,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA95" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G95,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB95" s="1">
+        <f>_xlfn.XLOOKUP(G95,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC95" s="7">
+        <f>_xlfn.XLOOKUP(G95,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD95" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>214</v>
       </c>
@@ -10006,8 +12797,35 @@
         <f>_xlfn.XLOOKUP(P96,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>1.2</v>
       </c>
+      <c r="X96" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M96,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Bali</v>
+      </c>
+      <c r="Y96" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M96,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z96" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G96,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA96" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G96,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB96" s="1">
+        <f>_xlfn.XLOOKUP(G96,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC96" s="7">
+        <f>_xlfn.XLOOKUP(G96,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD96" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>215</v>
       </c>
@@ -10088,8 +12906,35 @@
         <f>_xlfn.XLOOKUP(P97,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>1.1</v>
       </c>
+      <c r="X97" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M97,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y97" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M97,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z97" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G97,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA97" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G97,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB97" s="1">
+        <f>_xlfn.XLOOKUP(G97,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC97" s="7">
+        <f>_xlfn.XLOOKUP(G97,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD97" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>217</v>
       </c>
@@ -10170,8 +13015,35 @@
         <f>_xlfn.XLOOKUP(P98,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.3</v>
       </c>
+      <c r="X98" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M98,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Sumatera Utara</v>
+      </c>
+      <c r="Y98" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M98,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z98" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G98,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA98" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G98,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Cargo</v>
+      </c>
+      <c r="AB98" s="1">
+        <f>_xlfn.XLOOKUP(G98,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>5</v>
+      </c>
+      <c r="AC98" s="7">
+        <f>_xlfn.XLOOKUP(G98,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>8000</v>
+      </c>
+      <c r="AD98" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>219</v>
       </c>
@@ -10252,8 +13124,35 @@
         <f>_xlfn.XLOOKUP(P99,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>4.5</v>
       </c>
+      <c r="X99" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M99,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Barat</v>
+      </c>
+      <c r="Y99" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M99,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>VIP</v>
+      </c>
+      <c r="Z99" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G99,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA99" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G99,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Regular</v>
+      </c>
+      <c r="AB99" s="1">
+        <f>_xlfn.XLOOKUP(G99,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>4</v>
+      </c>
+      <c r="AC99" s="7">
+        <f>_xlfn.XLOOKUP(G99,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>10000</v>
+      </c>
+      <c r="AD99" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>220</v>
       </c>
@@ -10334,8 +13233,35 @@
         <f>_xlfn.XLOOKUP(P100,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>3.2</v>
       </c>
+      <c r="X100" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M100,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y100" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M100,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Gold</v>
+      </c>
+      <c r="Z100" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G100,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>J&amp;T Express</v>
+      </c>
+      <c r="AA100" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G100,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB100" s="1">
+        <f>_xlfn.XLOOKUP(G100,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC100" s="7">
+        <f>_xlfn.XLOOKUP(G100,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>15000</v>
+      </c>
+      <c r="AD100" s="1" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>221</v>
       </c>
@@ -10415,6 +13341,33 @@
       <c r="W101" s="1" t="str">
         <f>_xlfn.XLOOKUP(P101,[2]Master_Product_Catalog!$A$2:$A$16,[2]Master_Product_Catalog!$G$2:$G$16,"Nothing")</f>
         <v>0.3</v>
+      </c>
+      <c r="X101" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M101,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$D$2:$D$11)</f>
+        <v>Jawa Tengah</v>
+      </c>
+      <c r="Y101" s="1" t="str">
+        <f>_xlfn.XLOOKUP(M101,[1]Master_Customer_Profile!$A$2:$A$11,[1]Master_Customer_Profile!$G$2:$G$11)</f>
+        <v>Platinum</v>
+      </c>
+      <c r="Z101" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G101,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$B$2:$B$7)</f>
+        <v>SiCepat</v>
+      </c>
+      <c r="AA101" s="1" t="str">
+        <f>_xlfn.XLOOKUP(G101,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$C$2:$C$7)</f>
+        <v>Express</v>
+      </c>
+      <c r="AB101" s="1">
+        <f>_xlfn.XLOOKUP(G101,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$D$2:$D$7)</f>
+        <v>2</v>
+      </c>
+      <c r="AC101" s="7">
+        <f>_xlfn.XLOOKUP(G101,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
+        <v>16000</v>
+      </c>
+      <c r="AD101" s="1" t="e">
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/Excel/advanced_assessment_project/Raw_Transactions_2024_finish.xlsx
+++ b/Exam/Excel/advanced_assessment_project/Raw_Transactions_2024_finish.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\Project\Data-Analyst\Exam\Excel\advanced_assessment_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A8E13B-F97A-4E0D-B2F6-BDDED7910EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB02D64-0268-481D-92B3-6BDD6F6B67F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{56521A79-FDF7-45C8-BAA3-ABC64B3F8849}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,28 +36,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2027,6 +2006,105 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Master_Commission_Rule"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>VIP</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>Gold</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>Silver</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>Standard</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>Electronics</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>0.05</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>0.04</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>0.03</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>0.02</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>Fashion</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>0.08</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>0.07</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>0.05</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>0.04</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>Home &amp; Living</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>0.06</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>0.05</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>0.04</v>
+          </cell>
+          <cell r="E4" t="str">
+            <v>0.03</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>Beauty &amp; Health</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>0.1</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>0.08</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>0.06</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>0.05</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2344,7 +2422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A4B63D-0D46-44D9-8B15-778A85DACDCF}">
-  <dimension ref="A1:AD101"/>
+  <dimension ref="A1:AG101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -2377,7 +2455,7 @@
     <col min="30" max="30" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2469,7 +2547,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -2574,12 +2652,12 @@
         <f>_xlfn.XLOOKUP(G2,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD2" s="1" t="e" cm="1">
-        <f t="array" ref="AD2:AD101">INDEX(MATCH(S2,S2:S101,0),MATCH(Y2:Y101,0))</f>
-        <v>#N/A</v>
+      <c r="AD2" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S2,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y2,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -2684,11 +2762,20 @@
         <f>_xlfn.XLOOKUP(G3,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD3" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD3" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S3,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y3,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
+      </c>
+      <c r="AF3">
+        <f>MATCH(S2,[4]Master_Commission_Rule!$A$2:$A$5,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG3">
+        <f>MATCH(Y4,[4]Master_Commission_Rule!$B$1:$E$1,0)</f>
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -2793,11 +2880,12 @@
         <f>_xlfn.XLOOKUP(G4,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD4" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD4" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S4,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y4,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.08</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
@@ -2902,11 +2990,12 @@
         <f>_xlfn.XLOOKUP(G5,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD5" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD5" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S5,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y5,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.07</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
@@ -3011,11 +3100,12 @@
         <f>_xlfn.XLOOKUP(G6,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>25000</v>
       </c>
-      <c r="AD6" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD6" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S6,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y6,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.08</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
@@ -3120,11 +3210,12 @@
         <f>_xlfn.XLOOKUP(G7,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD7" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD7" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S7,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y7,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>49</v>
       </c>
@@ -3229,11 +3320,12 @@
         <f>_xlfn.XLOOKUP(G8,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>25000</v>
       </c>
-      <c r="AD8" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD8" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S8,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y8,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>51</v>
       </c>
@@ -3338,11 +3430,12 @@
         <f>_xlfn.XLOOKUP(G9,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD9" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD9" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S9,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y9,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>55</v>
       </c>
@@ -3447,11 +3540,12 @@
         <f>_xlfn.XLOOKUP(G10,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD10" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD10" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S10,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y10,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.03</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>58</v>
       </c>
@@ -3556,11 +3650,12 @@
         <f>_xlfn.XLOOKUP(G11,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD11" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD11" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S11,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y11,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>60</v>
       </c>
@@ -3665,11 +3760,12 @@
         <f>_xlfn.XLOOKUP(G12,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD12" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD12" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S12,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y12,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>63</v>
       </c>
@@ -3774,11 +3870,12 @@
         <f>_xlfn.XLOOKUP(G13,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD13" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD13" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S13,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y13,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>66</v>
       </c>
@@ -3883,11 +3980,12 @@
         <f>_xlfn.XLOOKUP(G14,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>8000</v>
       </c>
-      <c r="AD14" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD14" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S14,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y14,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>68</v>
       </c>
@@ -3992,11 +4090,12 @@
         <f>_xlfn.XLOOKUP(G15,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD15" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD15" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S15,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y15,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>71</v>
       </c>
@@ -4101,8 +4200,9 @@
         <f>_xlfn.XLOOKUP(G16,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>8000</v>
       </c>
-      <c r="AD16" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD16" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S16,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y16,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -4210,8 +4310,9 @@
         <f>_xlfn.XLOOKUP(G17,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD17" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD17" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S17,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y17,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -4319,8 +4420,9 @@
         <f>_xlfn.XLOOKUP(G18,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD18" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD18" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S18,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y18,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -4428,8 +4530,9 @@
         <f>_xlfn.XLOOKUP(G19,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD19" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD19" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S19,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y19,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
@@ -4537,8 +4640,9 @@
         <f>_xlfn.XLOOKUP(G20,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD20" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD20" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S20,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y20,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -4646,8 +4750,9 @@
         <f>_xlfn.XLOOKUP(G21,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>8000</v>
       </c>
-      <c r="AD21" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD21" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S21,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y21,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4756,6 +4861,7 @@
         <v>15000</v>
       </c>
       <c r="AD22" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S22,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y22,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -4864,8 +4970,9 @@
         <f>_xlfn.XLOOKUP(G23,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD23" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD23" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S23,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y23,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -4973,8 +5080,9 @@
         <f>_xlfn.XLOOKUP(G24,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD24" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD24" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S24,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y24,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -5083,6 +5191,7 @@
         <v>12000</v>
       </c>
       <c r="AD25" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S25,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y25,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -5191,8 +5300,9 @@
         <f>_xlfn.XLOOKUP(G26,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD26" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD26" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S26,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y26,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -5300,8 +5410,9 @@
         <f>_xlfn.XLOOKUP(G27,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD27" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD27" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S27,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y27,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.07</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -5409,8 +5520,9 @@
         <f>_xlfn.XLOOKUP(G28,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD28" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD28" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S28,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y28,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -5518,8 +5630,9 @@
         <f>_xlfn.XLOOKUP(G29,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD29" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD29" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S29,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y29,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -5627,8 +5740,9 @@
         <f>_xlfn.XLOOKUP(G30,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD30" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD30" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S30,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y30,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -5736,8 +5850,9 @@
         <f>_xlfn.XLOOKUP(G31,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>8000</v>
       </c>
-      <c r="AD31" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD31" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S31,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y31,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -5845,8 +5960,9 @@
         <f>_xlfn.XLOOKUP(G32,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD32" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD32" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S32,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y32,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -5954,8 +6070,9 @@
         <f>_xlfn.XLOOKUP(G33,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>8000</v>
       </c>
-      <c r="AD33" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD33" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S33,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y33,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -6063,8 +6180,9 @@
         <f>_xlfn.XLOOKUP(G34,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD34" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD34" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S34,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y34,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -6172,8 +6290,9 @@
         <f>_xlfn.XLOOKUP(G35,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD35" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD35" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S35,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y35,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
@@ -6281,8 +6400,9 @@
         <f>_xlfn.XLOOKUP(G36,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD36" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD36" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S36,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y36,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.07</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
@@ -6391,6 +6511,7 @@
         <v>25000</v>
       </c>
       <c r="AD37" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S37,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y37,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -6499,8 +6620,9 @@
         <f>_xlfn.XLOOKUP(G38,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD38" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD38" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S38,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y38,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.07</v>
       </c>
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.25">
@@ -6608,8 +6730,9 @@
         <f>_xlfn.XLOOKUP(G39,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>8000</v>
       </c>
-      <c r="AD39" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD39" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S39,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y39,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.25">
@@ -6717,8 +6840,9 @@
         <f>_xlfn.XLOOKUP(G40,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>25000</v>
       </c>
-      <c r="AD40" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD40" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S40,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y40,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.25">
@@ -6826,8 +6950,9 @@
         <f>_xlfn.XLOOKUP(G41,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD41" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD41" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S41,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y41,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.25">
@@ -6935,8 +7060,9 @@
         <f>_xlfn.XLOOKUP(G42,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>8000</v>
       </c>
-      <c r="AD42" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD42" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S42,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y42,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.25">
@@ -7045,6 +7171,7 @@
         <v>12000</v>
       </c>
       <c r="AD43" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S43,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y43,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -7153,8 +7280,9 @@
         <f>_xlfn.XLOOKUP(G44,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD44" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD44" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S44,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y44,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.25">
@@ -7262,8 +7390,9 @@
         <f>_xlfn.XLOOKUP(G45,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD45" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD45" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S45,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y45,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.25">
@@ -7371,8 +7500,9 @@
         <f>_xlfn.XLOOKUP(G46,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD46" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD46" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S46,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y46,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.25">
@@ -7480,8 +7610,9 @@
         <f>_xlfn.XLOOKUP(G47,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD47" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD47" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S47,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y47,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.25">
@@ -7590,6 +7721,7 @@
         <v>10000</v>
       </c>
       <c r="AD48" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S48,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y48,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -7698,8 +7830,9 @@
         <f>_xlfn.XLOOKUP(G49,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD49" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD49" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S49,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y49,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="50" spans="1:30" x14ac:dyDescent="0.25">
@@ -7807,8 +7940,9 @@
         <f>_xlfn.XLOOKUP(G50,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD50" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD50" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S50,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y50,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="51" spans="1:30" x14ac:dyDescent="0.25">
@@ -7916,8 +8050,9 @@
         <f>_xlfn.XLOOKUP(G51,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD51" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD51" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S51,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y51,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="52" spans="1:30" x14ac:dyDescent="0.25">
@@ -8025,8 +8160,9 @@
         <f>_xlfn.XLOOKUP(G52,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD52" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD52" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S52,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y52,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.25">
@@ -8134,8 +8270,9 @@
         <f>_xlfn.XLOOKUP(G53,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD53" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD53" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S53,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y53,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.25">
@@ -8243,8 +8380,9 @@
         <f>_xlfn.XLOOKUP(G54,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD54" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD54" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S54,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y54,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.25">
@@ -8353,6 +8491,7 @@
         <v>15000</v>
       </c>
       <c r="AD55" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S55,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y55,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -8461,8 +8600,9 @@
         <f>_xlfn.XLOOKUP(G56,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD56" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD56" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S56,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y56,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="57" spans="1:30" x14ac:dyDescent="0.25">
@@ -8571,6 +8711,7 @@
         <v>8000</v>
       </c>
       <c r="AD57" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S57,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y57,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -8679,8 +8820,9 @@
         <f>_xlfn.XLOOKUP(G58,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD58" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD58" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S58,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y58,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.25">
@@ -8788,8 +8930,9 @@
         <f>_xlfn.XLOOKUP(G59,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD59" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD59" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S59,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y59,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.25">
@@ -8897,8 +9040,9 @@
         <f>_xlfn.XLOOKUP(G60,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD60" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD60" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S60,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y60,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="61" spans="1:30" x14ac:dyDescent="0.25">
@@ -9006,8 +9150,9 @@
         <f>_xlfn.XLOOKUP(G61,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD61" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD61" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S61,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y61,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.25">
@@ -9116,6 +9261,7 @@
         <v>8000</v>
       </c>
       <c r="AD62" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S62,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y62,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -9224,8 +9370,9 @@
         <f>_xlfn.XLOOKUP(G63,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD63" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD63" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S63,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y63,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.25">
@@ -9333,8 +9480,9 @@
         <f>_xlfn.XLOOKUP(G64,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>25000</v>
       </c>
-      <c r="AD64" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD64" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S64,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y64,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.25">
@@ -9442,8 +9590,9 @@
         <f>_xlfn.XLOOKUP(G65,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD65" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD65" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S65,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y65,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="66" spans="1:30" x14ac:dyDescent="0.25">
@@ -9551,8 +9700,9 @@
         <f>_xlfn.XLOOKUP(G66,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD66" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD66" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S66,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y66,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.25">
@@ -9660,8 +9810,9 @@
         <f>_xlfn.XLOOKUP(G67,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD67" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD67" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S67,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y67,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.25">
@@ -9769,8 +9920,9 @@
         <f>_xlfn.XLOOKUP(G68,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD68" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD68" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S68,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y68,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.25">
@@ -9879,6 +10031,7 @@
         <v>15000</v>
       </c>
       <c r="AD69" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S69,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y69,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -9987,8 +10140,9 @@
         <f>_xlfn.XLOOKUP(G70,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD70" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD70" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S70,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y70,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.25">
@@ -10097,6 +10251,7 @@
         <v>12000</v>
       </c>
       <c r="AD71" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S71,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y71,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -10206,6 +10361,7 @@
         <v>16000</v>
       </c>
       <c r="AD72" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S72,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y72,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -10315,6 +10471,7 @@
         <v>16000</v>
       </c>
       <c r="AD73" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S73,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y73,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -10423,8 +10580,9 @@
         <f>_xlfn.XLOOKUP(G74,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD74" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD74" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S74,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y74,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="75" spans="1:30" x14ac:dyDescent="0.25">
@@ -10532,8 +10690,9 @@
         <f>_xlfn.XLOOKUP(G75,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>8000</v>
       </c>
-      <c r="AD75" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD75" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S75,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y75,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="76" spans="1:30" x14ac:dyDescent="0.25">
@@ -10641,8 +10800,9 @@
         <f>_xlfn.XLOOKUP(G76,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>8000</v>
       </c>
-      <c r="AD76" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD76" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S76,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y76,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="77" spans="1:30" x14ac:dyDescent="0.25">
@@ -10750,8 +10910,9 @@
         <f>_xlfn.XLOOKUP(G77,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD77" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD77" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S77,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y77,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="78" spans="1:30" x14ac:dyDescent="0.25">
@@ -10859,8 +11020,9 @@
         <f>_xlfn.XLOOKUP(G78,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>25000</v>
       </c>
-      <c r="AD78" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD78" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S78,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y78,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="79" spans="1:30" x14ac:dyDescent="0.25">
@@ -10968,8 +11130,9 @@
         <f>_xlfn.XLOOKUP(G79,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD79" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD79" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S79,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y79,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.07</v>
       </c>
     </row>
     <row r="80" spans="1:30" x14ac:dyDescent="0.25">
@@ -11077,8 +11240,9 @@
         <f>_xlfn.XLOOKUP(G80,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>25000</v>
       </c>
-      <c r="AD80" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD80" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S80,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y80,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
     <row r="81" spans="1:30" x14ac:dyDescent="0.25">
@@ -11187,6 +11351,7 @@
         <v>8000</v>
       </c>
       <c r="AD81" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S81,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y81,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -11296,6 +11461,7 @@
         <v>15000</v>
       </c>
       <c r="AD82" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S82,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y82,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -11404,8 +11570,9 @@
         <f>_xlfn.XLOOKUP(G83,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD83" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD83" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S83,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y83,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="84" spans="1:30" x14ac:dyDescent="0.25">
@@ -11513,8 +11680,9 @@
         <f>_xlfn.XLOOKUP(G84,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>25000</v>
       </c>
-      <c r="AD84" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD84" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S84,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y84,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="85" spans="1:30" x14ac:dyDescent="0.25">
@@ -11622,8 +11790,9 @@
         <f>_xlfn.XLOOKUP(G85,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD85" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD85" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S85,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y85,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="86" spans="1:30" x14ac:dyDescent="0.25">
@@ -11731,8 +11900,9 @@
         <f>_xlfn.XLOOKUP(G86,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD86" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD86" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S86,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y86,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
     <row r="87" spans="1:30" x14ac:dyDescent="0.25">
@@ -11840,8 +12010,9 @@
         <f>_xlfn.XLOOKUP(G87,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>25000</v>
       </c>
-      <c r="AD87" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD87" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S87,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y87,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="88" spans="1:30" x14ac:dyDescent="0.25">
@@ -11949,8 +12120,9 @@
         <f>_xlfn.XLOOKUP(G88,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD88" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD88" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S88,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y88,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="89" spans="1:30" x14ac:dyDescent="0.25">
@@ -12058,8 +12230,9 @@
         <f>_xlfn.XLOOKUP(G89,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD89" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD89" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S89,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y89,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.07</v>
       </c>
     </row>
     <row r="90" spans="1:30" x14ac:dyDescent="0.25">
@@ -12168,6 +12341,7 @@
         <v>15000</v>
       </c>
       <c r="AD90" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S90,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y90,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -12276,8 +12450,9 @@
         <f>_xlfn.XLOOKUP(G91,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>12000</v>
       </c>
-      <c r="AD91" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD91" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S91,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y91,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="92" spans="1:30" x14ac:dyDescent="0.25">
@@ -12385,8 +12560,9 @@
         <f>_xlfn.XLOOKUP(G92,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>25000</v>
       </c>
-      <c r="AD92" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD92" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S92,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y92,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="93" spans="1:30" x14ac:dyDescent="0.25">
@@ -12494,8 +12670,9 @@
         <f>_xlfn.XLOOKUP(G93,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD93" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD93" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S93,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y93,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="94" spans="1:30" x14ac:dyDescent="0.25">
@@ -12604,6 +12781,7 @@
         <v>12000</v>
       </c>
       <c r="AD94" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S94,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y94,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -12712,8 +12890,9 @@
         <f>_xlfn.XLOOKUP(G95,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>16000</v>
       </c>
-      <c r="AD95" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD95" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S95,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y95,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="96" spans="1:30" x14ac:dyDescent="0.25">
@@ -12821,8 +13000,9 @@
         <f>_xlfn.XLOOKUP(G96,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>8000</v>
       </c>
-      <c r="AD96" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD96" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S96,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y96,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="97" spans="1:30" x14ac:dyDescent="0.25">
@@ -12930,8 +13110,9 @@
         <f>_xlfn.XLOOKUP(G97,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD97" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD97" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S97,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y97,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.07</v>
       </c>
     </row>
     <row r="98" spans="1:30" x14ac:dyDescent="0.25">
@@ -13039,8 +13220,9 @@
         <f>_xlfn.XLOOKUP(G98,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>8000</v>
       </c>
-      <c r="AD98" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD98" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S98,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y98,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.04</v>
       </c>
     </row>
     <row r="99" spans="1:30" x14ac:dyDescent="0.25">
@@ -13148,8 +13330,9 @@
         <f>_xlfn.XLOOKUP(G99,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>10000</v>
       </c>
-      <c r="AD99" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD99" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S99,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y99,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.06</v>
       </c>
     </row>
     <row r="100" spans="1:30" x14ac:dyDescent="0.25">
@@ -13257,8 +13440,9 @@
         <f>_xlfn.XLOOKUP(G100,[3]Master_SLA_Shipping!$A$2:$A$7,[3]Master_SLA_Shipping!$E$2:$E$7)</f>
         <v>15000</v>
       </c>
-      <c r="AD100" s="1" t="e">
-        <v>#N/A</v>
+      <c r="AD100" s="1" t="str">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S100,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y100,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="101" spans="1:30" x14ac:dyDescent="0.25">
@@ -13367,6 +13551,7 @@
         <v>16000</v>
       </c>
       <c r="AD101" s="1" t="e">
+        <f>INDEX([4]Master_Commission_Rule!$B$2:$E$5,MATCH(S101,[4]Master_Commission_Rule!$A$2:$A$5,0),MATCH(Y101,[4]Master_Commission_Rule!$B$1:$E$1,0))</f>
         <v>#N/A</v>
       </c>
     </row>
